--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$H$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$H$256</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,21 +512,21 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>亞昕 昕富琚</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -546,21 +546,21 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>全坤雙星</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -584,17 +584,17 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -614,21 +614,25 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+          <t>印象左岸</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -648,21 +652,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>宏道巴黎花都</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -682,21 +686,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+          <t>悅田吾澍</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -716,21 +724,21 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>新富雙宇</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -750,21 +758,21 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>新濠漾4-英倫公園</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -784,21 +792,21 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>星河帝寶</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -818,21 +826,21 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
+          <t>晴合豐川</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -852,21 +860,25 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+          <t>晴空大地</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -886,21 +898,25 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>凱越豐汎</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+          <t>永悅天漾</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -920,25 +936,21 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>印象左岸</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>82~89萬元/坪</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15~35坪1~3房</t>
-        </is>
-      </c>
+          <t>漢皇一寓</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -958,25 +970,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>悅田吾澍</t>
+          <t>環泥水澍</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77~88萬元/坪</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>17~29坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -996,25 +1008,21 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>晴空大地</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>58~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18~37坪2房</t>
-        </is>
-      </c>
+          <t>福容大都會</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1034,25 +1042,21 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>永悅天漾</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>62~68萬元/坪</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>27~33坪3房</t>
-        </is>
-      </c>
+          <t>萊茵水花園</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1072,25 +1076,25 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>環泥水澍</t>
+          <t>都廳大院</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78~86萬元/坪</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15~18坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1105,30 +1109,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>三重區</t>
+          <t>五股區</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>都廳大院</t>
+          <t>九揚威騰堡</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65~75萬元/坪</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>18~44坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1148,25 +1152,25 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>九揚威騰堡</t>
+          <t>九揚雙子星</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45~48萬元/坪</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20~33坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1186,25 +1190,25 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>九揚雙子星</t>
+          <t>四季禾禾</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>16~33坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1224,25 +1228,25 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>四季禾禾</t>
+          <t>幸福享享</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>20~26坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1262,25 +1266,21 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>幸福享享</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>53萬元/坪</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>17~31.41坪2~3房</t>
-        </is>
-      </c>
+          <t>快樂王國-夢享城</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1305,20 +1305,20 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48~50萬元/坪</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>20~36坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1343,20 +1343,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47~50萬元/坪</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>15~50坪1房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1381,20 +1381,20 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57~59萬元/坪</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>23~29坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1419,20 +1419,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46~51萬元/坪</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>21~30坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1457,20 +1457,20 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>58~63萬元/坪</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>20~27坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1495,20 +1495,20 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>48~52萬元/坪</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>15~28坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1533,20 +1533,20 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>54~58萬元/坪</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>27~33坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1571,20 +1571,20 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40~42萬元/坪</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>18~28坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1609,20 +1609,20 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>25~31坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1642,25 +1642,21 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>地景富邑</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>56~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>26~46坪2~4房</t>
-        </is>
-      </c>
+          <t>合嘉楓疆</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1680,25 +1676,25 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>地景新世代</t>
+          <t>地景富邑</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>62~68萬元/坪</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>15~33坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1718,25 +1714,25 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>百達莊園</t>
+          <t>地景新世代</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>27~47坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1756,25 +1752,21 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>築。滿滿</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>56萬元/坪</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>26~42坪2房</t>
-        </is>
-      </c>
+          <t>明志書苑</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1794,25 +1786,25 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>閱讀台灣</t>
+          <t>百達莊園</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>63萬元/坪</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>26~38坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1827,30 +1819,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>蘆洲區</t>
+          <t>泰山區</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>鴻悅玖馥</t>
+          <t>築。滿滿</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>65~69萬元/坪</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>15.97~28.69坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1860,35 +1852,31 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>土城樹林線</t>
+          <t>三重蘆洲線</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>三峽區</t>
+          <t>泰山區</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>立信園立方</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>60萬元/坪</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>14~23坪2~3房</t>
-        </is>
-      </c>
+          <t>義泰信</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1898,22 +1886,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>土城樹林線</t>
+          <t>三重蘆洲線</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>泰山區</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>AIT禾運智價園區</t>
+          <t>閱讀台灣</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>50~55萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -1922,7 +1910,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1932,35 +1924,31 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>土城樹林線</t>
+          <t>三重蘆洲線</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>蘆洲區</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>世界花園</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>58萬元/坪</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>0坪2~4房</t>
-        </is>
-      </c>
+          <t>當代集賢-琢謙</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1970,35 +1958,35 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>土城樹林線</t>
+          <t>三重蘆洲線</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>蘆洲區</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>仁基京品</t>
+          <t>鴻悅玖馥</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>48~53萬元/坪</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>18~36坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2013,30 +2001,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>三峽區</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>和耀美居</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>55~60萬元/坪</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>26~37坪2~3房</t>
-        </is>
-      </c>
+          <t>合昶澄真</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2051,30 +2035,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>三峽區</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>寶佳淳青</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>58~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>24.04~37.75坪2~3房</t>
-        </is>
-      </c>
+          <t>家豪.大將1</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2089,26 +2069,26 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>三峽區</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>智富時代</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>38~40萬元/坪</t>
-        </is>
-      </c>
+          <t>文傑愛樂</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2123,30 +2103,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>三峽區</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>有富富玉</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>52~55萬元/坪</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>18~41坪1~4房</t>
-        </is>
-      </c>
+          <t>文傑鉑悅</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2161,17 +2137,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>土城區</t>
+          <t>三峽區</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>永寧寶磊III</t>
+          <t>立信園立方</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>50~55萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2180,7 +2156,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2200,25 +2180,25 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>皇翔MRT</t>
+          <t>AIT禾運智價園區</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>57~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>12~32坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2238,25 +2218,25 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>紅布朗花園</t>
+          <t>世界花園</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>50~56萬元/坪</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>17~29坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2276,25 +2256,25 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>綠見竺</t>
+          <t>仁基京品</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>47~54萬元/坪</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>30~45坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2314,25 +2294,21 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>迴東騰</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>80萬元/坪</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>25~36坪2~3房</t>
-        </is>
-      </c>
+          <t>合康雙匯</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2352,25 +2328,21 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>金城舞2-都心花園</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>45~48萬元/坪</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>19~46坪2~4房</t>
-        </is>
-      </c>
+          <t>合謙上謙城</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2385,26 +2357,30 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>和耀美居</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2419,26 +2395,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>寶佳淳青</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2453,26 +2433,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>智富時代</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2487,26 +2471,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
+          <t>有富.彩玉</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+      <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2521,26 +2505,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>有富富玉</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2555,26 +2543,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
+          <t>有富寶玉</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+      <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2589,26 +2577,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
+          <t>朗沐L'AMOUR</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+      <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2623,26 +2611,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>永寧寶磊III</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2657,26 +2649,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>皇翔MRT</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2691,26 +2687,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
+          <t>福容雙捷A+</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2725,26 +2721,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>紅布朗花園</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2759,26 +2759,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>27~31坪2~3房</t>
-        </is>
-      </c>
+          <t>綠見竺</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2793,30 +2797,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>欣懋川玥</t>
+          <t>迴東騰</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>41~47萬元/坪</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>21~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2831,30 +2835,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>騰翔樹与苑</t>
+          <t>金城舞2-都心花園</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>43~46萬元/坪</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>23~33坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2869,30 +2873,26 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>鶯歌區</t>
+          <t>樹林區</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>京懋明日和</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>53~58萬元/坪</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>24~40坪2~3房</t>
-        </is>
-      </c>
+          <t>欣好蒔光</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2907,30 +2907,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>鶯歌區</t>
+          <t>樹林區</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>京澄為德</t>
+          <t>欣懋川玥</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>53~57萬元/坪</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>28~44坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2945,30 +2945,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>鶯歌區</t>
+          <t>樹林區</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>合嘉菁緻</t>
+          <t>騰翔樹与苑</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>39~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>23~32坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2988,25 +2988,25 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>合康世紀滙</t>
+          <t>京懋明日和</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>48~53萬元/坪</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>19~32坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3026,25 +3026,25 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>景自慢</t>
+          <t>京澄為德</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>36~39萬元/坪</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>26~36坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3064,25 +3064,25 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>渼麗綻</t>
+          <t>合嘉菁緻</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>51~55萬元/坪</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>22.48~34.77坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3102,25 +3102,25 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>金和昌仰沐</t>
+          <t>合康世紀滙</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>52~56萬元/坪</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>25.85~46.94坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3140,25 +3140,21 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>鳴日之城-日禾</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>46~49萬元/坪</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>28~34坪2~3房</t>
-        </is>
-      </c>
+          <t>國華綻</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -3168,35 +3164,31 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>協富青睞</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>85~89萬元/坪</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>18.82~21.31坪2房</t>
-        </is>
-      </c>
+          <t>富霖富鄰</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -3206,35 +3198,35 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>友座紳鄰</t>
+          <t>景自慢</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>60~70萬元/坪</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>17~35坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -3244,35 +3236,35 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>名毅吾山II-靚山</t>
+          <t>渼麗綻</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>55~60萬元/坪</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>25~42坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -3282,35 +3274,35 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>國揚光河</t>
+          <t>金和昌仰沐</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>88~95萬元/坪</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>22~47坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -3320,35 +3312,31 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>馥春居</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr"/>
       <c r="G79" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3358,35 +3346,35 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>鳴日之城-日禾</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
       <c r="G80" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3406,25 +3394,21 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>【欣聯鉅星科技總部】企業旗艦廠辦</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
       <c r="G81" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3444,25 +3428,25 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>協富青睞</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3482,25 +3466,25 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>友座紳鄰</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
       <c r="G83" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3520,25 +3504,25 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>名毅吾山II-靚山</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3558,25 +3542,25 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>國揚光河</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3601,20 +3585,20 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
       <c r="G86" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3634,25 +3618,25 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>東基M1</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>40~56坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3672,25 +3656,25 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>東基M1</t>
+          <t>波爾多2樂菲莊園</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>96~108萬元/坪</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>16~53坪1~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3700,35 +3684,35 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>八里區</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>波爾多2樂菲莊園</t>
+          <t>勤樸天翔</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>58~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>18~54坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3748,25 +3732,25 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>勤樸天翔</t>
+          <t>勤樸天逸</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>24~26萬元/坪</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>20~39坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3786,25 +3770,25 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>勤樸天逸</t>
+          <t>大新田幸福之森</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>26~28萬元/坪</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>22~34坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
       <c r="G91" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3824,25 +3808,25 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>大新田幸福之森</t>
+          <t>日初</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>42~48萬元/坪</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>18~34坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3862,25 +3846,25 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>日初</t>
+          <t>紐約心光</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>23~45坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3900,25 +3884,21 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>紐約心光</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>41~46萬元/坪</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>24.88~37.09坪2~3房</t>
-        </is>
-      </c>
+          <t>豐邑港麗</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr"/>
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3943,20 +3923,20 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>72~76萬元/坪</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>28~51坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3981,20 +3961,20 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>23~35坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4019,7 +3999,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>55~60萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
@@ -4028,7 +4008,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4053,20 +4037,20 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>48~49萬元/坪</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>18~30坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4091,20 +4075,20 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>63~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>28~39.6坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
       <c r="G99" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4124,25 +4108,21 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>富都馨</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>75~83萬元/坪</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>16~28坪1~3房</t>
-        </is>
-      </c>
+          <t>富都新玉-富都區</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr"/>
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4162,25 +4142,21 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>新月大河</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>65~75萬元/坪</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>20~30坪2~3房</t>
-        </is>
-      </c>
+          <t>富都新玉-新玉區</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr"/>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4200,25 +4176,25 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>自由之丘</t>
+          <t>富都馨</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>70~75萬元/坪</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>17~43坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4238,12 +4214,12 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>西勝時星</t>
+          <t>新月大河</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>63~67萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
@@ -4252,7 +4228,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4272,25 +4252,21 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>這一站，幸福</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>46~58萬元/坪</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>14~50坪1~3房</t>
-        </is>
-      </c>
+          <t>日和淳</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr"/>
       <c r="G104" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4305,26 +4281,26 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>中光極</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>54~56萬元/坪</t>
-        </is>
-      </c>
+          <t>春城麗都</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
       <c r="F105" s="2" t="inlineStr"/>
       <c r="G105" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4339,30 +4315,26 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>宏樸 曉霧</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>68~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>18~28坪1~2房</t>
-        </is>
-      </c>
+          <t>皇鼎心莊</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr"/>
       <c r="G106" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4377,17 +4349,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>富創得AI新創園區</t>
+          <t>自由之丘</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>55~80萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -4396,7 +4368,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4411,30 +4387,30 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>富堡晶鑄</t>
+          <t>西勝時星</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>75~80萬元/坪</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>0坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
       <c r="G108" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4449,30 +4425,30 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>山侘一生</t>
+          <t>這一站，幸福</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>70~80萬元/坪</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>18~62.3坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
       <c r="G109" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4487,30 +4463,26 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-林境</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>54~57萬元/坪</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>20~25坪2房</t>
-        </is>
-      </c>
+          <t>邦瓏雍玥</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr"/>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4530,25 +4502,25 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-逸境</t>
+          <t>中光極</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>48~56萬元/坪</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>17~32坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
       <c r="G111" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4568,25 +4540,21 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴中山</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>40~55坪2~3房</t>
-        </is>
-      </c>
+          <t>九揚華樂</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
       <c r="G112" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4606,25 +4574,21 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>築禾琢玥</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>18~40坪2~3房</t>
-        </is>
-      </c>
+          <t>原昕吾旭</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr"/>
       <c r="G113" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4644,25 +4608,25 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>群和 FUTURE LINK</t>
+          <t>宏樸 曉霧</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>59~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>18~34坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
       <c r="G114" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4682,21 +4646,21 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>家悦美</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+      <c r="F115" s="2" t="inlineStr"/>
       <c r="G115" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4716,21 +4680,25 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+          <t>富創得AI新創園區</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4750,21 +4718,25 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+          <t>富堡晶鑄</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
       <c r="G117" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4784,21 +4756,21 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>富浤一響</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+      <c r="F118" s="2" t="inlineStr"/>
       <c r="G118" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4818,21 +4790,25 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr"/>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+          <t>山侘一生</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
       <c r="G119" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4852,21 +4828,21 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>易捷聿白</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+      <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4886,21 +4862,25 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+          <t>森鉅M-林境</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
       <c r="G121" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4920,21 +4900,25 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+          <t>森鉅M-逸境</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4954,21 +4938,21 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>瑞德豐錦</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+      <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4988,21 +4972,21 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>福樺中央大樓</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+      <c r="F124" s="2" t="inlineStr"/>
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5022,21 +5006,25 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+          <t>福樺富貴中山</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -5056,21 +5044,21 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>立陽頤興</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>26.6~39.53坪2~4房</t>
-        </is>
-      </c>
+      <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -5090,25 +5078,25 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>長耀里</t>
+          <t>築禾琢玥</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>50~56萬元/坪</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>18~29坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -5118,35 +5106,35 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>和雅琚</t>
+          <t>群和 FUTURE LINK</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>82~85萬元/坪</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>12~28坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -5156,31 +5144,31 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>55~60萬元/坪</t>
-        </is>
-      </c>
+          <t>聯虹珺玥</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -5190,35 +5178,31 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>75~88萬元/坪</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>21~44坪2~3房</t>
-        </is>
-      </c>
+          <t>聿見美璟</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -5228,35 +5212,31 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>60~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>15~41坪1~3房</t>
-        </is>
-      </c>
+          <t>謙旭</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -5266,35 +5246,35 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>長耀里</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>72~80萬元/坪</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>13~61坪1~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
       <c r="G132" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -5314,25 +5294,21 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>60~67萬元/坪</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>25~47坪2~3房</t>
-        </is>
-      </c>
+          <t>双捷橙品</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr"/>
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -5347,30 +5323,30 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>和雅琚</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>120~131萬元/坪</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>25~55坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
       <c r="G134" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -5385,30 +5361,26 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>85~96萬元/坪</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>24.1~38.59坪2~3房</t>
-        </is>
-      </c>
+          <t>好植</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -5423,30 +5395,30 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>81~92萬元/坪</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>22~33坪開放式格局~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
       <c r="G136" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -5461,30 +5433,26 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>77~79萬元/坪</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>32.45~32.75坪2房</t>
-        </is>
-      </c>
+          <t>東瑩玥光-涵光區</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -5499,30 +5467,26 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>86萬元/坪</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>21~32坪2~3房</t>
-        </is>
-      </c>
+          <t>欽禾</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr"/>
       <c r="G138" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -5537,30 +5501,26 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>95~105萬元/坪</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>18~42坪2~3房</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr"/>
       <c r="G139" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -5575,30 +5535,30 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>55~59萬元/坪</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
       <c r="G140" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -5613,30 +5573,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>45~55萬元/坪</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>17~34坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -5651,30 +5611,30 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>68~72萬元/坪</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>20~39坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5689,30 +5649,30 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>55~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>17~33坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
       <c r="G143" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5732,25 +5692,25 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>65~70萬元/坪</t>
-        </is>
-      </c>
-      <c r="F144" s="2" t="inlineStr">
-        <is>
-          <t>20~33坪開放式格局~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5770,25 +5730,21 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
-        </is>
-      </c>
-      <c r="E145" s="2" t="inlineStr">
-        <is>
-          <t>82~91萬元/坪</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>18~36坪開放式格局~3房</t>
-        </is>
-      </c>
+          <t>京東賞</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5808,25 +5764,25 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>108~125萬元/坪</t>
-        </is>
-      </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>26~50坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -5846,25 +5802,25 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>大業</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>90~105萬元/坪</t>
-        </is>
-      </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>26~54坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -5879,26 +5835,30 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>心晴好</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -5913,26 +5873,30 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>悠森學</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -5947,26 +5911,30 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr"/>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>新板東京</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -5981,26 +5949,26 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+      <c r="F151" s="2" t="inlineStr"/>
       <c r="G151" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -6015,26 +5983,30 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>永雄府中心</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -6049,26 +6021,30 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>江翠Park</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -6083,26 +6059,30 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr"/>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>甲山林帝景6號</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -6117,26 +6097,30 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr"/>
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -6151,26 +6135,26 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>立信帝國花園廣場</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr"/>
-      <c r="F156" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+      <c r="F156" s="2" t="inlineStr"/>
       <c r="G156" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -6185,26 +6169,30 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>立信晴朗</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -6219,26 +6207,30 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr"/>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>立信雙星</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -6253,26 +6245,30 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>25~43坪2~3房</t>
-        </is>
-      </c>
+          <t>遠揚之森A⁺</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -6287,30 +6283,30 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>鑄見</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>63~73萬元/坪</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>15.8~24.7坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -6320,31 +6316,31 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>香榭京宴</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+      <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -6354,31 +6350,31 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>友座豐禾</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr"/>
-      <c r="F162" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+      <c r="F162" s="2" t="inlineStr"/>
       <c r="G162" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -6388,31 +6384,31 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>漢皇River Sky</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+      <c r="F163" s="2" t="inlineStr"/>
       <c r="G163" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -6422,31 +6418,31 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+      <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -6456,31 +6452,35 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr"/>
-      <c r="F165" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr"/>
       <c r="G165" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -6504,17 +6504,17 @@
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr"/>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+      <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6534,21 +6534,21 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>文心慕慕</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+      <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6568,21 +6568,25 @@
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr"/>
-      <c r="F168" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>東煒大局</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr"/>
       <c r="G168" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -6602,21 +6606,25 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>汐科爵鼎</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr"/>
       <c r="G169" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -6636,21 +6644,25 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr"/>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>美麗山林</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -6670,21 +6682,25 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr"/>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>雲禾月</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr"/>
       <c r="G171" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -6699,26 +6715,30 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
-        </is>
-      </c>
-      <c r="E172" s="2" t="inlineStr"/>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>23~42坪2~3房</t>
-        </is>
-      </c>
+          <t>京美晴朗</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr"/>
       <c r="G172" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -6733,26 +6753,26 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>36~38萬元/坪</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr"/>
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -6767,30 +6787,30 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>60~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>14~31坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -6805,30 +6825,30 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>35~43萬元/坪</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>26~87坪2~5房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -6843,30 +6863,30 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>60~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F176" s="2" t="inlineStr">
-        <is>
-          <t>27~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -6886,25 +6906,21 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>33~39萬元/坪</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>22~42坪2~4房</t>
-        </is>
-      </c>
+          <t>村泉蒔美</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr"/>
       <c r="G177" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -6924,25 +6940,21 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E178" s="2" t="inlineStr">
-        <is>
-          <t>39~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>25~36坪2~3房</t>
-        </is>
-      </c>
+          <t>湯泉紅樹林</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr"/>
       <c r="G178" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -6962,25 +6974,21 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>35~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>26~47坪2~4房</t>
-        </is>
-      </c>
+          <t>致茂橋豐</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -7000,50 +7008,50 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>21~35坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市（青埔）</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>青埔周邊（中壢/大園）</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>50萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr"/>
@@ -7052,7 +7060,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -7072,12 +7084,12 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>32萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr"/>
@@ -7086,7 +7098,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -7106,25 +7122,25 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>38~46萬元/坪</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>18~36坪1~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -7144,25 +7160,25 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>25~34坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
       <c r="G184" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -7182,25 +7198,25 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>25~26萬元/坪</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>20~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -7220,25 +7236,25 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>大亮FIKA</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>37萬元/坪</t>
-        </is>
-      </c>
-      <c r="F186" s="2" t="inlineStr">
-        <is>
-          <t>24~33坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -7258,25 +7274,21 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
-        </is>
-      </c>
-      <c r="E187" s="2" t="inlineStr">
-        <is>
-          <t>63~69萬元/坪</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr">
-        <is>
-          <t>15.68~21.42坪2房</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -7301,20 +7313,20 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>48~49萬元/坪</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>19~22坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -7339,20 +7351,20 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>48~49萬元/坪</t>
-        </is>
-      </c>
-      <c r="F189" s="2" t="inlineStr">
-        <is>
-          <t>19~22坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -7377,20 +7389,20 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>45~46萬元/坪</t>
-        </is>
-      </c>
-      <c r="F190" s="2" t="inlineStr">
-        <is>
-          <t>46~47坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -7410,25 +7422,21 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E191" s="2" t="inlineStr">
-        <is>
-          <t>53~63萬元/坪</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>26~47坪2房</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -7448,25 +7456,25 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>48~55萬元/坪</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>26~50坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -7486,25 +7494,21 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
-        </is>
-      </c>
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>60~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>25~39坪3房</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -7524,25 +7528,25 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -7562,25 +7566,25 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜誠泱</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F195" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -7600,25 +7604,21 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
-        </is>
-      </c>
-      <c r="E196" s="2" t="inlineStr">
-        <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F196" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>宜雄湛</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -7641,22 +7641,18 @@
           <t>家瑞No.2</t>
         </is>
       </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -7676,25 +7672,25 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -7714,25 +7710,21 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
-        </is>
-      </c>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -7752,25 +7744,21 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr"/>
       <c r="G200" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -7790,25 +7778,25 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>31~33坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -7828,25 +7816,25 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>19.89~35.63坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -7866,25 +7854,21 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>62~65萬元/坪</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>19.89~35.63坪1~3房</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -7904,25 +7888,21 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>63~78萬元/坪</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>19.74~32.11坪2~3房</t>
-        </is>
-      </c>
+          <t>晶采學</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -7942,21 +7922,21 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
-        </is>
-      </c>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>27~29萬元/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7981,20 +7961,20 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>39~42萬元/坪</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>20~24坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -8014,25 +7994,21 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>23~24萬元/坪</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr">
-        <is>
-          <t>80~129坪4~6房</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -8052,25 +8028,25 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>52~62萬元/坪</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr">
-        <is>
-          <t>21.18~31.38坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr"/>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -8090,25 +8066,25 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>45~49萬元/坪</t>
-        </is>
-      </c>
-      <c r="F209" s="2" t="inlineStr">
-        <is>
-          <t>24~42坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr"/>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -8128,25 +8104,25 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>37~42萬元/坪</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>26~46坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr"/>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -8166,25 +8142,25 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>48~55萬元/坪</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>22~36坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr"/>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -8204,12 +8180,12 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>36~38萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
@@ -8218,7 +8194,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr"/>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -8238,25 +8218,25 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>47~50萬元/坪</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>28~43.92坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr"/>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -8276,25 +8256,25 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>32~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>25~45坪1房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -8319,20 +8299,20 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>32~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="inlineStr">
-        <is>
-          <t>25~45坪1房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -8352,25 +8332,25 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>32~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>25~45坪1房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -8390,25 +8370,25 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>32~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F217" s="2" t="inlineStr">
-        <is>
-          <t>25~45坪1房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -8428,25 +8408,25 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>藍海帝國-綠景苑</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>32~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>25~45坪1房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -8466,25 +8446,21 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr">
-        <is>
-          <t>39~43萬元/坪</t>
-        </is>
-      </c>
-      <c r="F219" s="2" t="inlineStr">
-        <is>
-          <t>25~41坪2~3房</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr"/>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -8504,25 +8480,25 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>49~52萬元/坪</t>
-        </is>
-      </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>21.47~32.17坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr"/>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -8542,25 +8518,25 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>19~22萬元/坪</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>30.02~41.19坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr"/>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -8580,25 +8556,25 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>43~45萬元/坪</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>29~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr"/>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -8618,25 +8594,25 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>32~37萬元/坪</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr">
-        <is>
-          <t>23~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr"/>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -8656,25 +8632,25 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>58萬元/坪</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="inlineStr">
-        <is>
-          <t>30~38坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr"/>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -8689,30 +8665,30 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>大園區</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>24~28萬元/坪</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>22.5~44.5坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr"/>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -8727,30 +8703,30 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>大園區</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>53萬元/坪</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>25~33坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr"/>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -8770,25 +8746,25 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>24~29萬元/坪</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>80~100坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr"/>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -8808,25 +8784,25 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>34~38萬元/坪</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>29.65~45.56坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr"/>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -8846,12 +8822,12 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>44~47萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr"/>
@@ -8860,7 +8836,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr"/>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -8880,25 +8860,25 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>31~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr">
-        <is>
-          <t>22~32坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -8918,25 +8898,25 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>32~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr">
-        <is>
-          <t>26~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -8956,25 +8936,21 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
-        </is>
-      </c>
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>21坪2房</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -8994,25 +8970,25 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>63~64萬元/坪</t>
-        </is>
-      </c>
-      <c r="F233" s="2" t="inlineStr">
-        <is>
-          <t>26~37坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -9032,25 +9008,25 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>0坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -9070,25 +9046,25 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F235" s="2" t="inlineStr">
-        <is>
-          <t>0坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -9108,25 +9084,25 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>0坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -9146,25 +9122,25 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr">
-        <is>
-          <t>0坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -9184,25 +9160,25 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr">
-        <is>
-          <t>0坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -9222,25 +9198,25 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>32~33萬元/坪</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr">
-        <is>
-          <t>0坪4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -9260,25 +9236,25 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>32~34萬元/坪</t>
-        </is>
-      </c>
-      <c r="F240" s="2" t="inlineStr">
-        <is>
-          <t>0坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -9298,12 +9274,12 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>30~34萬元/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr"/>
@@ -9312,7 +9288,11 @@
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -9332,25 +9312,25 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>富總日日</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>47~49萬元/坪</t>
-        </is>
-      </c>
-      <c r="F242" s="2" t="inlineStr">
-        <is>
-          <t>23~40坪2~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -9370,25 +9350,25 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>32~38萬元/坪</t>
-        </is>
-      </c>
-      <c r="F243" s="2" t="inlineStr">
-        <is>
-          <t>0坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -9408,25 +9388,25 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>30~38萬元/坪</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>50~70坪3~4房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -9446,25 +9426,21 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
-        </is>
-      </c>
-      <c r="E245" s="2" t="inlineStr">
-        <is>
-          <t>28~33萬元/坪</t>
-        </is>
-      </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>19~25坪2~3房</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -9484,25 +9460,25 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>29~35萬元/坪</t>
-        </is>
-      </c>
-      <c r="F246" s="2" t="inlineStr">
-        <is>
-          <t>23~32坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -9522,25 +9498,25 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>29~33萬元/坪</t>
-        </is>
-      </c>
-      <c r="F247" s="2" t="inlineStr">
-        <is>
-          <t>24~42坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -9560,25 +9536,25 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>33~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="inlineStr">
-        <is>
-          <t>26~34坪2~3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -9598,25 +9574,25 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>47萬元/坪</t>
-        </is>
-      </c>
-      <c r="F249" s="2" t="inlineStr">
-        <is>
-          <t>27.38~47坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -9636,25 +9612,25 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>25~26萬元/坪</t>
-        </is>
-      </c>
-      <c r="F250" s="2" t="inlineStr">
-        <is>
-          <t>16~21坪2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -9674,25 +9650,25 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>34~35萬元/坪</t>
-        </is>
-      </c>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>16.48~26.79坪1~2房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -9712,25 +9688,25 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>逸偉A+</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>66~70萬元/坪</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>26~44坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -9750,25 +9726,21 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
-        </is>
-      </c>
-      <c r="E253" s="2" t="inlineStr">
-        <is>
-          <t>36~37萬元/坪</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>25~33坪2~3房</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -9788,25 +9760,25 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>28~36萬元/坪</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>54~72坪3~5房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr"/>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -9826,25 +9798,25 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>高誠君品</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>24~27萬元/坪</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>28~46坪3房</t>
-        </is>
-      </c>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr"/>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -9864,111 +9836,31 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>37~40萬元/坪</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="inlineStr">
-        <is>
-          <t>17~38坪2~4房</t>
-        </is>
-      </c>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>桃園市（青埔）</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>青埔周邊（中壢/大園）</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>大園區</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>35萬元/坪</t>
-        </is>
-      </c>
-      <c r="F257" s="2" t="inlineStr">
-        <is>
-          <t>24~38坪2~3房</t>
-        </is>
-      </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>預售屋</t>
-        </is>
-      </c>
-      <c r="H257" s="2" t="inlineStr"/>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>桃園市（青埔）</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>青埔周邊（中壢/大園）</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>大園區</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>高誠君品</t>
-        </is>
-      </c>
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>34~38萬元/坪</t>
-        </is>
-      </c>
-      <c r="F258" s="2" t="inlineStr">
-        <is>
-          <t>26~39坪2~3房</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>預售屋</t>
-        </is>
-      </c>
-      <c r="H258" s="2" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-07-11 19:29（台灣時間）  共 257 筆　資料來源：樂屋網</t>
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-07-11 19:49（台灣時間）  共 255 筆　資料來源：樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H258"/>
+  <autoFilter ref="A1:H256"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23841,7 +23841,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-11 20:37（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-11 22:21（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23841,7 +23841,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-11 22:21（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-11 22:32（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -4077,15 +4077,11 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>新北市五股區成州段5地號(成洲七路32號旁)</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4093,7 +4089,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -23841,7 +23837,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-11 22:32（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-13 19:48（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23837,7 +23837,7 @@
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-13 19:48（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-14 15:31（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$506</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J506"/>
+  <dimension ref="A1:J508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22132,20 +22132,16 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr"/>
-      <c r="G467" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G467" s="2" t="inlineStr"/>
       <c r="H467" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22153,12 +22149,12 @@
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22180,18 +22176,18 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr"/>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -22228,18 +22224,18 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -22276,18 +22272,18 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -22324,12 +22320,20 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E471" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F471" s="2" t="inlineStr"/>
-      <c r="G471" s="2" t="inlineStr"/>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22337,7 +22341,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
@@ -22364,20 +22368,12 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E472" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr"/>
       <c r="F472" s="2" t="inlineStr"/>
-      <c r="G472" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22385,7 +22381,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
@@ -22412,16 +22408,20 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr"/>
-      <c r="G473" s="2" t="inlineStr"/>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22429,7 +22429,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -22544,7 +22544,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -22588,20 +22588,16 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr"/>
-      <c r="G477" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G477" s="2" t="inlineStr"/>
       <c r="H477" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22609,7 +22605,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
@@ -22636,16 +22632,20 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr"/>
-      <c r="G478" s="2" t="inlineStr"/>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22653,7 +22653,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -22680,7 +22680,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -22724,20 +22724,16 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22745,7 +22741,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
@@ -22772,16 +22768,20 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr"/>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -22816,20 +22816,16 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
+          <t>富總日日</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G482" s="2" t="inlineStr"/>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22837,7 +22833,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22864,14 +22860,10 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
-        </is>
-      </c>
-      <c r="E483" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr"/>
       <c r="F483" s="2" t="inlineStr"/>
       <c r="G483" s="2" t="inlineStr"/>
       <c r="H483" s="2" t="inlineStr">
@@ -22886,7 +22878,7 @@
       </c>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22908,16 +22900,20 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr"/>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22925,7 +22921,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
@@ -22952,20 +22948,16 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G485" s="2" t="inlineStr"/>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22973,7 +22965,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -23000,20 +22992,16 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr"/>
-      <c r="G486" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區後館路1巷旁</t>
-        </is>
-      </c>
+      <c r="G486" s="2" t="inlineStr"/>
       <c r="H486" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23021,7 +23009,7 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
@@ -23048,7 +23036,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -23059,7 +23047,7 @@
       <c r="F487" s="2" t="inlineStr"/>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -23096,12 +23084,20 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E488" s="2" t="inlineStr"/>
+          <t>日勝好日子</t>
+        </is>
+      </c>
+      <c r="E488" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F488" s="2" t="inlineStr"/>
-      <c r="G488" s="2" t="inlineStr"/>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區後館路1巷旁</t>
+        </is>
+      </c>
       <c r="H488" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23109,7 +23105,7 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J488" s="2" t="inlineStr">
@@ -23136,7 +23132,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
+          <t>日青悠</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -23147,7 +23143,7 @@
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
+          <t>桃園市大園區五青路63巷257號旁</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -23184,14 +23180,10 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr"/>
       <c r="F490" s="2" t="inlineStr"/>
       <c r="G490" s="2" t="inlineStr"/>
       <c r="H490" s="2" t="inlineStr">
@@ -23228,16 +23220,20 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr"/>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23245,7 +23241,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -23272,20 +23268,16 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G492" s="2" t="inlineStr"/>
       <c r="H492" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23293,7 +23285,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -23320,28 +23312,24 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號旁</t>
-        </is>
-      </c>
+      <c r="G493" s="2" t="inlineStr"/>
       <c r="H493" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23368,16 +23356,20 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr"/>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號</t>
+        </is>
+      </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23385,7 +23377,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
@@ -23412,24 +23404,28 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr"/>
-      <c r="G495" s="2" t="inlineStr"/>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr">
@@ -23456,7 +23452,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -23500,20 +23496,16 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr"/>
-      <c r="G497" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G497" s="2" t="inlineStr"/>
       <c r="H497" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23521,7 +23513,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr">
@@ -23548,7 +23540,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23592,18 +23584,18 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區環區西路597號</t>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
         </is>
       </c>
       <c r="H499" s="2" t="inlineStr">
@@ -23640,7 +23632,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -23684,12 +23676,20 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E501" s="2" t="inlineStr"/>
+          <t>薪成家II</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr"/>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
+          <t>逸偉A+</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
@@ -23768,14 +23768,10 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
-        </is>
-      </c>
-      <c r="E503" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr"/>
       <c r="F503" s="2" t="inlineStr"/>
       <c r="G503" s="2" t="inlineStr"/>
       <c r="H503" s="2" t="inlineStr">
@@ -23812,10 +23808,14 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr"/>
+          <t>鈞貴極美II</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F504" s="2" t="inlineStr"/>
       <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr">
@@ -23834,15 +23834,99 @@
         </is>
       </c>
     </row>
+    <row r="505">
+      <c r="A505" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B505" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C505" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D505" s="2" t="inlineStr">
+        <is>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F505" s="2" t="inlineStr"/>
+      <c r="G505" s="2" t="inlineStr"/>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
     <row r="506">
-      <c r="A506" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-07-14 15:31（台灣時間）　共 503 筆　資料來源：好房網、樂屋網</t>
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B506" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D506" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr"/>
+      <c r="F506" s="2" t="inlineStr"/>
+      <c r="G506" s="2" t="inlineStr"/>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-07-15 15:35（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J504"/>
+  <autoFilter ref="A1:J506"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23921,7 +23921,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-15 15:35（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-16 15:52（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23921,7 +23921,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-16 15:52（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-17 15:40（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23921,7 +23921,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-17 15:40（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-18 15:16（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23921,7 +23921,7 @@
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-18 15:16（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-19 16:01（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$506</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$507</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J508"/>
+  <dimension ref="A1:J509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7024,23 +7024,23 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>馥春錦-山紫</t>
+          <t>金城舞3-學世花園</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>新北市土城區延吉街211號旁</t>
+          <t>新北市土城區金城路二段181號</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -7072,12 +7072,12 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>馥春錦-水明</t>
+          <t>馥春錦-山紫</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>馥華之丘（第一期）</t>
+          <t>馥春錦-水明</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7131,7 +7131,7 @@
       <c r="F144" s="2" t="inlineStr"/>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>新北市土城區青福街、青隆街口</t>
+          <t>新北市土城區延吉街211號旁</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7163,23 +7163,23 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>樹林區</t>
+          <t>土城區</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>北大儛</t>
+          <t>馥華之丘（第一期）</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>新北市樹林區大學段二小段110地號</t>
+          <t>新北市土城區青福街、青隆街口</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>將捷朗學</t>
+          <t>北大儛</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -7227,7 +7227,7 @@
       <c r="F146" s="2" t="inlineStr"/>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>新北市樹林區學勤路333號旁</t>
+          <t>新北市樹林區大學段二小段110地號</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7264,18 +7264,18 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>欣好蒔光</t>
+          <t>將捷朗學</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>新北市樹林區柑園街一段170號對面</t>
+          <t>新北市樹林區學勤路333號旁</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7312,18 +7312,18 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>欣懋川玥</t>
+          <t>欣好蒔光</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>新北市樹林區西圳街二段12號旁</t>
+          <t>新北市樹林區柑園街一段170號對面</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7360,18 +7360,18 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>騰翔樹与苑</t>
+          <t>欣懋川玥</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>新北市樹林區民權街</t>
+          <t>新北市樹林區西圳街二段12號旁</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -7403,23 +7403,23 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>鶯歌區</t>
+          <t>樹林區</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>上林旭</t>
+          <t>騰翔 樹与苑</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區中山路138巷</t>
+          <t>新北市樹林區民權街68號旁</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7456,16 +7456,20 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>京懋明日和</t>
+          <t>上林旭</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區中山路138巷</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7473,7 +7477,7 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
@@ -7500,20 +7504,16 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>京澄為德</t>
+          <t>京懋明日和</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鳳七路與龍三路口</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -7548,23 +7548,23 @@
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>台北捷寶</t>
+          <t>京澄為德</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區鶯桃路93號</t>
+          <t>新北市鶯歌區鳳七路與龍三路口</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr">
@@ -7596,23 +7596,23 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>合嘉菁緻</t>
+          <t>台北捷寶</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區國中街與高職東街交叉口</t>
+          <t>新北市鶯歌區鶯桃路93號</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
@@ -7644,16 +7644,20 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>合康世紀滙</t>
+          <t>合嘉菁緻</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區國中街與高職東街交叉口</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7661,7 +7665,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -7688,20 +7692,16 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>國家新美院</t>
+          <t>合康世紀滙</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區國慶段1321地號</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>國家藝術館</t>
+          <t>國家新美院</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -7747,7 +7747,7 @@
       <c r="F157" s="2" t="inlineStr"/>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區光明街與育英街口</t>
+          <t>新北市鶯歌區國慶段1321地號</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>國華綻</t>
+          <t>國家藝術館</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -7795,7 +7795,7 @@
       <c r="F158" s="2" t="inlineStr"/>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區鶯桃路182巷96弄</t>
+          <t>新北市鶯歌區光明街與育英街口</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -7832,18 +7832,18 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>宏苑THE ONE</t>
+          <t>國華綻</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區龍七路與鳳七路附近</t>
+          <t>新北市鶯歌區鶯桃路182巷96弄</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>富霖富鄰</t>
+          <t>宏苑THE ONE</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       <c r="F160" s="2" t="inlineStr"/>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區永吉段 570 地號</t>
+          <t>新北市鶯歌區龍七路與鳳七路附近</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>巨東・藏</t>
+          <t>富霖富鄰</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -7939,7 +7939,7 @@
       <c r="F161" s="2" t="inlineStr"/>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區國光街62號旁</t>
+          <t>新北市鶯歌區永吉段 570 地號</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -7976,16 +7976,20 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>景自慢</t>
+          <t>巨東・藏</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區國光街62號旁</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7993,7 +7997,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8020,20 +8024,16 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>渼麗綻</t>
+          <t>景自慢</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鶯桃路413巷</t>
-        </is>
-      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>金和昌仰沐</t>
+          <t>渼麗綻</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       <c r="F164" s="2" t="inlineStr"/>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區鶯歌路285旁</t>
+          <t>新北市鶯歌區鶯桃路413巷</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8116,12 +8116,20 @@
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>馥春居</t>
-        </is>
-      </c>
-      <c r="E165" s="2" t="inlineStr"/>
+          <t>金和昌仰沐</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鶯歌路285旁</t>
+        </is>
+      </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8129,7 +8137,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -8156,23 +8164,23 @@
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>鳴日之城-日安</t>
+          <t>馥春居</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr"/>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區鶯桃路二段與鳳吉一街交叉口</t>
+          <t>新北市鶯歌區永和街56巷13號</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
@@ -8204,7 +8212,7 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>鳴日之城-日禾</t>
+          <t>鳴日之城-日安</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -8215,7 +8223,7 @@
       <c r="F167" s="2" t="inlineStr"/>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>新北市鶯歌區鶯桃路二段與鳳吉一街路口</t>
+          <t>新北市鶯歌區鶯桃路二段與鳳吉一街交叉口</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8242,22 +8250,30 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>新店深坑線</t>
+          <t>土城樹林線</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>新店區</t>
+          <t>鶯歌區</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>【欣聯鉅星科技總部】企業旗艦廠辦</t>
-        </is>
-      </c>
-      <c r="E168" s="2" t="inlineStr"/>
+          <t>鳴日之城-日禾</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鶯桃路二段與鳳吉一街路口</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8265,7 +8281,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8292,20 +8308,12 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>中央一邸</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>【欣聯鉅星科技總部】企業旗艦廠辦</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr"/>
       <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>新北市新店區中央一街41號</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8313,7 +8321,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8340,7 +8348,7 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>協富青睞</t>
+          <t>中央一邸</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -8351,7 +8359,7 @@
       <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區福園段345地號等4筆</t>
+          <t>新北市新店區中央一街41號</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8388,16 +8396,20 @@
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>友座紳鄰</t>
+          <t>協富青睞</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>新北市新店區福園段345地號等4筆</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8405,7 +8417,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -8432,28 +8444,24 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>合環永新</t>
+          <t>友座紳鄰</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>新北市新店區永新街20號</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8480,7 +8488,7 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>名毅吾山II-靚山</t>
+          <t>合環永新</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -8491,7 +8499,7 @@
       <c r="F173" s="2" t="inlineStr"/>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區安康路二段127號旁</t>
+          <t>新北市新店區永新街20號</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -8528,7 +8536,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>國揚光河</t>
+          <t>名毅吾山II-靚山</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -8539,12 +8547,12 @@
       <c r="F174" s="2" t="inlineStr"/>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區寶橋路235巷167號旁</t>
+          <t>新北市新店區安康路二段127號旁</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
@@ -8576,7 +8584,7 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>寶安JR</t>
+          <t>國揚光河</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -8587,12 +8595,12 @@
       <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區寶安街58巷</t>
+          <t>新北市新店區寶橋路235巷167號旁</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
@@ -8624,23 +8632,23 @@
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>寶鈺</t>
+          <t>寶安JR</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區十四張路、啓文路口</t>
+          <t>新北市新店區寶安街58巷</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -8672,16 +8680,20 @@
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>寶鈺</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>新北市新店區十四張路、啓文路口</t>
+        </is>
+      </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8689,7 +8701,7 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
@@ -8716,20 +8728,16 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>敦南之森</t>
+          <t>御中央Ⅱ</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>新北市新店區永安街45號</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8737,7 +8745,7 @@
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
@@ -8764,18 +8772,18 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>敦泰苑</t>
+          <t>敦南之森</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區黎明路8號</t>
+          <t>新北市新店區永安街45號</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -8812,7 +8820,7 @@
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>昇峰安曼</t>
+          <t>敦泰苑</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -8823,7 +8831,7 @@
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區安康路二段</t>
+          <t>新北市新店區黎明路8號</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -8860,7 +8868,7 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>東基M1</t>
+          <t>昇峰安曼</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -8871,7 +8879,7 @@
       <c r="F181" s="2" t="inlineStr"/>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區寶安街</t>
+          <t>新北市新店區安康路二段</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -8908,7 +8916,7 @@
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>樂菲莊園-波爾多2</t>
+          <t>東基M1</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -8919,12 +8927,12 @@
       <c r="F182" s="2" t="inlineStr"/>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區央北二路289號</t>
+          <t>新北市新店區寶安街</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -8956,18 +8964,18 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>波爾多</t>
+          <t>樂菲莊園-波爾多2</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區溪園路/央北三路口</t>
+          <t>新北市新店區央北二路289號</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9004,24 +9012,28 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>波爾多2樂菲莊園</t>
+          <t>波爾多</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>新北市新店區溪園路/央北三路口</t>
+        </is>
+      </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -9048,20 +9060,16 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>湯泉綠中海</t>
+          <t>波爾多2樂菲莊園</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>新北市新店區安祥路、祥和路口</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9069,7 +9077,7 @@
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
@@ -9096,18 +9104,18 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>知馨</t>
+          <t>湯泉綠中海</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區中央三街85號</t>
+          <t>新北市新店區安祥路、祥和路口</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9144,7 +9152,7 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>碧澄市</t>
+          <t>知馨</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -9155,7 +9163,7 @@
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區青山路311號對面</t>
+          <t>新北市新店區中央三街85號</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9187,28 +9195,28 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>深坑區</t>
+          <t>新店區</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>宏博建設紅葉街案</t>
+          <t>碧澄市</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>新北市深坑區紅葉街</t>
+          <t>新北市新店區青山路311號對面</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
@@ -9230,34 +9238,38 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>新莊林口線</t>
+          <t>新店深坑線</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>八里區</t>
+          <t>深坑區</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>勤樸天翔</t>
+          <t>宏博建設紅葉街案</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>新北市深坑區紅葉街</t>
+        </is>
+      </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
@@ -9284,7 +9296,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>勤樸天逸</t>
+          <t>勤樸天翔</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9328,20 +9340,16 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>城市君臨</t>
+          <t>勤樸天逸</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區文昌二街37號斜對面</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9349,7 +9357,7 @@
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
@@ -9376,7 +9384,7 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>大新田幸福之森</t>
+          <t>城市君臨</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -9387,7 +9395,7 @@
       <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區十三行路</t>
+          <t>新北市八里區文昌二街37號斜對面</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -9424,23 +9432,23 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>日初</t>
+          <t>大新田幸福之森</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區中山路三段、訊塘二路交叉口</t>
+          <t>新北市八里區十三行路</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -9472,7 +9480,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>百欣豐光</t>
+          <t>日初</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -9483,12 +9491,12 @@
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區中山路二段323巷27號</t>
+          <t>新北市八里區中山路三段、訊塘二路交叉口</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -9520,16 +9528,20 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>紐約心光</t>
+          <t>百欣豐光</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>新北市八里區中山路二段323巷27號</t>
+        </is>
+      </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9537,7 +9549,7 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
@@ -9564,28 +9576,24 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>蒔光．墅</t>
+          <t>紐約心光</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區賢一街與中山路一段交叉口</t>
-        </is>
-      </c>
+      <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
@@ -9612,20 +9620,28 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>豐邑港麗</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr"/>
+          <t>蒔光．墅</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>萬/戶</t>
+        </is>
+      </c>
       <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>新北市八里區賢一街與中山路一段交叉口</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -9652,20 +9668,12 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>馥桂園</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>豐邑港麗</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
       <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段117巷22~26號</t>
-        </is>
-      </c>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9673,7 +9681,7 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
@@ -9695,12 +9703,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>新莊區</t>
+          <t>八里區</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>亞昕商匯中心</t>
+          <t>馥桂園</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9711,7 +9719,7 @@
       <c r="F199" s="2" t="inlineStr"/>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區富貴路、昌仁路口</t>
+          <t>新北市八里區龍米路二段117巷22~26號</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -9748,7 +9756,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>亞昕森中央</t>
+          <t>亞昕商匯中心</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -9796,7 +9804,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>勝旺家</t>
+          <t>亞昕森中央</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9807,7 +9815,7 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區福美街172巷</t>
+          <t>新北市新莊區富貴路、昌仁路口</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9844,7 +9852,7 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>勝旺新</t>
+          <t>勝旺家</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -9855,12 +9863,12 @@
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區福德三街</t>
+          <t>新北市新莊區福美街172巷</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -9892,7 +9900,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>合勤共生宅台北保健館</t>
+          <t>勝旺新</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9903,7 +9911,7 @@
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區長青街15號</t>
+          <t>新北市新莊區福德三街</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9940,23 +9948,23 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>國家壹號廣場</t>
+          <t>合勤共生宅台北保健館</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路</t>
+          <t>新北市新莊區長青街15號</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
@@ -9988,7 +9996,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>國王大道KING PARK</t>
+          <t>國家壹號廣場</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9999,7 +10007,7 @@
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原路</t>
+          <t>新北市新莊區中央路</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10036,16 +10044,20 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>國鉅富</t>
+          <t>國王大道KING PARK</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中原路</t>
+        </is>
+      </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10053,7 +10065,7 @@
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -10080,7 +10092,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>大將美樹</t>
+          <t>國鉅富</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -10124,28 +10136,24 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>宸熙丰悦</t>
+          <t>大將美樹</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區中正路260號</t>
-        </is>
-      </c>
+      <c r="G208" s="2" t="inlineStr"/>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
@@ -10172,18 +10180,18 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>富都新玉</t>
+          <t>宸熙丰悦</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街</t>
+          <t>新北市新莊區中正路260號</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10220,7 +10228,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>富都新玉-富都區</t>
+          <t>富都新玉</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10231,12 +10239,12 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街(中港國小對面)</t>
+          <t>新北市新莊區中港一街</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
@@ -10268,7 +10276,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>富都新玉-新玉區</t>
+          <t>富都新玉-富都區</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10279,7 +10287,7 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街(中港國小對面).</t>
+          <t>新北市新莊區中港一街(中港國小對面)</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10316,18 +10324,18 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>富都馨</t>
+          <t>富都新玉-新玉區</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區昌德街上</t>
+          <t>新北市新莊區中港一街(中港國小對面).</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10364,7 +10372,7 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>寰宇一號</t>
+          <t>富都馨</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -10375,12 +10383,12 @@
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區新北大道三段、新知八路、新知十路</t>
+          <t>新北市新莊區昌德街上</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
@@ -10412,23 +10420,23 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>文華苑</t>
+          <t>寰宇一號</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原路及中華路口</t>
+          <t>新北市新莊區新北大道三段、新知八路、新知十路</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
@@ -10460,18 +10468,18 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>新月大河</t>
+          <t>文華苑</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路55號旁</t>
+          <t>新北市新莊區中原路及中華路口</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10508,23 +10516,23 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>日健居</t>
+          <t>新月大河</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路188號</t>
+          <t>新北市新莊區瓊林路55號旁</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
@@ -10556,20 +10564,28 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>日和淳</t>
-        </is>
-      </c>
-      <c r="E217" s="2" t="inlineStr"/>
+          <t>日健居</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中港路188號</t>
+        </is>
+      </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10596,20 +10612,12 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>昀集富昱</t>
-        </is>
-      </c>
-      <c r="E218" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>日和淳</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
       <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區五工二路86巷36號</t>
-        </is>
-      </c>
+      <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10617,7 +10625,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
@@ -10644,12 +10652,20 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>春城麗都</t>
-        </is>
-      </c>
-      <c r="E219" s="2" t="inlineStr"/>
+          <t>昀集富昱</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工二路86巷36號</t>
+        </is>
+      </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10657,7 +10673,7 @@
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J219" s="2" t="inlineStr">
@@ -10684,28 +10700,20 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>本格明水</t>
-        </is>
-      </c>
-      <c r="E220" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>春城麗都</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
       <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區新知一路77號</t>
-        </is>
-      </c>
+      <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
@@ -10732,23 +10740,23 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>河成心湛</t>
+          <t>本格明水</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中華路一段26巷</t>
+          <t>新北市新莊區新知一路77號</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
@@ -10780,18 +10788,18 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>玄泰蔦居</t>
+          <t>河成心湛</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原段212、213、214地號</t>
+          <t>新北市新莊區中華路一段26巷</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -10828,7 +10836,7 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>百邑富都匯</t>
+          <t>玄泰蔦居</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -10839,7 +10847,7 @@
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路、中華路口</t>
+          <t>新北市新莊區中原段212、213、214地號</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -10876,7 +10884,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>皇鼎心莊</t>
+          <t>百邑富都匯</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -10887,7 +10895,7 @@
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區民安路157號</t>
+          <t>新北市新莊區中央路、中華路口</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -10924,18 +10932,18 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設中平路案(尚未取得建照)</t>
+          <t>皇鼎心莊</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中平路、榮華路二段</t>
+          <t>新北市新莊區民安路157號</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -10972,7 +10980,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
+          <t>碧瑤建設中平路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -10983,12 +10991,12 @@
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路</t>
+          <t>新北市新莊區中平路、榮華路二段</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -11020,18 +11028,18 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>碧瑤敦灃</t>
+          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區副都心段一小段228、231、242地號</t>
+          <t>新北市新莊區瓊林路</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11068,23 +11076,23 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>禾蓮心中美</t>
+          <t>碧瑤敦灃</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路148號</t>
+          <t>新北市新莊區副都心段一小段228、231、242地號</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
@@ -11116,16 +11124,20 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>自由之丘</t>
+          <t>禾蓮心中美</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中港路148號</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11133,7 +11145,7 @@
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11160,7 +11172,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>西勝時星</t>
+          <t>自由之丘</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -11204,28 +11216,24 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>豐盛</t>
+          <t>西勝時星</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區豐盛二街、新樹路699巷</t>
-        </is>
-      </c>
+      <c r="G231" s="2" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J231" s="2" t="inlineStr">
@@ -11252,24 +11260,28 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>這一站，幸福</t>
+          <t>豐盛</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區豐盛二街、新樹路699巷</t>
+        </is>
+      </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
@@ -11296,10 +11308,14 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>邦瓏雍玥</t>
-        </is>
-      </c>
-      <c r="E233" s="2" t="inlineStr"/>
+          <t>這一站，幸福</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
@@ -11336,20 +11352,12 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>馥華之道</t>
-        </is>
-      </c>
-      <c r="E234" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>邦瓏雍玥</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr"/>
       <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區福營路、福營路270號交叉口</t>
-        </is>
-      </c>
+      <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11357,7 +11365,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -11384,23 +11392,23 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>麗寶ALL IN ONE</t>
+          <t>馥華之道</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路558號</t>
+          <t>新北市新莊區福營路、福營路270號交叉口</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
@@ -11427,23 +11435,23 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Classy Home</t>
+          <t>麗寶ALL IN ONE</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路與民族路口</t>
+          <t>新北市新莊區中央路558號</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -11480,24 +11488,28 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>中光極</t>
+          <t>Classy Home</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr"/>
-      <c r="G237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區忠孝路與民族路口</t>
+        </is>
+      </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr">
@@ -11524,20 +11536,16 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>九揚華樂</t>
+          <t>中光極</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區力行段955地號</t>
-        </is>
-      </c>
+      <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11545,7 +11553,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -11572,7 +11580,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>亞昕天匯</t>
+          <t>九揚華樂</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -11583,7 +11591,7 @@
       <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路及信義路交叉口</t>
+          <t>新北市林口區力行段955地號</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -11620,23 +11628,23 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>亞昕昕銀座</t>
+          <t>亞昕天匯</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段636號</t>
+          <t>新北市林口區文化二路及信義路交叉口</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
@@ -11668,7 +11676,7 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>亞昕森匯</t>
+          <t>亞昕昕銀座</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -11679,7 +11687,7 @@
       <c r="F241" s="2" t="inlineStr"/>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區文化三路一段636號</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -11716,23 +11724,23 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>亞昕．寓邸</t>
+          <t>亞昕森匯</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
@@ -11764,7 +11772,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>仁愛金鑽</t>
+          <t>亞昕．寓邸</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -11775,12 +11783,12 @@
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段、新生街口</t>
+          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
@@ -11812,18 +11820,18 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>優學</t>
+          <t>仁愛金鑽</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區佳林路</t>
+          <t>新北市林口區仁愛路一段、新生街口</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -11860,23 +11868,23 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>原昕吾旭</t>
+          <t>優學</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 644 、656地號</t>
+          <t>新北市林口區佳林路</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -11908,18 +11916,18 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>原森TWIN TOWERS</t>
+          <t>原昕吾旭</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路及仁愛二路口</t>
+          <t>新北市林口區麗林段 644 、656地號</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -11956,7 +11964,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>和洲艾美</t>
+          <t>原森TWIN TOWERS</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -11967,7 +11975,7 @@
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化一路二段、寶林路口</t>
+          <t>新北市林口區文化三路及仁愛二路口</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -12004,7 +12012,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>大新青慕</t>
+          <t>和洲艾美</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -12015,7 +12023,7 @@
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中華路、文化二路二段口</t>
+          <t>新北市林口區文化一路二段、寶林路口</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12052,7 +12060,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>宏樸 曉霧</t>
+          <t>大新青慕</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -12063,7 +12071,7 @@
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區八德路500巷、惠民街30巷口</t>
+          <t>新北市林口區中華路、文化二路二段口</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12100,7 +12108,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>宏樸日心說</t>
+          <t>宏樸 曉霧</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -12111,12 +12119,12 @@
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民享路與中北三街口</t>
+          <t>新北市林口區八德路500巷、惠民街30巷口</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
@@ -12148,20 +12156,28 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>家悦美</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr"/>
+          <t>宏樸日心說</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F251" s="2" t="inlineStr"/>
-      <c r="G251" s="2" t="inlineStr"/>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區民享路與中北三街口</t>
+        </is>
+      </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
@@ -12188,20 +12204,12 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>家睦中山</t>
-        </is>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家悦美</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr"/>
       <c r="F252" s="2" t="inlineStr"/>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區中山路151號旁</t>
-        </is>
-      </c>
+      <c r="G252" s="2" t="inlineStr"/>
       <c r="H252" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12209,7 +12217,7 @@
       </c>
       <c r="I252" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J252" s="2" t="inlineStr">
@@ -12236,7 +12244,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>富創得AI新創園區</t>
+          <t>家睦中山</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -12247,7 +12255,7 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區工四路20號</t>
+          <t>新北市林口區中山路151號旁</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12284,7 +12292,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>富堡晶鑄</t>
+          <t>富創得AI新創園區</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -12295,7 +12303,7 @@
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷及三民路</t>
+          <t>新北市林口區工四路20號</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12332,12 +12340,20 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>富浤一響</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr"/>
+          <t>富堡晶鑄</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F255" s="2" t="inlineStr"/>
-      <c r="G255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化三路一段39巷及三民路</t>
+        </is>
+      </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12345,7 +12361,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
@@ -12372,28 +12388,20 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>寬隱</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>富浤一響</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr"/>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區東明二街98號</t>
-        </is>
-      </c>
+      <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
@@ -12420,7 +12428,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>小.學堂</t>
+          <t>寬隱</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -12431,12 +12439,12 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段 499 地號</t>
+          <t>新北市林口區東明二街98號</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr">
@@ -12468,7 +12476,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>山侘一生</t>
+          <t>小.學堂</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -12479,7 +12487,7 @@
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區建林段645地號</t>
+          <t>新北市林口區力行段 499 地號</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12516,7 +12524,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>新潤世界都心</t>
+          <t>山侘一生</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -12527,7 +12535,7 @@
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段168號旁</t>
+          <t>新北市林口區建林段645地號</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12564,18 +12572,18 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>易捷聿白</t>
+          <t>新潤世界都心</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區惠民街30巷25號旁</t>
+          <t>新北市林口區文化三路二段168號旁</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12612,7 +12620,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>春木日輝</t>
+          <t>易捷聿白</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -12623,7 +12631,7 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民富街</t>
+          <t>新北市林口區惠民街30巷25號旁</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -12660,23 +12668,23 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>森聯摩天41</t>
+          <t>春木日輝</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段69號</t>
+          <t>新北市林口區民富街</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
@@ -12708,7 +12716,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-林境</t>
+          <t>森聯摩天41</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -12719,12 +12727,12 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 512 地號</t>
+          <t>新北市林口區文化三路一段69號</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr">
@@ -12756,16 +12764,20 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-逸境</t>
+          <t>森鉅M-林境</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr"/>
-      <c r="G264" s="2" t="inlineStr"/>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區麗林段 512 地號</t>
+        </is>
+      </c>
       <c r="H264" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12773,7 +12785,7 @@
       </c>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J264" s="2" t="inlineStr">
@@ -12800,20 +12812,16 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>源峰上境</t>
+          <t>森鉅M-逸境</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr"/>
-      <c r="G265" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區松柏路80號</t>
-        </is>
-      </c>
+      <c r="G265" s="2" t="inlineStr"/>
       <c r="H265" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12821,7 +12829,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
@@ -12848,18 +12856,18 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>潤鴻日麗</t>
+          <t>源峰上境</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區松柏路80號</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -12896,18 +12904,18 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>瑞德豐錦</t>
+          <t>潤鴻日麗</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林路309巷</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -12944,7 +12952,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>璽來登帝璽</t>
+          <t>瑞德豐錦</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -12955,7 +12963,7 @@
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區三民路、八德路口</t>
+          <t>新北市林口區竹林路309巷</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -12992,7 +13000,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>盛德誠</t>
+          <t>璽來登帝璽</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -13003,7 +13011,7 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢四街、過崙街口</t>
+          <t>新北市林口區三民路、八德路口</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13040,12 +13048,20 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>福樺中央大樓</t>
-        </is>
-      </c>
-      <c r="E270" s="2" t="inlineStr"/>
+          <t>盛德誠</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F270" s="2" t="inlineStr"/>
-      <c r="G270" s="2" t="inlineStr"/>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區南勢四街、過崙街口</t>
+        </is>
+      </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13053,7 +13069,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -13080,14 +13096,10 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴中山</t>
-        </is>
-      </c>
-      <c r="E271" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>福樺中央大樓</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr"/>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr"/>
       <c r="H271" s="2" t="inlineStr">
@@ -13124,20 +13136,16 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴莊園</t>
+          <t>福樺富貴中山</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr"/>
-      <c r="G272" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化二路一段</t>
-        </is>
-      </c>
+      <c r="G272" s="2" t="inlineStr"/>
       <c r="H272" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13145,7 +13153,7 @@
       </c>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J272" s="2" t="inlineStr">
@@ -13172,7 +13180,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>立軒天蒔</t>
+          <t>福樺富貴莊園</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -13183,7 +13191,7 @@
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
+          <t>新北市林口區文化二路一段</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13220,12 +13228,20 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>立陽頤興</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr"/>
+          <t>立軒天蒔</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F274" s="2" t="inlineStr"/>
-      <c r="G274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
+        </is>
+      </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13233,7 +13249,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -13260,20 +13276,12 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>竹城.日和</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立陽頤興</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr"/>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區建林段1261地號</t>
-        </is>
-      </c>
+      <c r="G275" s="2" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13281,7 +13289,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -13308,7 +13316,7 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>築禾琢玥</t>
+          <t>竹城.日和</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -13319,7 +13327,7 @@
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢三街</t>
+          <t>新北市林口區建林段1261地號</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13356,18 +13364,18 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>群和 FUTURE LINK</t>
+          <t>築禾琢玥</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段11地號</t>
+          <t>新北市林口區南勢三街</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13404,23 +13412,23 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>翫美A9</t>
+          <t>群和 FUTURE LINK</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷</t>
+          <t>新北市林口區力行段11地號</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
@@ -13452,23 +13460,23 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>聯虹珺玥</t>
+          <t>翫美A9</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林一路.</t>
+          <t>新北市林口區文化三路一段39巷</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
@@ -13500,18 +13508,18 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>聿翔沐風</t>
+          <t>聯虹珺玥</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路、民族路口</t>
+          <t>新北市林口區竹林一路.</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13548,18 +13556,18 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>聿翔沐風</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路604巷</t>
+          <t>新北市林口區忠孝路、民族路口</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13596,18 +13604,18 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>謙旭</t>
+          <t>聿見美璟</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段</t>
+          <t>新北市林口區忠孝路604巷</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -13644,7 +13652,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>證源富匠</t>
+          <t>謙旭</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -13655,12 +13663,12 @@
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路</t>
+          <t>新北市林口區仁愛路一段</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
@@ -13692,23 +13700,23 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>證源富承</t>
+          <t>證源富匠</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路158號對面</t>
+          <t>新北市林口區林口路</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
@@ -13740,7 +13748,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>長耀 IPARK</t>
+          <t>證源富承</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -13751,7 +13759,7 @@
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
+          <t>新北市林口區林口路158號對面</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13788,23 +13796,23 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>長耀中山路案</t>
+          <t>長耀 IPARK</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段與中山路口交叉口</t>
+          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
@@ -13836,23 +13844,23 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>長耀加</t>
+          <t>長耀中山路案</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段555巷</t>
+          <t>新北市林口區文化三路二段與中山路口交叉口</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
@@ -13884,7 +13892,7 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>長耀里</t>
+          <t>長耀加</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -13895,7 +13903,7 @@
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段137地號</t>
+          <t>新北市林口區文化三路一段555巷</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13932,18 +13940,18 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>長虹天聚</t>
+          <t>長耀里</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中山路與民權路交叉口</t>
+          <t>新北市林口區力行段137地號</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -13980,18 +13988,18 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>頤昌松玥</t>
+          <t>長虹天聚</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段211巷</t>
+          <t>新北市林口區中山路與民權路交叉口</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -14018,28 +14026,28 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>双捷橙品</t>
+          <t>頤昌松玥</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景平路723號旁</t>
+          <t>新北市林口區文化三路二段211巷</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14076,23 +14084,23 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>君奕華品</t>
+          <t>双捷橙品</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街57巷11號</t>
+          <t>新北市中和區景平路723號旁</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
@@ -14124,23 +14132,23 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>和典永峰</t>
+          <t>君奕華品</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區立人街14巷77號</t>
+          <t>新北市中和區景新街57巷11號</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
@@ -14172,18 +14180,18 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>和御</t>
+          <t>和典永峰</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路與新生街口</t>
+          <t>新北市中和區立人街14巷77號</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14220,7 +14228,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>和雅琚</t>
+          <t>和御</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -14231,7 +14239,7 @@
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區福祥路85巷口</t>
+          <t>新北市中和區連城路與新生街口</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14268,7 +14276,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>大同新紀元</t>
+          <t>和雅琚</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -14279,7 +14287,7 @@
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路、錦和路口</t>
+          <t>新北市中和區福祥路85巷口</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14316,18 +14324,18 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>好植</t>
+          <t>大同新紀元</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街2號</t>
+          <t>新北市中和區連城路、錦和路口</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -14364,7 +14372,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>宜安三六</t>
+          <t>好植</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -14375,12 +14383,12 @@
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區保健路72號</t>
+          <t>新北市中和區景新街2號</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
@@ -14412,24 +14420,28 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
+          <t>宜安三六</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" s="2" t="inlineStr"/>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區保健路72號</t>
+        </is>
+      </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
@@ -14456,28 +14468,24 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠A基地</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區環河西路三段、永和路</t>
-        </is>
-      </c>
+      <c r="G300" s="2" t="inlineStr"/>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
@@ -14504,7 +14512,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠B基地</t>
+          <t>左岸明珠A基地</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -14520,7 +14528,7 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
@@ -14552,7 +14560,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>忻揚馥群</t>
+          <t>左岸明珠B基地</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -14563,12 +14571,12 @@
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區南山路247號</t>
+          <t>新北市中和區環河西路三段、永和路</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
@@ -14600,18 +14608,18 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>忻揚馥群</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr"/>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街112號</t>
+          <t>新北市中和區南山路247號</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14648,20 +14656,28 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E304" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
@@ -14688,7 +14704,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr"/>
@@ -14728,7 +14744,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>欽禾</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
@@ -14768,14 +14784,10 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr"/>
       <c r="F307" s="2" t="inlineStr"/>
       <c r="G307" s="2" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
@@ -14812,28 +14824,24 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G308" s="2" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
@@ -14860,7 +14868,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -14871,12 +14879,12 @@
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路309號</t>
+          <t>新北市中和區中和路410號</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
@@ -14908,16 +14916,20 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr"/>
-      <c r="G310" s="2" t="inlineStr"/>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連城路309號</t>
+        </is>
+      </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14925,7 +14937,7 @@
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
@@ -14952,28 +14964,24 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路159巷</t>
-        </is>
-      </c>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
@@ -15000,7 +15008,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -15011,12 +15019,12 @@
       <c r="F312" s="2" t="inlineStr"/>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連勝街26巷8號</t>
+          <t>新北市中和區景平路159巷</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
@@ -15048,16 +15056,20 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr"/>
-      <c r="G313" s="2" t="inlineStr"/>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連勝街26巷8號</t>
+        </is>
+      </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15065,7 +15077,7 @@
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J313" s="2" t="inlineStr">
@@ -15092,20 +15104,16 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr"/>
-      <c r="G314" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區民有街49號</t>
-        </is>
-      </c>
+      <c r="G314" s="2" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15113,7 +15121,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J314" s="2" t="inlineStr">
@@ -15135,23 +15143,23 @@
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr"/>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街22巷2號</t>
+          <t>新北市中和區民有街49號</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15188,16 +15196,20 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr"/>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松柏街22巷2號</t>
+        </is>
+      </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15205,7 +15217,7 @@
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr">
@@ -15232,20 +15244,16 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
-        </is>
-      </c>
+      <c r="G317" s="2" t="inlineStr"/>
       <c r="H317" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15253,7 +15261,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
@@ -15280,18 +15288,18 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路二段521號</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -15328,23 +15336,23 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr">
@@ -15376,18 +15384,18 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區金門街287巷</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15424,24 +15432,28 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr"/>
-      <c r="G321" s="2" t="inlineStr"/>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區存德街15號</t>
+        </is>
+      </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J321" s="2" t="inlineStr">
@@ -15468,20 +15480,16 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路</t>
-        </is>
-      </c>
+      <c r="G322" s="2" t="inlineStr"/>
       <c r="H322" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15489,7 +15497,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15516,23 +15524,23 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
+          <t>大業</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道一段</t>
+          <t>新北市板橋區華江一路</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr">
@@ -15564,7 +15572,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -15575,12 +15583,12 @@
       <c r="F324" s="2" t="inlineStr"/>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr">
@@ -15612,7 +15620,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -15623,12 +15631,12 @@
       <c r="F325" s="2" t="inlineStr"/>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
@@ -15660,23 +15668,23 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路二段183號旁</t>
+          <t>新北市板橋區文化路二段與華江一路口</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
@@ -15708,18 +15716,18 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅東路</t>
+          <t>新北市板橋區民生路二段183號旁</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -15756,7 +15764,7 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -15767,7 +15775,7 @@
       <c r="F328" s="2" t="inlineStr"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -15804,18 +15812,18 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -15852,23 +15860,23 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I330" s="2" t="inlineStr">
@@ -15900,7 +15908,7 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
@@ -15911,7 +15919,7 @@
       <c r="F331" s="2" t="inlineStr"/>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -15948,18 +15956,18 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -15996,18 +16004,18 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -16044,7 +16052,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -16055,7 +16063,7 @@
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區田單北街61號</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -16092,18 +16100,18 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區三民路二段72號</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -16140,24 +16148,28 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
-      <c r="G336" s="2" t="inlineStr"/>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區大華街72號旁</t>
+        </is>
+      </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J336" s="2" t="inlineStr">
@@ -16184,7 +16196,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -16228,28 +16240,24 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr"/>
-      <c r="G338" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
-        </is>
-      </c>
+      <c r="G338" s="2" t="inlineStr"/>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J338" s="2" t="inlineStr">
@@ -16276,18 +16284,18 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16324,7 +16332,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -16335,7 +16343,7 @@
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16372,7 +16380,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -16383,7 +16391,7 @@
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16420,23 +16428,23 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr">
@@ -16468,23 +16476,23 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林濱河帝景</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr">
@@ -16516,7 +16524,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -16527,7 +16535,7 @@
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16564,20 +16572,28 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E345" s="2" t="inlineStr"/>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F345" s="2" t="inlineStr"/>
-      <c r="G345" s="2" t="inlineStr"/>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
+        </is>
+      </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J345" s="2" t="inlineStr">
@@ -16604,28 +16620,20 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
-        </is>
-      </c>
-      <c r="E346" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr"/>
       <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
-        </is>
-      </c>
+      <c r="G346" s="2" t="inlineStr"/>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J346" s="2" t="inlineStr">
@@ -16652,7 +16660,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -16663,12 +16671,12 @@
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr">
@@ -16700,7 +16708,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -16711,7 +16719,7 @@
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路600號對面</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -16748,18 +16756,18 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16796,18 +16804,18 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16844,7 +16852,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -16855,12 +16863,12 @@
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr">
@@ -16892,23 +16900,23 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區南雅南路二段68號</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr">
@@ -16940,23 +16948,23 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr">
@@ -16988,24 +16996,28 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
-      <c r="G354" s="2" t="inlineStr"/>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段65號</t>
+        </is>
+      </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -17032,28 +17044,24 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>遠揚之森A⁺</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區信義段217地號</t>
-        </is>
-      </c>
+      <c r="G355" s="2" t="inlineStr"/>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J355" s="2" t="inlineStr">
@@ -17080,7 +17088,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -17091,12 +17099,12 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr">
@@ -17128,12 +17136,20 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E357" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F357" s="2" t="inlineStr"/>
-      <c r="G357" s="2" t="inlineStr"/>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17141,7 +17157,7 @@
       </c>
       <c r="I357" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J357" s="2" t="inlineStr">
@@ -17163,25 +17179,17 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
-        </is>
-      </c>
-      <c r="E358" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr"/>
       <c r="F358" s="2" t="inlineStr"/>
-      <c r="G358" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區環河東路一段152號</t>
-        </is>
-      </c>
+      <c r="G358" s="2" t="inlineStr"/>
       <c r="H358" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17189,7 +17197,7 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr">
@@ -17216,12 +17224,20 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E359" s="2" t="inlineStr"/>
+          <t>M PLUS</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F359" s="2" t="inlineStr"/>
-      <c r="G359" s="2" t="inlineStr"/>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區環河東路一段152號</t>
+        </is>
+      </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17229,7 +17245,7 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J359" s="2" t="inlineStr">
@@ -17256,20 +17272,12 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr"/>
       <c r="F360" s="2" t="inlineStr"/>
-      <c r="G360" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G360" s="2" t="inlineStr"/>
       <c r="H360" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17277,7 +17285,7 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
@@ -17304,23 +17312,23 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
@@ -17352,7 +17360,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -17363,12 +17371,12 @@
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -17400,7 +17408,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17411,12 +17419,12 @@
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr">
@@ -17448,20 +17456,28 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E364" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F364" s="2" t="inlineStr"/>
-      <c r="G364" s="2" t="inlineStr"/>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr">
@@ -17488,28 +17504,20 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr"/>
       <c r="F365" s="2" t="inlineStr"/>
-      <c r="G365" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G365" s="2" t="inlineStr"/>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
@@ -17536,7 +17544,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -17547,12 +17555,12 @@
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
@@ -17584,16 +17592,20 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr"/>
-      <c r="G367" s="2" t="inlineStr"/>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17601,7 +17613,7 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr">
@@ -17618,30 +17630,26 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr"/>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G368" s="2" t="inlineStr"/>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17649,7 +17657,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -17676,12 +17684,20 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E369" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" s="2" t="inlineStr"/>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17689,7 +17705,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -17716,14 +17732,10 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr"/>
       <c r="F370" s="2" t="inlineStr"/>
       <c r="G370" s="2" t="inlineStr"/>
       <c r="H370" s="2" t="inlineStr">
@@ -17760,28 +17772,24 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
-      <c r="G371" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G371" s="2" t="inlineStr"/>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr">
@@ -17808,23 +17816,23 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
@@ -17856,16 +17864,20 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr"/>
-      <c r="G373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17873,7 +17885,7 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
@@ -17900,28 +17912,24 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G374" s="2" t="inlineStr"/>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -17948,7 +17956,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -17959,12 +17967,12 @@
       <c r="F375" s="2" t="inlineStr"/>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr">
@@ -17996,7 +18004,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -18007,12 +18015,12 @@
       <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr">
@@ -18044,24 +18052,28 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
@@ -18083,12 +18095,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -18132,20 +18144,16 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr"/>
-      <c r="G379" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G379" s="2" t="inlineStr"/>
       <c r="H379" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18153,7 +18161,7 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr">
@@ -18180,18 +18188,18 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
+          <t>兆美萬海</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr"/>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區尚頂一街</t>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
@@ -18228,7 +18236,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -18239,7 +18247,7 @@
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
@@ -18276,12 +18284,20 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E382" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F382" s="2" t="inlineStr"/>
-      <c r="G382" s="2" t="inlineStr"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18289,7 +18305,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -18316,20 +18332,12 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr"/>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G383" s="2" t="inlineStr"/>
       <c r="H383" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18337,7 +18345,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18364,7 +18372,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -18375,7 +18383,7 @@
       <c r="F384" s="2" t="inlineStr"/>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
@@ -18412,7 +18420,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -18423,7 +18431,7 @@
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -18460,23 +18468,23 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr"/>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr">
@@ -18508,23 +18516,23 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
@@ -18556,7 +18564,7 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -18567,12 +18575,12 @@
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr">
@@ -18604,23 +18612,23 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr"/>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr">
@@ -18652,18 +18660,18 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr"/>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -18700,16 +18708,20 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr"/>
-      <c r="G391" s="2" t="inlineStr"/>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18717,7 +18729,7 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr">
@@ -18744,28 +18756,24 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr"/>
-      <c r="G392" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G392" s="2" t="inlineStr"/>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -18792,7 +18800,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -18803,7 +18811,7 @@
       <c r="F393" s="2" t="inlineStr"/>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -18840,23 +18848,23 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr"/>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr">
@@ -18888,18 +18896,18 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr"/>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18936,7 +18944,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -18947,7 +18955,7 @@
       <c r="F396" s="2" t="inlineStr"/>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18984,7 +18992,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -18995,7 +19003,7 @@
       <c r="F397" s="2" t="inlineStr"/>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -19032,18 +19040,18 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr"/>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -19080,16 +19088,20 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr"/>
-      <c r="G399" s="2" t="inlineStr"/>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19097,7 +19109,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr">
@@ -19124,20 +19136,16 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr"/>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G400" s="2" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19145,7 +19153,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr">
@@ -19157,33 +19165,33 @@
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr"/>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19220,16 +19228,20 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr"/>
-      <c r="G402" s="2" t="inlineStr"/>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19237,7 +19249,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
@@ -19264,7 +19276,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -19308,20 +19320,16 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr"/>
-      <c r="G404" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G404" s="2" t="inlineStr"/>
       <c r="H404" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19329,7 +19337,7 @@
       </c>
       <c r="I404" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J404" s="2" t="inlineStr">
@@ -19356,7 +19364,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -19367,7 +19375,7 @@
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
@@ -19404,18 +19412,18 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -19452,16 +19460,20 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr"/>
-      <c r="G407" s="2" t="inlineStr"/>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19469,7 +19481,7 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
@@ -19496,20 +19508,16 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
-      <c r="G408" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G408" s="2" t="inlineStr"/>
       <c r="H408" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19517,7 +19525,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -19544,18 +19552,18 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -19592,18 +19600,18 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -19640,18 +19648,18 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -19688,12 +19696,20 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E412" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F412" s="2" t="inlineStr"/>
-      <c r="G412" s="2" t="inlineStr"/>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19701,7 +19717,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
@@ -19728,20 +19744,12 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E413" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr"/>
       <c r="F413" s="2" t="inlineStr"/>
-      <c r="G413" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G413" s="2" t="inlineStr"/>
       <c r="H413" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19749,7 +19757,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr">
@@ -19776,16 +19784,20 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr"/>
-      <c r="G414" s="2" t="inlineStr"/>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19793,7 +19805,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -19820,7 +19832,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -19864,10 +19876,14 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E416" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr"/>
       <c r="H416" s="2" t="inlineStr">
@@ -19904,14 +19920,10 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E417" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr"/>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr"/>
       <c r="H417" s="2" t="inlineStr">
@@ -19948,20 +19960,16 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
-      <c r="G418" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G418" s="2" t="inlineStr"/>
       <c r="H418" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19969,7 +19977,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -19996,7 +20004,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -20007,7 +20015,7 @@
       <c r="F419" s="2" t="inlineStr"/>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -20044,12 +20052,20 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E420" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F420" s="2" t="inlineStr"/>
-      <c r="G420" s="2" t="inlineStr"/>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20057,7 +20073,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr">
@@ -20084,20 +20100,12 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E421" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr"/>
       <c r="F421" s="2" t="inlineStr"/>
-      <c r="G421" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G421" s="2" t="inlineStr"/>
       <c r="H421" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20105,7 +20113,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
@@ -20132,16 +20140,20 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr"/>
-      <c r="G422" s="2" t="inlineStr"/>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20149,7 +20161,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr">
@@ -20176,10 +20188,14 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E423" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F423" s="2" t="inlineStr"/>
       <c r="G423" s="2" t="inlineStr"/>
       <c r="H423" s="2" t="inlineStr">
@@ -20216,7 +20232,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr"/>
@@ -20256,20 +20272,12 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E425" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr"/>
       <c r="F425" s="2" t="inlineStr"/>
-      <c r="G425" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20277,7 +20285,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr">
@@ -20304,7 +20312,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -20315,7 +20323,7 @@
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -20352,12 +20360,20 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E427" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F427" s="2" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr"/>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20365,7 +20381,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr">
@@ -20392,14 +20408,10 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E428" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr"/>
       <c r="F428" s="2" t="inlineStr"/>
       <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr">
@@ -20436,7 +20448,7 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -20480,20 +20492,16 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr"/>
-      <c r="G430" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G430" s="2" t="inlineStr"/>
       <c r="H430" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20501,7 +20509,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr">
@@ -20528,12 +20536,20 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E431" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F431" s="2" t="inlineStr"/>
-      <c r="G431" s="2" t="inlineStr"/>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20541,7 +20557,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -20568,28 +20584,20 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr"/>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G432" s="2" t="inlineStr"/>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20616,20 +20624,28 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F433" s="2" t="inlineStr"/>
-      <c r="G433" s="2" t="inlineStr"/>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr">
@@ -20656,7 +20672,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
@@ -20696,20 +20712,12 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E435" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr"/>
       <c r="F435" s="2" t="inlineStr"/>
-      <c r="G435" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G435" s="2" t="inlineStr"/>
       <c r="H435" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20717,7 +20725,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr">
@@ -20744,12 +20752,20 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F436" s="2" t="inlineStr"/>
-      <c r="G436" s="2" t="inlineStr"/>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H436" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20757,7 +20773,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr">
@@ -20784,20 +20800,12 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr"/>
       <c r="F437" s="2" t="inlineStr"/>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G437" s="2" t="inlineStr"/>
       <c r="H437" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20805,7 +20813,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr">
@@ -20832,16 +20840,20 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr"/>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20849,7 +20861,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20876,20 +20888,16 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr"/>
-      <c r="G439" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G439" s="2" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20897,7 +20905,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr">
@@ -20924,16 +20932,20 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr"/>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20941,7 +20953,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -20968,7 +20980,7 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -21012,20 +21024,16 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21033,7 +21041,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21060,16 +21068,20 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr"/>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21077,7 +21089,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
@@ -21104,7 +21116,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -21148,7 +21160,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -21192,20 +21204,16 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr"/>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21213,7 +21221,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
@@ -21240,7 +21248,7 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
@@ -21251,7 +21259,7 @@
       <c r="F447" s="2" t="inlineStr"/>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -21288,16 +21296,20 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr"/>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21305,7 +21317,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21332,7 +21344,7 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
@@ -21376,7 +21388,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -21420,7 +21432,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -21464,10 +21476,14 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E452" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F452" s="2" t="inlineStr"/>
       <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
@@ -21504,14 +21520,10 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E453" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr"/>
       <c r="F453" s="2" t="inlineStr"/>
       <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr">
@@ -21548,7 +21560,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -21592,7 +21604,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -21636,7 +21648,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -21680,7 +21692,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -21724,20 +21736,16 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G458" s="2" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21745,7 +21753,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
@@ -21767,21 +21775,25 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr"/>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21789,7 +21801,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21816,20 +21828,16 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G460" s="2" t="inlineStr"/>
       <c r="H460" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21837,7 +21845,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
@@ -21864,16 +21872,20 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr"/>
-      <c r="G461" s="2" t="inlineStr"/>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H461" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21881,7 +21893,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J461" s="2" t="inlineStr">
@@ -21908,7 +21920,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -21952,7 +21964,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -21996,20 +22008,16 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr"/>
-      <c r="G464" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G464" s="2" t="inlineStr"/>
       <c r="H464" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22017,7 +22025,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
@@ -22044,16 +22052,20 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr"/>
-      <c r="G465" s="2" t="inlineStr"/>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22061,7 +22073,7 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J465" s="2" t="inlineStr">
@@ -22088,7 +22100,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -22132,7 +22144,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22154,7 +22166,7 @@
       </c>
       <c r="J467" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22176,20 +22188,16 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr"/>
-      <c r="G468" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G468" s="2" t="inlineStr"/>
       <c r="H468" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22197,12 +22205,12 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22224,18 +22232,18 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -22272,18 +22280,18 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -22320,18 +22328,18 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr"/>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -22368,12 +22376,20 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E472" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F472" s="2" t="inlineStr"/>
-      <c r="G472" s="2" t="inlineStr"/>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22381,7 +22397,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
@@ -22408,20 +22424,12 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E473" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr"/>
       <c r="F473" s="2" t="inlineStr"/>
-      <c r="G473" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G473" s="2" t="inlineStr"/>
       <c r="H473" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22429,7 +22437,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr">
@@ -22456,16 +22464,20 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr"/>
-      <c r="G474" s="2" t="inlineStr"/>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H474" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22473,7 +22485,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr">
@@ -22500,7 +22512,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -22544,7 +22556,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -22588,7 +22600,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -22632,20 +22644,16 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr"/>
-      <c r="G478" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22653,7 +22661,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -22680,16 +22688,20 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr"/>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22697,7 +22709,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">
@@ -22724,7 +22736,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -22768,20 +22780,16 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G481" s="2" t="inlineStr"/>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22789,7 +22797,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -22816,16 +22824,20 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22833,7 +22845,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22860,10 +22872,14 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E483" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F483" s="2" t="inlineStr"/>
       <c r="G483" s="2" t="inlineStr"/>
       <c r="H483" s="2" t="inlineStr">
@@ -22878,7 +22894,7 @@
       </c>
       <c r="J483" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22900,20 +22916,12 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr"/>
       <c r="F484" s="2" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G484" s="2" t="inlineStr"/>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22921,12 +22929,12 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22948,16 +22956,20 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr"/>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22965,7 +22977,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -22992,7 +23004,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -23036,20 +23048,16 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr"/>
-      <c r="G487" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G487" s="2" t="inlineStr"/>
       <c r="H487" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23057,7 +23065,7 @@
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J487" s="2" t="inlineStr">
@@ -23084,7 +23092,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -23095,7 +23103,7 @@
       <c r="F488" s="2" t="inlineStr"/>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -23132,7 +23140,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -23143,7 +23151,7 @@
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -23180,12 +23188,20 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F490" s="2" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr"/>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23193,7 +23209,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
@@ -23220,20 +23236,12 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E491" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr"/>
       <c r="F491" s="2" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G491" s="2" t="inlineStr"/>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23241,7 +23249,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -23268,16 +23276,20 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr"/>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23285,7 +23297,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -23312,7 +23324,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -23356,20 +23368,16 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G494" s="2" t="inlineStr"/>
       <c r="H494" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23377,7 +23385,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
@@ -23404,23 +23412,23 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr"/>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I495" s="2" t="inlineStr">
@@ -23452,24 +23460,28 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr"/>
-      <c r="G496" s="2" t="inlineStr"/>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr">
@@ -23496,7 +23508,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -23540,7 +23552,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23584,20 +23596,16 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G499" s="2" t="inlineStr"/>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23605,7 +23613,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -23632,16 +23640,20 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr"/>
-      <c r="G500" s="2" t="inlineStr"/>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23649,7 +23661,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
@@ -23676,20 +23688,16 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G501" s="2" t="inlineStr"/>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23697,7 +23705,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -23724,16 +23732,20 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23741,7 +23753,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23768,10 +23780,14 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E503" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F503" s="2" t="inlineStr"/>
       <c r="G503" s="2" t="inlineStr"/>
       <c r="H503" s="2" t="inlineStr">
@@ -23808,14 +23824,10 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr"/>
       <c r="F504" s="2" t="inlineStr"/>
       <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr">
@@ -23852,7 +23864,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -23896,10 +23908,14 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E506" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E506" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr"/>
       <c r="H506" s="2" t="inlineStr">
@@ -23918,15 +23934,55 @@
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-07-19 16:01（台灣時間）　共 505 筆　資料來源：好房網、樂屋網</t>
+    <row r="507">
+      <c r="A507" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B507" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C507" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D507" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr"/>
+      <c r="F507" s="2" t="inlineStr"/>
+      <c r="G507" s="2" t="inlineStr"/>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-07-20 19:28（台灣時間）　共 506 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J506"/>
+  <autoFilter ref="A1:J507"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -23977,7 +23977,7 @@
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-20 19:28（台灣時間）　共 506 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-21 17:44（台灣時間）　共 506 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$508</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J509"/>
+  <dimension ref="A1:J510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14656,33 +14656,29 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>昇陽國旭</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景新街112號</t>
-        </is>
-      </c>
+      <c r="G304" s="2" t="inlineStr"/>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14704,20 +14700,28 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E305" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F305" s="2" t="inlineStr"/>
-      <c r="G305" s="2" t="inlineStr"/>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
@@ -14744,7 +14748,7 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr"/>
@@ -14784,7 +14788,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>欽禾</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr"/>
@@ -14824,14 +14828,10 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E308" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr"/>
       <c r="F308" s="2" t="inlineStr"/>
       <c r="G308" s="2" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
@@ -14868,28 +14868,24 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr"/>
-      <c r="G309" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G309" s="2" t="inlineStr"/>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J309" s="2" t="inlineStr">
@@ -14916,7 +14912,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -14927,12 +14923,12 @@
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路309號</t>
+          <t>新北市中和區中和路410號</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
@@ -14964,16 +14960,20 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連城路309號</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14981,7 +14981,7 @@
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
@@ -15008,28 +15008,24 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路159巷</t>
-        </is>
-      </c>
+      <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr">
@@ -15056,7 +15052,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
@@ -15067,12 +15063,12 @@
       <c r="F313" s="2" t="inlineStr"/>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連勝街26巷8號</t>
+          <t>新北市中和區景平路159巷</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">
@@ -15104,16 +15100,20 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr"/>
-      <c r="G314" s="2" t="inlineStr"/>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連勝街26巷8號</t>
+        </is>
+      </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J314" s="2" t="inlineStr">
@@ -15148,20 +15148,16 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr"/>
-      <c r="G315" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區民有街49號</t>
-        </is>
-      </c>
+      <c r="G315" s="2" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15169,7 +15165,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J315" s="2" t="inlineStr">
@@ -15191,23 +15187,23 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr"/>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街22巷2號</t>
+          <t>新北市中和區民有街49號</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -15244,16 +15240,20 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr"/>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松柏街22巷2號</t>
+        </is>
+      </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15261,7 +15261,7 @@
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
@@ -15288,20 +15288,16 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
-        </is>
-      </c>
+      <c r="G318" s="2" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15309,7 +15305,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
@@ -15336,18 +15332,18 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
       <c r="G319" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路二段521號</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -15384,23 +15380,23 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr">
@@ -15432,18 +15428,18 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr"/>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區金門街287巷</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -15480,24 +15476,28 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr"/>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區存德街15號</t>
+        </is>
+      </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15524,20 +15524,16 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路</t>
-        </is>
-      </c>
+      <c r="G323" s="2" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15545,7 +15541,7 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J323" s="2" t="inlineStr">
@@ -15572,23 +15568,23 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
+          <t>大業</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr"/>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區縣民大道一段</t>
+          <t>新北市板橋區華江一路</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr">
@@ -15620,7 +15616,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -15631,12 +15627,12 @@
       <c r="F325" s="2" t="inlineStr"/>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
@@ -15668,7 +15664,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -15679,12 +15675,12 @@
       <c r="F326" s="2" t="inlineStr"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
@@ -15716,23 +15712,23 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路二段183號旁</t>
+          <t>新北市板橋區文化路二段與華江一路口</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr">
@@ -15764,18 +15760,18 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅東路</t>
+          <t>新北市板橋區民生路二段183號旁</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -15812,7 +15808,7 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
@@ -15823,7 +15819,7 @@
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -15860,18 +15856,18 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -15908,23 +15904,23 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I331" s="2" t="inlineStr">
@@ -15956,7 +15952,7 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -15967,7 +15963,7 @@
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -16004,18 +16000,18 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -16052,18 +16048,18 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -16100,7 +16096,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -16111,7 +16107,7 @@
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區田單北街61號</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -16148,18 +16144,18 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區三民路二段72號</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -16196,24 +16192,28 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr"/>
-      <c r="G337" s="2" t="inlineStr"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區大華街72號旁</t>
+        </is>
+      </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J337" s="2" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -16284,28 +16284,24 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr"/>
-      <c r="G339" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
-        </is>
-      </c>
+      <c r="G339" s="2" t="inlineStr"/>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J339" s="2" t="inlineStr">
@@ -16332,18 +16328,18 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16380,7 +16376,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -16391,7 +16387,7 @@
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16428,7 +16424,7 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -16439,7 +16435,7 @@
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -16476,23 +16472,23 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr">
@@ -16524,23 +16520,23 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林濱河帝景</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I344" s="2" t="inlineStr">
@@ -16572,7 +16568,7 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
@@ -16583,7 +16579,7 @@
       <c r="F345" s="2" t="inlineStr"/>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -16620,20 +16616,28 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E346" s="2" t="inlineStr"/>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr"/>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
+        </is>
+      </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J346" s="2" t="inlineStr">
@@ -16660,28 +16664,20 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
-        </is>
-      </c>
-      <c r="E347" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr"/>
       <c r="F347" s="2" t="inlineStr"/>
-      <c r="G347" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
-        </is>
-      </c>
+      <c r="G347" s="2" t="inlineStr"/>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J347" s="2" t="inlineStr">
@@ -16708,7 +16704,7 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -16719,12 +16715,12 @@
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr">
@@ -16756,7 +16752,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -16767,7 +16763,7 @@
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路600號對面</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16804,18 +16800,18 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16852,18 +16848,18 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -16900,7 +16896,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -16911,12 +16907,12 @@
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr">
@@ -16948,23 +16944,23 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區南雅南路二段68號</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr">
@@ -16996,23 +16992,23 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr">
@@ -17044,24 +17040,28 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" s="2" t="inlineStr"/>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段65號</t>
+        </is>
+      </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J355" s="2" t="inlineStr">
@@ -17088,28 +17088,24 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>遠揚之森A⁺</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr"/>
-      <c r="G356" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區信義段217地號</t>
-        </is>
-      </c>
+      <c r="G356" s="2" t="inlineStr"/>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr">
@@ -17136,7 +17132,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -17147,12 +17143,12 @@
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr">
@@ -17184,12 +17180,20 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E358" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F358" s="2" t="inlineStr"/>
-      <c r="G358" s="2" t="inlineStr"/>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17197,7 +17201,7 @@
       </c>
       <c r="I358" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J358" s="2" t="inlineStr">
@@ -17219,25 +17223,17 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
-        </is>
-      </c>
-      <c r="E359" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr"/>
       <c r="F359" s="2" t="inlineStr"/>
-      <c r="G359" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區環河東路一段152號</t>
-        </is>
-      </c>
+      <c r="G359" s="2" t="inlineStr"/>
       <c r="H359" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17245,7 +17241,7 @@
       </c>
       <c r="I359" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J359" s="2" t="inlineStr">
@@ -17272,12 +17268,20 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr"/>
+          <t>M PLUS</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F360" s="2" t="inlineStr"/>
-      <c r="G360" s="2" t="inlineStr"/>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區環河東路一段152號</t>
+        </is>
+      </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17285,7 +17289,7 @@
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
@@ -17312,20 +17316,12 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E361" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr"/>
-      <c r="G361" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G361" s="2" t="inlineStr"/>
       <c r="H361" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17333,7 +17329,7 @@
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
@@ -17360,23 +17356,23 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -17408,7 +17404,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17419,12 +17415,12 @@
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr">
@@ -17456,7 +17452,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -17467,12 +17463,12 @@
       <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr">
@@ -17504,20 +17500,28 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F365" s="2" t="inlineStr"/>
-      <c r="G365" s="2" t="inlineStr"/>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
@@ -17544,28 +17548,20 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E366" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr"/>
       <c r="F366" s="2" t="inlineStr"/>
-      <c r="G366" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G366" s="2" t="inlineStr"/>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
@@ -17592,7 +17588,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -17603,12 +17599,12 @@
       <c r="F367" s="2" t="inlineStr"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr">
@@ -17640,16 +17636,20 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr"/>
-      <c r="G368" s="2" t="inlineStr"/>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -17674,30 +17674,26 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G369" s="2" t="inlineStr"/>
       <c r="H369" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17705,7 +17701,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -17732,12 +17728,20 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" s="2" t="inlineStr"/>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17745,7 +17749,7 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
@@ -17772,14 +17776,10 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E371" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr"/>
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr"/>
       <c r="H371" s="2" t="inlineStr">
@@ -17816,28 +17816,24 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr"/>
-      <c r="G372" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G372" s="2" t="inlineStr"/>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr">
@@ -17864,23 +17860,23 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F373" s="2" t="inlineStr"/>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr">
@@ -17912,16 +17908,20 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -17956,28 +17956,24 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr"/>
-      <c r="G375" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G375" s="2" t="inlineStr"/>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -18004,7 +18000,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -18015,12 +18011,12 @@
       <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr">
@@ -18052,7 +18048,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -18063,12 +18059,12 @@
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
@@ -18100,24 +18096,28 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr"/>
-      <c r="G378" s="2" t="inlineStr"/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -18139,12 +18139,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -18188,20 +18188,16 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr"/>
-      <c r="G380" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G380" s="2" t="inlineStr"/>
       <c r="H380" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18209,7 +18205,7 @@
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
@@ -18236,18 +18232,18 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
+          <t>兆美萬海</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區尚頂一街</t>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
@@ -18284,7 +18280,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -18295,7 +18291,7 @@
       <c r="F382" s="2" t="inlineStr"/>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
@@ -18332,12 +18328,20 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18345,7 +18349,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18372,20 +18376,12 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E384" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr"/>
       <c r="F384" s="2" t="inlineStr"/>
-      <c r="G384" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G384" s="2" t="inlineStr"/>
       <c r="H384" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18393,7 +18389,7 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -18420,7 +18416,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -18431,7 +18427,7 @@
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -18468,7 +18464,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -18479,7 +18475,7 @@
       <c r="F386" s="2" t="inlineStr"/>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
@@ -18516,23 +18512,23 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
@@ -18564,23 +18560,23 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr">
@@ -18612,7 +18608,7 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -18623,12 +18619,12 @@
       <c r="F389" s="2" t="inlineStr"/>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr">
@@ -18660,23 +18656,23 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr"/>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr">
@@ -18708,18 +18704,18 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
@@ -18756,16 +18752,20 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr"/>
-      <c r="G392" s="2" t="inlineStr"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -18800,28 +18800,24 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr"/>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G393" s="2" t="inlineStr"/>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr">
@@ -18848,7 +18844,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -18859,7 +18855,7 @@
       <c r="F394" s="2" t="inlineStr"/>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18896,23 +18892,23 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr"/>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I395" s="2" t="inlineStr">
@@ -18944,18 +18940,18 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr"/>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18992,7 +18988,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -19003,7 +18999,7 @@
       <c r="F397" s="2" t="inlineStr"/>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -19040,7 +19036,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -19051,7 +19047,7 @@
       <c r="F398" s="2" t="inlineStr"/>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -19088,18 +19084,18 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr"/>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
@@ -19136,16 +19132,20 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr"/>
-      <c r="G400" s="2" t="inlineStr"/>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19153,7 +19153,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr">
@@ -19180,20 +19180,16 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr"/>
-      <c r="G401" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G401" s="2" t="inlineStr"/>
       <c r="H401" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19201,7 +19197,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
@@ -19213,33 +19209,33 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr"/>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -19276,16 +19272,20 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr"/>
-      <c r="G403" s="2" t="inlineStr"/>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19293,7 +19293,7 @@
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J403" s="2" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -19364,20 +19364,16 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
-      <c r="G405" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G405" s="2" t="inlineStr"/>
       <c r="H405" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19385,7 +19381,7 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J405" s="2" t="inlineStr">
@@ -19412,7 +19408,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -19423,7 +19419,7 @@
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -19460,18 +19456,18 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -19508,16 +19504,20 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
-      <c r="G408" s="2" t="inlineStr"/>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -19552,20 +19552,16 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
-      <c r="G409" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G409" s="2" t="inlineStr"/>
       <c r="H409" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19573,7 +19569,7 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr">
@@ -19600,18 +19596,18 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -19648,18 +19644,18 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -19696,18 +19692,18 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr"/>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -19744,12 +19740,20 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E413" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F413" s="2" t="inlineStr"/>
-      <c r="G413" s="2" t="inlineStr"/>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19757,7 +19761,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr">
@@ -19784,20 +19788,12 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E414" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr"/>
       <c r="F414" s="2" t="inlineStr"/>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G414" s="2" t="inlineStr"/>
       <c r="H414" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19805,7 +19801,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -19832,16 +19828,20 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr"/>
-      <c r="G415" s="2" t="inlineStr"/>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -19920,10 +19920,14 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E417" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr"/>
       <c r="H417" s="2" t="inlineStr">
@@ -19960,14 +19964,10 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E418" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr"/>
       <c r="F418" s="2" t="inlineStr"/>
       <c r="G418" s="2" t="inlineStr"/>
       <c r="H418" s="2" t="inlineStr">
@@ -20004,20 +20004,16 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G419" s="2" t="inlineStr"/>
       <c r="H419" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20025,7 +20021,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
@@ -20052,7 +20048,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -20063,7 +20059,7 @@
       <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -20100,12 +20096,20 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E421" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F421" s="2" t="inlineStr"/>
-      <c r="G421" s="2" t="inlineStr"/>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20113,7 +20117,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
@@ -20140,20 +20144,12 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E422" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr"/>
       <c r="F422" s="2" t="inlineStr"/>
-      <c r="G422" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G422" s="2" t="inlineStr"/>
       <c r="H422" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20161,7 +20157,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr">
@@ -20188,16 +20184,20 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -20232,10 +20232,14 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E424" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F424" s="2" t="inlineStr"/>
       <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
@@ -20272,7 +20276,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr"/>
@@ -20312,20 +20316,12 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E426" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr"/>
       <c r="F426" s="2" t="inlineStr"/>
-      <c r="G426" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20333,7 +20329,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr">
@@ -20360,7 +20356,7 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -20371,7 +20367,7 @@
       <c r="F427" s="2" t="inlineStr"/>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
@@ -20408,12 +20404,20 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E428" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F428" s="2" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20421,7 +20425,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
@@ -20448,14 +20452,10 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E429" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr"/>
       <c r="F429" s="2" t="inlineStr"/>
       <c r="G429" s="2" t="inlineStr"/>
       <c r="H429" s="2" t="inlineStr">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -20536,20 +20536,16 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr"/>
-      <c r="G431" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G431" s="2" t="inlineStr"/>
       <c r="H431" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20557,7 +20553,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -20584,12 +20580,20 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr"/>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20597,7 +20601,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20624,28 +20628,20 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr"/>
       <c r="F433" s="2" t="inlineStr"/>
-      <c r="G433" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G433" s="2" t="inlineStr"/>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr">
@@ -20672,20 +20668,28 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E434" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F434" s="2" t="inlineStr"/>
-      <c r="G434" s="2" t="inlineStr"/>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr">
@@ -20712,7 +20716,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
@@ -20752,20 +20756,12 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr"/>
       <c r="F436" s="2" t="inlineStr"/>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20773,7 +20769,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr">
@@ -20800,12 +20796,20 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F437" s="2" t="inlineStr"/>
-      <c r="G437" s="2" t="inlineStr"/>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20813,7 +20817,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr">
@@ -20840,20 +20844,12 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr"/>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20861,7 +20857,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20888,16 +20884,20 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr"/>
-      <c r="G439" s="2" t="inlineStr"/>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20905,7 +20905,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr">
@@ -20932,20 +20932,16 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20953,7 +20949,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -20980,16 +20976,20 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -21068,20 +21068,16 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21089,7 +21085,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
@@ -21116,16 +21112,20 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr"/>
-      <c r="G444" s="2" t="inlineStr"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21133,7 +21133,7 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -21248,20 +21248,16 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G447" s="2" t="inlineStr"/>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21269,7 +21265,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21296,7 +21292,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -21307,7 +21303,7 @@
       <c r="F448" s="2" t="inlineStr"/>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -21344,16 +21340,20 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr"/>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21361,7 +21361,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -21432,7 +21432,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
@@ -21520,10 +21520,14 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E453" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F453" s="2" t="inlineStr"/>
       <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr">
@@ -21560,14 +21564,10 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr"/>
       <c r="F454" s="2" t="inlineStr"/>
       <c r="G454" s="2" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -21692,7 +21692,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -21780,20 +21780,16 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G459" s="2" t="inlineStr"/>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21801,7 +21797,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21823,21 +21819,25 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
@@ -21872,20 +21872,16 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr"/>
-      <c r="G461" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G461" s="2" t="inlineStr"/>
       <c r="H461" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21893,7 +21889,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J461" s="2" t="inlineStr">
@@ -21920,16 +21916,20 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr"/>
-      <c r="G462" s="2" t="inlineStr"/>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21937,7 +21937,7 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -22052,20 +22052,16 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr"/>
-      <c r="G465" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G465" s="2" t="inlineStr"/>
       <c r="H465" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22073,7 +22069,7 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J465" s="2" t="inlineStr">
@@ -22100,16 +22096,20 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr"/>
-      <c r="G466" s="2" t="inlineStr"/>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22117,7 +22117,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22210,7 +22210,7 @@
       </c>
       <c r="J468" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22232,20 +22232,16 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
-      <c r="G469" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G469" s="2" t="inlineStr"/>
       <c r="H469" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22253,12 +22249,12 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22280,18 +22276,18 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -22328,18 +22324,18 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr"/>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -22376,18 +22372,18 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr"/>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -22424,12 +22420,20 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E473" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F473" s="2" t="inlineStr"/>
-      <c r="G473" s="2" t="inlineStr"/>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22437,7 +22441,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr">
@@ -22464,20 +22468,12 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E474" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr"/>
       <c r="F474" s="2" t="inlineStr"/>
-      <c r="G474" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G474" s="2" t="inlineStr"/>
       <c r="H474" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22485,7 +22481,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr">
@@ -22512,16 +22508,20 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr"/>
-      <c r="G475" s="2" t="inlineStr"/>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22529,7 +22529,7 @@
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J475" s="2" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -22688,20 +22688,16 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G479" s="2" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22709,7 +22705,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">
@@ -22736,16 +22732,20 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr"/>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22753,7 +22753,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
@@ -22780,7 +22780,7 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
@@ -22824,20 +22824,16 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G482" s="2" t="inlineStr"/>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22845,7 +22841,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22872,16 +22868,20 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr"/>
-      <c r="G483" s="2" t="inlineStr"/>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22889,7 +22889,7 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J483" s="2" t="inlineStr">
@@ -22916,10 +22916,14 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F484" s="2" t="inlineStr"/>
       <c r="G484" s="2" t="inlineStr"/>
       <c r="H484" s="2" t="inlineStr">
@@ -22934,7 +22938,7 @@
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22956,20 +22960,12 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E485" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr"/>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G485" s="2" t="inlineStr"/>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22977,12 +22973,12 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23004,16 +23000,20 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr"/>
-      <c r="G486" s="2" t="inlineStr"/>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
@@ -23048,7 +23048,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -23092,20 +23092,16 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr"/>
-      <c r="G488" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G488" s="2" t="inlineStr"/>
       <c r="H488" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23113,7 +23109,7 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J488" s="2" t="inlineStr">
@@ -23140,7 +23136,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -23151,7 +23147,7 @@
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -23188,7 +23184,7 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -23199,7 +23195,7 @@
       <c r="F490" s="2" t="inlineStr"/>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -23236,12 +23232,20 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E491" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F491" s="2" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr"/>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23249,7 +23253,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -23276,20 +23280,12 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E492" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr"/>
       <c r="F492" s="2" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G492" s="2" t="inlineStr"/>
       <c r="H492" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23297,7 +23293,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -23324,16 +23320,20 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr"/>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23341,7 +23341,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23368,7 +23368,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -23412,20 +23412,16 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr"/>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G495" s="2" t="inlineStr"/>
       <c r="H495" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23433,7 +23429,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr">
@@ -23460,23 +23456,23 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr"/>
       <c r="G496" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I496" s="2" t="inlineStr">
@@ -23508,24 +23504,28 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr"/>
-      <c r="G497" s="2" t="inlineStr"/>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr">
@@ -23552,7 +23552,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23596,7 +23596,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -23640,20 +23640,16 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr"/>
-      <c r="G500" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G500" s="2" t="inlineStr"/>
       <c r="H500" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23661,7 +23657,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
@@ -23688,16 +23684,20 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr"/>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -23732,20 +23732,16 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G502" s="2" t="inlineStr"/>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23753,7 +23749,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23780,16 +23776,20 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr"/>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23797,7 +23797,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr">
@@ -23824,10 +23824,14 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F504" s="2" t="inlineStr"/>
       <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr">
@@ -23864,14 +23868,10 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E505" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr"/>
       <c r="F505" s="2" t="inlineStr"/>
       <c r="G505" s="2" t="inlineStr"/>
       <c r="H505" s="2" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -23952,10 +23952,14 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E507" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F507" s="2" t="inlineStr"/>
       <c r="G507" s="2" t="inlineStr"/>
       <c r="H507" s="2" t="inlineStr">
@@ -23974,15 +23978,55 @@
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-07-21 17:44（台灣時間）　共 506 筆　資料來源：好房網、樂屋網</t>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D508" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr"/>
+      <c r="F508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr"/>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-07-22 17:41（台灣時間）　共 507 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J507"/>
+  <autoFilter ref="A1:J508"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24021,7 +24021,7 @@
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-22 17:41（台灣時間）　共 507 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-23 17:35（台灣時間）　共 507 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24065,7 +24065,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-24 17:17（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-25 15:39（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24065,7 +24065,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-25 15:39（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-26 17:06（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -5869,15 +5869,11 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>新北市土城區明德段360地號</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -5885,7 +5881,7 @@
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -24065,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-26 17:06（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-27 20:47（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24061,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-27 20:47（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-28 18:16（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24061,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-28 18:16（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-29 18:20（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24061,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-29 18:20（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-30 17:48（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24061,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-30 17:48（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-07-31 18:16（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24061,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-07-31 18:16（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-01 16:46（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24061,7 +24061,7 @@
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-01 16:46（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-02 17:02（台灣時間）　共 508 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24201,7 +24201,7 @@
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-03 20:47（台灣時間）　共 511 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-04 18:22（台灣時間）　共 511 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$517</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J514"/>
+  <dimension ref="A1:J519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9520,20 +9520,16 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>城市君臨</t>
+          <t>四季Lavie</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區文昌二街37號斜對面</t>
-        </is>
-      </c>
+      <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9541,12 +9537,12 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9564,7 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>大新田幸福之森</t>
+          <t>城市君臨</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -9579,7 +9575,7 @@
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區十三行路</t>
+          <t>新北市八里區文昌二街37號斜對面</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -9616,23 +9612,23 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>日初</t>
+          <t>大新田幸福之森</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區中山路三段、訊塘二路交叉口</t>
+          <t>新北市八里區十三行路</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -9664,7 +9660,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>百欣豐光</t>
+          <t>日初</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9675,12 +9671,12 @@
       <c r="F198" s="2" t="inlineStr"/>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區中山路二段323巷27號</t>
+          <t>新北市八里區中山路三段、訊塘二路交叉口</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -9712,16 +9708,20 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>紐約心光</t>
+          <t>百欣豐光</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>新北市八里區中山路二段323巷27號</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
@@ -9756,28 +9756,24 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>蒔光．墅</t>
+          <t>紐約心光</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區賢一街與中山路一段交叉口</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
@@ -9804,20 +9800,28 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>豐邑港麗</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr"/>
+          <t>蒔光．墅</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>萬/戶</t>
+        </is>
+      </c>
       <c r="F201" s="2" t="inlineStr"/>
-      <c r="G201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>新北市八里區賢一街與中山路一段交叉口</t>
+        </is>
+      </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -9844,20 +9848,12 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>馥桂園</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>豐邑港麗</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
       <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段117巷22~26號</t>
-        </is>
-      </c>
+      <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9865,7 +9861,7 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
@@ -9887,12 +9883,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>新莊區</t>
+          <t>八里區</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>亞昕商匯中心</t>
+          <t>馥桂園</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9903,7 +9899,7 @@
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區富貴路、昌仁路口</t>
+          <t>新北市八里區龍米路二段117巷22~26號</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -9940,7 +9936,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>亞昕森中央</t>
+          <t>亞昕商匯中心</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -9988,7 +9984,7 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>勝旺家</t>
+          <t>亞昕森中央</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -9999,7 +9995,7 @@
       <c r="F205" s="2" t="inlineStr"/>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區福美街172巷</t>
+          <t>新北市新莊區富貴路、昌仁路口</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10036,7 +10032,7 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>勝旺新</t>
+          <t>勝旺家</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -10047,12 +10043,12 @@
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區福德三街</t>
+          <t>新北市新莊區福美街172巷</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
@@ -10084,7 +10080,7 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>合勤共生宅台北保健館</t>
+          <t>勝旺新</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -10095,7 +10091,7 @@
       <c r="F207" s="2" t="inlineStr"/>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區長青街15號</t>
+          <t>新北市新莊區福德三街</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -10132,23 +10128,23 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>國家壹號廣場</t>
+          <t>合勤共生宅台北保健館</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路</t>
+          <t>新北市新莊區長青街15號</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
@@ -10180,7 +10176,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>國王大道KING PARK</t>
+          <t>國家壹號廣場</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10191,7 +10187,7 @@
       <c r="F209" s="2" t="inlineStr"/>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原路</t>
+          <t>新北市新莊區中央路</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -10228,16 +10224,20 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>國鉅富</t>
+          <t>國王大道KING PARK</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中原路</t>
+        </is>
+      </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>大將美樹</t>
+          <t>國鉅富</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10316,28 +10316,24 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>宸熙丰悦</t>
+          <t>大將美樹</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區中正路260號</t>
-        </is>
-      </c>
+      <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
@@ -10364,18 +10360,18 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>富都新玉</t>
+          <t>宸熙丰悦</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街</t>
+          <t>新北市新莊區中正路260號</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10412,7 +10408,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>富都新玉-富都區</t>
+          <t>富都新玉</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -10423,12 +10419,12 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街(中港國小對面)</t>
+          <t>新北市新莊區中港一街</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
@@ -10460,7 +10456,7 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>富都新玉-新玉區</t>
+          <t>富都新玉-富都區</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -10471,7 +10467,7 @@
       <c r="F215" s="2" t="inlineStr"/>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街(中港國小對面).</t>
+          <t>新北市新莊區中港一街(中港國小對面)</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10508,18 +10504,18 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>富都馨</t>
+          <t>富都新玉-新玉區</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F216" s="2" t="inlineStr"/>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區昌德街上</t>
+          <t>新北市新莊區中港一街(中港國小對面).</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10556,7 +10552,7 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>寰宇一號</t>
+          <t>富都馨</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -10567,12 +10563,12 @@
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區新北大道三段、新知八路、新知十路</t>
+          <t>新北市新莊區昌德街上</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
@@ -10604,23 +10600,23 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>文華苑</t>
+          <t>寰宇一號</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原路及中華路口</t>
+          <t>新北市新莊區新北大道三段、新知八路、新知十路</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
@@ -10652,18 +10648,18 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>新月大河</t>
+          <t>文華苑</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路55號旁</t>
+          <t>新北市新莊區中原路及中華路口</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -10700,23 +10696,23 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>日健居</t>
+          <t>新月大河</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路188號</t>
+          <t>新北市新莊區瓊林路55號旁</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
@@ -10748,20 +10744,28 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>日和淳</t>
-        </is>
-      </c>
-      <c r="E221" s="2" t="inlineStr"/>
+          <t>日健居</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F221" s="2" t="inlineStr"/>
-      <c r="G221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中港路188號</t>
+        </is>
+      </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J221" s="2" t="inlineStr">
@@ -10788,20 +10792,12 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>昀集富昱</t>
-        </is>
-      </c>
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>日和淳</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr"/>
       <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區五工二路86巷36號</t>
-        </is>
-      </c>
+      <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10809,7 +10805,7 @@
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
@@ -10836,12 +10832,20 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>春城麗都</t>
-        </is>
-      </c>
-      <c r="E223" s="2" t="inlineStr"/>
+          <t>昀集富昱</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F223" s="2" t="inlineStr"/>
-      <c r="G223" s="2" t="inlineStr"/>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工二路86巷36號</t>
+        </is>
+      </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10849,7 +10853,7 @@
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr">
@@ -10876,28 +10880,20 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>本格明水</t>
-        </is>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>春城麗都</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr"/>
       <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區新知一路77號</t>
-        </is>
-      </c>
+      <c r="G224" s="2" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -10924,23 +10920,23 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>河成心湛</t>
+          <t>本格明水</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中華路一段26巷</t>
+          <t>新北市新莊區新知一路77號</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
@@ -10972,18 +10968,18 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>玄泰蔦居</t>
+          <t>河成心湛</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原段212、213、214地號</t>
+          <t>新北市新莊區中華路一段26巷</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11020,7 +11016,7 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>百邑富都匯</t>
+          <t>玄泰蔦居</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -11031,7 +11027,7 @@
       <c r="F227" s="2" t="inlineStr"/>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路、中華路口</t>
+          <t>新北市新莊區中原段212、213、214地號</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -11068,7 +11064,7 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>皇鼎心莊</t>
+          <t>百邑富都匯</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -11079,7 +11075,7 @@
       <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區民安路157號</t>
+          <t>新北市新莊區中央路、中華路口</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11116,18 +11112,18 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設中平路案(尚未取得建照)</t>
+          <t>皇鼎心莊</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F229" s="2" t="inlineStr"/>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中平路、榮華路二段</t>
+          <t>新北市新莊區民安路157號</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11164,7 +11160,7 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
+          <t>碧瑤建設中平路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -11175,12 +11171,12 @@
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路</t>
+          <t>新北市新莊區中平路、榮華路二段</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
@@ -11212,18 +11208,18 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>碧瑤敦灃</t>
+          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區副都心段一小段228、231、242地號</t>
+          <t>新北市新莊區瓊林路</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11260,23 +11256,23 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>禾蓮心中美</t>
+          <t>碧瑤敦灃</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路148號</t>
+          <t>新北市新莊區副都心段一小段228、231、242地號</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
@@ -11308,16 +11304,20 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>自由之丘</t>
+          <t>禾蓮心中美</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr"/>
-      <c r="G233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中港路148號</t>
+        </is>
+      </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11325,7 +11325,7 @@
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>西勝時星</t>
+          <t>自由之丘</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -11396,28 +11396,24 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>豐盛</t>
+          <t>西勝時星</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr"/>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區豐盛二街、新樹路699巷</t>
-        </is>
-      </c>
+      <c r="G235" s="2" t="inlineStr"/>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J235" s="2" t="inlineStr">
@@ -11444,24 +11440,28 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>這一站，幸福</t>
+          <t>豐盛</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr"/>
-      <c r="G236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區豐盛二街、新樹路699巷</t>
+        </is>
+      </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
@@ -11488,10 +11488,14 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>邦瓏雍玥</t>
-        </is>
-      </c>
-      <c r="E237" s="2" t="inlineStr"/>
+          <t>這一站，幸福</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr"/>
       <c r="H237" s="2" t="inlineStr">
@@ -11528,20 +11532,12 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>馥華之道</t>
-        </is>
-      </c>
-      <c r="E238" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>邦瓏雍玥</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr"/>
       <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區福營路、福營路270號交叉口</t>
-        </is>
-      </c>
+      <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11549,7 +11545,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -11576,23 +11572,23 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>麗寶ALL IN ONE</t>
+          <t>馥華之道</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr"/>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路558號</t>
+          <t>新北市新莊區福營路、福營路270號交叉口</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
@@ -11619,23 +11615,23 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Classy Home</t>
+          <t>麗寶ALL IN ONE</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr"/>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路與民族路口</t>
+          <t>新北市新莊區中央路558號</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -11672,24 +11668,28 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>中光極</t>
+          <t>Classy Home</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區忠孝路與民族路口</t>
+        </is>
+      </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -11716,20 +11716,16 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>九揚華樂</t>
+          <t>中光極</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr"/>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區力行段955地號</t>
-        </is>
-      </c>
+      <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11737,7 +11733,7 @@
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -11764,7 +11760,7 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>亞昕天匯</t>
+          <t>九揚華樂</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -11775,7 +11771,7 @@
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路及信義路交叉口</t>
+          <t>新北市林口區力行段955地號</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -11812,23 +11808,23 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>亞昕昕銀座</t>
+          <t>亞昕天匯</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段636號</t>
+          <t>新北市林口區文化二路及信義路交叉口</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -11860,7 +11856,7 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>亞昕森匯</t>
+          <t>亞昕昕銀座</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -11871,7 +11867,7 @@
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區文化三路一段636號</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -11908,23 +11904,23 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>亞昕．寓邸</t>
+          <t>亞昕森匯</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -11956,7 +11952,7 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>仁愛金鑽</t>
+          <t>亞昕．寓邸</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -11967,12 +11963,12 @@
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段、新生街口</t>
+          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
@@ -12004,18 +12000,18 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>優學</t>
+          <t>仁愛金鑽</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區佳林路</t>
+          <t>新北市林口區仁愛路一段、新生街口</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12052,23 +12048,23 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>原昕吾旭</t>
+          <t>優學</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 644 、656地號</t>
+          <t>新北市林口區佳林路</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
@@ -12100,18 +12096,18 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>原森TWIN TOWERS</t>
+          <t>原昕吾旭</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路及仁愛二路口</t>
+          <t>新北市林口區麗林段 644 、656地號</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12148,20 +12144,12 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>和洲艾美</t>
-        </is>
-      </c>
-      <c r="E251" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>原森</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr"/>
       <c r="F251" s="2" t="inlineStr"/>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化一路二段、寶林路口</t>
-        </is>
-      </c>
+      <c r="G251" s="2" t="inlineStr"/>
       <c r="H251" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12169,12 +12157,12 @@
       </c>
       <c r="I251" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12184,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>大新青慕</t>
+          <t>原森TWIN TOWERS</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -12207,7 +12195,7 @@
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中華路、文化二路二段口</t>
+          <t>新北市林口區文化三路及仁愛二路口</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12244,7 +12232,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>宏樸 曉霧</t>
+          <t>和洲艾美</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -12255,7 +12243,7 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區八德路500巷、惠民街30巷口</t>
+          <t>新北市林口區文化一路二段、寶林路口</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12292,7 +12280,7 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>宏樸日心說</t>
+          <t>大新青慕</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -12303,12 +12291,12 @@
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民享路與中北三街口</t>
+          <t>新北市林口區中華路、文化二路二段口</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
@@ -12340,12 +12328,20 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>家悦美</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr"/>
+          <t>宏樸 曉霧</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F255" s="2" t="inlineStr"/>
-      <c r="G255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區八德路500巷、惠民街30巷口</t>
+        </is>
+      </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12353,7 +12349,7 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
@@ -12380,7 +12376,7 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>家睦中山</t>
+          <t>宏樸日心說</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -12391,12 +12387,12 @@
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中山路151號旁</t>
+          <t>新北市林口區民享路與中北三街口</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr">
@@ -12428,20 +12424,12 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>富創得AI新創園區</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家悦美</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr"/>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區工四路20號</t>
-        </is>
-      </c>
+      <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12449,7 +12437,7 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
@@ -12476,7 +12464,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>富堡晶鑄</t>
+          <t>家睦中山</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -12487,7 +12475,7 @@
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷及三民路</t>
+          <t>新北市林口區中山路151號旁</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12524,12 +12512,20 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>富浤一響</t>
-        </is>
-      </c>
-      <c r="E259" s="2" t="inlineStr"/>
+          <t>富創得AI新創園區</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F259" s="2" t="inlineStr"/>
-      <c r="G259" s="2" t="inlineStr"/>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區工四路20號</t>
+        </is>
+      </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12537,7 +12533,7 @@
       </c>
       <c r="I259" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J259" s="2" t="inlineStr">
@@ -12564,7 +12560,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>寬隱</t>
+          <t>富堡晶鑄</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -12575,12 +12571,12 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區東明二街98號</t>
+          <t>新北市林口區文化三路一段39巷及三民路</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
@@ -12612,20 +12608,12 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>小.學堂</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>富浤一響</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr"/>
       <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區力行段 499 地號</t>
-        </is>
-      </c>
+      <c r="G261" s="2" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12633,7 +12621,7 @@
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -12660,7 +12648,7 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>山侘一生</t>
+          <t>寬隱</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -12671,12 +12659,12 @@
       <c r="F262" s="2" t="inlineStr"/>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區建林段645地號</t>
+          <t>新北市林口區東明二街98號</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
@@ -12708,7 +12696,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>新潤世界都心</t>
+          <t>小.學堂</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -12719,7 +12707,7 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段168號旁</t>
+          <t>新北市林口區力行段 499 地號</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -12756,18 +12744,18 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>易捷聿白</t>
+          <t>山侘一生</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區惠民街30巷25號旁</t>
+          <t>新北市林口區建林段645地號</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -12804,18 +12792,18 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>春木日輝</t>
+          <t>新潤世界都心</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民富街</t>
+          <t>新北市林口區文化三路二段168號旁</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -12852,23 +12840,23 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>森聯摩天41</t>
+          <t>易捷聿白</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr"/>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段69號</t>
+          <t>新北市林口區惠民街30巷25號旁</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
@@ -12900,18 +12888,18 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-林境</t>
+          <t>春木日輝</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 512 地號</t>
+          <t>新北市林口區民富街</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -12948,24 +12936,28 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-逸境</t>
+          <t>森聯摩天41</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr"/>
-      <c r="G268" s="2" t="inlineStr"/>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化三路一段69號</t>
+        </is>
+      </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J268" s="2" t="inlineStr">
@@ -12992,18 +12984,18 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>源峰上境</t>
+          <t>森鉅M-林境</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區松柏路80號</t>
+          <t>新北市林口區麗林段 512 地號</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13040,20 +13032,16 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>潤鴻日麗</t>
+          <t>森鉅M-逸境</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr"/>
-      <c r="G270" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
-        </is>
-      </c>
+      <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13061,7 +13049,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -13088,7 +13076,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>瑞德豐錦</t>
+          <t>源峰上境</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -13099,7 +13087,7 @@
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林路309巷</t>
+          <t>新北市林口區松柏路80號</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13136,18 +13124,18 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>璽來登帝璽</t>
+          <t>潤鴻日麗</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區三民路、八德路口</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13184,7 +13172,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>盛德誠</t>
+          <t>瑞德豐錦</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -13195,7 +13183,7 @@
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢四街、過崙街口</t>
+          <t>新北市林口區竹林路309巷</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -13232,12 +13220,20 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>福樺中央大樓</t>
-        </is>
-      </c>
-      <c r="E274" s="2" t="inlineStr"/>
+          <t>璽來登帝璽</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F274" s="2" t="inlineStr"/>
-      <c r="G274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區三民路、八德路口</t>
+        </is>
+      </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13245,7 +13241,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -13272,16 +13268,20 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴中山</t>
+          <t>盛德誠</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區南勢四街、過崙街口</t>
+        </is>
+      </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13289,7 +13289,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -13316,20 +13316,12 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴莊園</t>
-        </is>
-      </c>
-      <c r="E276" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>福樺中央大樓</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr"/>
       <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化二路一段</t>
-        </is>
-      </c>
+      <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13337,7 +13329,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -13364,20 +13356,16 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>立軒天蒔</t>
+          <t>福樺富貴中山</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr"/>
-      <c r="G277" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
-        </is>
-      </c>
+      <c r="G277" s="2" t="inlineStr"/>
       <c r="H277" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13385,7 +13373,7 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
@@ -13412,12 +13400,20 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>立陽頤興</t>
-        </is>
-      </c>
-      <c r="E278" s="2" t="inlineStr"/>
+          <t>福樺富貴莊園</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F278" s="2" t="inlineStr"/>
-      <c r="G278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化二路一段</t>
+        </is>
+      </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13425,7 +13421,7 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
@@ -13452,7 +13448,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>竹城.日和</t>
+          <t>立軒天蒔</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -13463,7 +13459,7 @@
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區建林段1261地號</t>
+          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13500,20 +13496,12 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>築禾琢玥</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立陽頤興</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr"/>
       <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區南勢三街</t>
-        </is>
-      </c>
+      <c r="G280" s="2" t="inlineStr"/>
       <c r="H280" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13521,7 +13509,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -13548,18 +13536,18 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>群和 FUTURE LINK</t>
+          <t>竹城.日和</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段11地號</t>
+          <t>新北市林口區建林段1261地號</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -13596,7 +13584,7 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>翫美A9</t>
+          <t>築禾琢玥</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -13607,12 +13595,12 @@
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷</t>
+          <t>新北市林口區南勢三街</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
@@ -13644,18 +13632,18 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>聯虹珺玥</t>
+          <t>群和 FUTURE LINK</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林一路.</t>
+          <t>新北市林口區力行段11地號</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13692,7 +13680,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>聿翔沐風</t>
+          <t>翫美A9</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -13703,12 +13691,12 @@
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路、民族路口</t>
+          <t>新北市林口區文化三路一段39巷</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
@@ -13740,7 +13728,7 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>聯虹珺玥</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -13751,7 +13739,7 @@
       <c r="F285" s="2" t="inlineStr"/>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路604巷</t>
+          <t>新北市林口區竹林一路.</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -13788,18 +13776,18 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>謙旭</t>
+          <t>聿翔沐風</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段</t>
+          <t>新北市林口區忠孝路、民族路口</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13836,23 +13824,23 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>證源富匠</t>
+          <t>聿見美璟</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路</t>
+          <t>新北市林口區忠孝路604巷</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
@@ -13884,18 +13872,18 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>證源富承</t>
+          <t>謙旭</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路158號對面</t>
+          <t>新北市林口區仁愛路一段</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13932,23 +13920,23 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>長耀 IPARK</t>
+          <t>證源富匠</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
+          <t>新北市林口區林口路</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
@@ -13980,23 +13968,23 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>長耀中山路案</t>
+          <t>證源富承</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段與中山路口交叉口</t>
+          <t>新北市林口區林口路158號對面</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
@@ -14028,7 +14016,7 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>長耀加</t>
+          <t>長耀 IPARK</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -14039,7 +14027,7 @@
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段555巷</t>
+          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14076,23 +14064,23 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>長耀里</t>
+          <t>長耀中山路案</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段137地號</t>
+          <t>新北市林口區文化三路二段與中山路口交叉口</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr">
@@ -14124,18 +14112,18 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>長虹天聚</t>
+          <t>長耀加</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中山路與民權路交叉口</t>
+          <t>新北市林口區文化三路一段555巷</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14172,7 +14160,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>頤昌松玥</t>
+          <t>長耀里</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -14183,7 +14171,7 @@
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段211巷</t>
+          <t>新北市林口區力行段137地號</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -14210,26 +14198,30 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>偉鉅雙捷韻</t>
+          <t>長虹天聚</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr"/>
-      <c r="G295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區中山路與民權路交叉口</t>
+        </is>
+      </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14237,12 +14229,12 @@
       </c>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14254,28 +14246,28 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>双捷橙品</t>
+          <t>頤昌松玥</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景平路723號旁</t>
+          <t>新北市林口區文化三路二段211巷</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14312,33 +14304,29 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>君奕華品</t>
+          <t>偉鉅雙捷韻</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr"/>
-      <c r="G297" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景新街57巷11號</t>
-        </is>
-      </c>
+      <c r="G297" s="2" t="inlineStr"/>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14348,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>和典永峰</t>
+          <t>双捷橙品</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -14371,7 +14359,7 @@
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區立人街14巷77號</t>
+          <t>新北市中和區景平路723號旁</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14408,7 +14396,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>和御</t>
+          <t>君奕華品</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -14419,12 +14407,12 @@
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路與新生街口</t>
+          <t>新北市中和區景新街57巷11號</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
@@ -14456,18 +14444,18 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>和雅琚</t>
+          <t>和典永峰</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區福祥路85巷口</t>
+          <t>新北市中和區立人街14巷77號</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14504,7 +14492,7 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>大同新紀元</t>
+          <t>和御</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
@@ -14515,7 +14503,7 @@
       <c r="F301" s="2" t="inlineStr"/>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路、錦和路口</t>
+          <t>新北市中和區連城路與新生街口</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14552,18 +14540,18 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>好植</t>
+          <t>和雅琚</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街2號</t>
+          <t>新北市中和區福祥路85巷口</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14600,23 +14588,23 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>宜安三六</t>
+          <t>大同新紀元</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr"/>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區保健路72號</t>
+          <t>新北市中和區連城路、錦和路口</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
@@ -14648,16 +14636,20 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
+          <t>好植</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街2號</t>
+        </is>
+      </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14665,7 +14657,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
@@ -14692,7 +14684,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠A基地</t>
+          <t>宜安三六</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -14703,7 +14695,7 @@
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區環河西路三段、永和路</t>
+          <t>新北市中和區保健路72號</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -14740,20 +14732,16 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠B基地</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr"/>
-      <c r="G306" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區環河西路三段、永和路</t>
-        </is>
-      </c>
+      <c r="G306" s="2" t="inlineStr"/>
       <c r="H306" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14761,7 +14749,7 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
@@ -14788,7 +14776,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>忻揚馥群</t>
+          <t>左岸明珠A基地</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -14799,7 +14787,7 @@
       <c r="F307" s="2" t="inlineStr"/>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區南山路247號</t>
+          <t>新北市中和區環河西路三段、永和路</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14836,16 +14824,20 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>昇陽國旭</t>
+          <t>左岸明珠B基地</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="2" t="inlineStr"/>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區環河西路三段、永和路</t>
+        </is>
+      </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14853,12 +14845,12 @@
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14880,18 +14872,18 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>忻揚馥群</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街112號</t>
+          <t>新北市中和區南山路247號</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -14928,10 +14920,14 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E310" s="2" t="inlineStr"/>
+          <t>昇陽國旭</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr">
@@ -14946,7 +14942,7 @@
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -14968,20 +14964,28 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
@@ -15008,7 +15012,7 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr"/>
@@ -15048,14 +15052,10 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>欽禾</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr"/>
       <c r="F313" s="2" t="inlineStr"/>
       <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr">
@@ -15092,28 +15092,20 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
-        </is>
-      </c>
-      <c r="E314" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr"/>
       <c r="F314" s="2" t="inlineStr"/>
-      <c r="G314" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G314" s="2" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J314" s="2" t="inlineStr">
@@ -15140,20 +15132,16 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr"/>
-      <c r="G315" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區連城路309號</t>
-        </is>
-      </c>
+      <c r="G315" s="2" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15161,7 +15149,7 @@
       </c>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J315" s="2" t="inlineStr">
@@ -15188,24 +15176,28 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr"/>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區中和路410號</t>
+        </is>
+      </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr">
@@ -15232,7 +15224,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -15243,12 +15235,12 @@
       <c r="F317" s="2" t="inlineStr"/>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景平路159巷</t>
+          <t>新北市中和區連城路309號</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
@@ -15280,20 +15272,16 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區連勝街26巷8號</t>
-        </is>
-      </c>
+      <c r="G318" s="2" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15301,7 +15289,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
@@ -15328,24 +15316,28 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" s="2" t="inlineStr"/>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景平路159巷</t>
+        </is>
+      </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J319" s="2" t="inlineStr">
@@ -15372,18 +15364,18 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區民有街49號</t>
+          <t>新北市中和區連勝街26巷8號</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -15415,25 +15407,21 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr"/>
-      <c r="G321" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區松柏街22巷2號</t>
-        </is>
-      </c>
+      <c r="G321" s="2" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15441,7 +15429,7 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J321" s="2" t="inlineStr">
@@ -15463,21 +15451,25 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr"/>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區民有街49號</t>
+        </is>
+      </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15485,7 +15477,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15512,18 +15504,18 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
+          <t>新北市板橋區松柏街22巷2號</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -15560,20 +15552,16 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區中山路二段521號</t>
-        </is>
-      </c>
+      <c r="G324" s="2" t="inlineStr"/>
       <c r="H324" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15581,7 +15569,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J324" s="2" t="inlineStr">
@@ -15608,7 +15596,7 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
@@ -15619,12 +15607,12 @@
       <c r="F325" s="2" t="inlineStr"/>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
@@ -15656,23 +15644,23 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
@@ -15704,24 +15692,28 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
-      <c r="G327" s="2" t="inlineStr"/>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區金門街287巷</t>
+        </is>
+      </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J327" s="2" t="inlineStr">
@@ -15748,23 +15740,23 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路</t>
+          <t>新北市板橋區存德街15號</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr">
@@ -15796,28 +15788,24 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
-      <c r="G329" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區縣民大道一段</t>
-        </is>
-      </c>
+      <c r="G329" s="2" t="inlineStr"/>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J329" s="2" t="inlineStr">
@@ -15844,18 +15832,18 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>大業</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區華江一路</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -15892,33 +15880,25 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>寶格利</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr"/>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
-        </is>
-      </c>
+      <c r="G331" s="2" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -15940,18 +15920,18 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路二段183號旁</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -15988,7 +15968,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -15999,7 +15979,7 @@
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅東路</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -16036,7 +16016,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -16047,12 +16027,12 @@
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區文化路二段與華江一路口</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
@@ -16084,7 +16064,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -16095,12 +16075,12 @@
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區民生路二段183號旁</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr">
@@ -16132,7 +16112,7 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -16143,12 +16123,12 @@
       <c r="F336" s="2" t="inlineStr"/>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
@@ -16180,7 +16160,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -16191,12 +16171,12 @@
       <c r="F337" s="2" t="inlineStr"/>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr">
@@ -16228,7 +16208,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -16239,12 +16219,12 @@
       <c r="F338" s="2" t="inlineStr"/>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr">
@@ -16276,7 +16256,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -16287,7 +16267,7 @@
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16324,7 +16304,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -16335,7 +16315,7 @@
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16372,18 +16352,18 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16420,24 +16400,28 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
-      <c r="G342" s="2" t="inlineStr"/>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區田單北街61號</t>
+        </is>
+      </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr">
@@ -16464,24 +16448,28 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
-      <c r="G343" s="2" t="inlineStr"/>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區三民路二段72號</t>
+        </is>
+      </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J343" s="2" t="inlineStr">
@@ -16508,7 +16496,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -16519,7 +16507,7 @@
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
+          <t>新北市板橋區大華街72號旁</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16556,28 +16544,24 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
-        </is>
-      </c>
+      <c r="G345" s="2" t="inlineStr"/>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J345" s="2" t="inlineStr">
@@ -16604,28 +16588,24 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
-        </is>
-      </c>
+      <c r="G346" s="2" t="inlineStr"/>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J346" s="2" t="inlineStr">
@@ -16652,18 +16632,18 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -16700,23 +16680,23 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr">
@@ -16748,7 +16728,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -16759,7 +16739,7 @@
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16796,7 +16776,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -16807,7 +16787,7 @@
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16844,12 +16824,20 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E351" s="2" t="inlineStr"/>
+          <t>甲山林濱河帝景</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>萬/戶</t>
+        </is>
+      </c>
       <c r="F351" s="2" t="inlineStr"/>
-      <c r="G351" s="2" t="inlineStr"/>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+        </is>
+      </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -16857,7 +16845,7 @@
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J351" s="2" t="inlineStr">
@@ -16884,7 +16872,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -16895,7 +16883,7 @@
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -16932,7 +16920,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信天朗</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -16943,12 +16931,12 @@
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr">
@@ -16980,20 +16968,12 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr"/>
       <c r="F354" s="2" t="inlineStr"/>
-      <c r="G354" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路600號對面</t>
-        </is>
-      </c>
+      <c r="G354" s="2" t="inlineStr"/>
       <c r="H354" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17001,7 +16981,7 @@
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -17028,23 +17008,23 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr">
@@ -17076,7 +17056,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -17087,7 +17067,7 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -17124,7 +17104,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -17135,12 +17115,12 @@
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr">
@@ -17172,7 +17152,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -17183,7 +17163,7 @@
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -17220,7 +17200,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -17231,12 +17211,12 @@
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I359" s="2" t="inlineStr">
@@ -17268,24 +17248,28 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr"/>
-      <c r="G360" s="2" t="inlineStr"/>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區南雅南路二段68號</t>
+        </is>
+      </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
@@ -17312,23 +17296,23 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區信義段217地號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
@@ -17360,23 +17344,23 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區文化路二段65號</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -17408,10 +17392,14 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E363" s="2" t="inlineStr"/>
+          <t>遠揚之森A⁺</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr"/>
       <c r="H363" s="2" t="inlineStr">
@@ -17443,28 +17431,28 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區環河東路一段152號</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr">
@@ -17491,17 +17479,25 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E365" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F365" s="2" t="inlineStr"/>
-      <c r="G365" s="2" t="inlineStr"/>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17509,7 +17505,7 @@
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
@@ -17531,25 +17527,17 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E366" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr"/>
       <c r="F366" s="2" t="inlineStr"/>
-      <c r="G366" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G366" s="2" t="inlineStr"/>
       <c r="H366" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17557,7 +17545,7 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
@@ -17584,7 +17572,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>M PLUS</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -17595,12 +17583,12 @@
       <c r="F367" s="2" t="inlineStr"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區環河東路一段152號</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr">
@@ -17632,20 +17620,12 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr"/>
       <c r="F368" s="2" t="inlineStr"/>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路388號旁</t>
-        </is>
-      </c>
+      <c r="G368" s="2" t="inlineStr"/>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17653,7 +17633,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -17680,23 +17660,23 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr"/>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I369" s="2" t="inlineStr">
@@ -17728,20 +17708,28 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr"/>
+          <t>敦南宴</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" s="2" t="inlineStr"/>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區永利路216巷</t>
+        </is>
+      </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
@@ -17768,23 +17756,23 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區復興街</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
@@ -17816,23 +17804,23 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>漢寶臺大苑</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區成功路一段132號</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
@@ -17864,14 +17852,10 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
-        </is>
-      </c>
-      <c r="E373" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr"/>
       <c r="F373" s="2" t="inlineStr"/>
       <c r="G373" s="2" t="inlineStr"/>
       <c r="H373" s="2" t="inlineStr">
@@ -17898,17 +17882,17 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -17919,12 +17903,12 @@
       <c r="F374" s="2" t="inlineStr"/>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區康寧街</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr">
@@ -17946,22 +17930,30 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr"/>
+          <t>頂溪大苑</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F375" s="2" t="inlineStr"/>
-      <c r="G375" s="2" t="inlineStr"/>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17969,7 +17961,7 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -17986,17 +17978,17 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -18040,23 +18032,23 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>富都康莊</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
+          <t>新北市汐止區康寧街</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
@@ -18088,20 +18080,12 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>萬/戶</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr"/>
       <c r="F378" s="2" t="inlineStr"/>
-      <c r="G378" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段190號旁</t>
-        </is>
-      </c>
+      <c r="G378" s="2" t="inlineStr"/>
       <c r="H378" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18109,7 +18093,7 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -18136,7 +18120,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -18180,7 +18164,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -18191,7 +18175,7 @@
       <c r="F380" s="2" t="inlineStr"/>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段125巷</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
@@ -18228,18 +18212,18 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段190號旁</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
@@ -18276,28 +18260,24 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr"/>
-      <c r="G382" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區湖東街5巷50號</t>
-        </is>
-      </c>
+      <c r="G382" s="2" t="inlineStr"/>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -18324,24 +18304,28 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段125巷</t>
+        </is>
+      </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18363,21 +18347,25 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr"/>
-      <c r="G384" s="2" t="inlineStr"/>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區民族二街30巷22號</t>
+        </is>
+      </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18385,7 +18373,7 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -18407,12 +18395,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -18423,12 +18411,12 @@
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
+          <t>新北市汐止區湖東街5巷50號</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I385" s="2" t="inlineStr">
@@ -18455,25 +18443,21 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr"/>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區尚頂一街</t>
-        </is>
-      </c>
+      <c r="G386" s="2" t="inlineStr"/>
       <c r="H386" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18481,7 +18465,7 @@
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr">
@@ -18508,20 +18492,16 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
-      <c r="G387" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
-        </is>
-      </c>
+      <c r="G387" s="2" t="inlineStr"/>
       <c r="H387" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18529,7 +18509,7 @@
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr">
@@ -18556,12 +18536,20 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr"/>
+          <t>兆美萬海</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F388" s="2" t="inlineStr"/>
-      <c r="G388" s="2" t="inlineStr"/>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
+        </is>
+      </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18569,7 +18557,7 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
@@ -18596,20 +18584,12 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E389" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>光全御苑</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr"/>
       <c r="F389" s="2" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G389" s="2" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18617,12 +18597,12 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18624,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -18655,7 +18635,7 @@
       <c r="F390" s="2" t="inlineStr"/>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -18692,7 +18672,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>合康植芯</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -18703,7 +18683,7 @@
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
@@ -18740,28 +18720,20 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
-        </is>
-      </c>
-      <c r="E392" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr"/>
       <c r="F392" s="2" t="inlineStr"/>
-      <c r="G392" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區坪頂路88號</t>
-        </is>
-      </c>
+      <c r="G392" s="2" t="inlineStr"/>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -18788,7 +18760,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -18799,7 +18771,7 @@
       <c r="F393" s="2" t="inlineStr"/>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -18836,7 +18808,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -18847,12 +18819,12 @@
       <c r="F394" s="2" t="inlineStr"/>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr">
@@ -18884,18 +18856,18 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr"/>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18932,7 +18904,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -18943,12 +18915,12 @@
       <c r="F396" s="2" t="inlineStr"/>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I396" s="2" t="inlineStr">
@@ -18980,16 +18952,20 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr"/>
-      <c r="G397" s="2" t="inlineStr"/>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區新市段118地號</t>
+        </is>
+      </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18997,7 +18973,7 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr">
@@ -19024,7 +19000,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -19035,7 +19011,7 @@
       <c r="F398" s="2" t="inlineStr"/>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -19072,23 +19048,23 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr"/>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr">
@@ -19120,7 +19096,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -19131,7 +19107,7 @@
       <c r="F400" s="2" t="inlineStr"/>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -19168,20 +19144,16 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr"/>
-      <c r="G401" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
-        </is>
-      </c>
+      <c r="G401" s="2" t="inlineStr"/>
       <c r="H401" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19189,7 +19161,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
@@ -19216,7 +19188,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -19227,12 +19199,12 @@
       <c r="F402" s="2" t="inlineStr"/>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I402" s="2" t="inlineStr">
@@ -19264,7 +19236,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -19275,12 +19247,12 @@
       <c r="F403" s="2" t="inlineStr"/>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr">
@@ -19312,7 +19284,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -19323,7 +19295,7 @@
       <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
@@ -19360,16 +19332,20 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
-      <c r="G405" s="2" t="inlineStr"/>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區中正東路二段5巷35號</t>
+        </is>
+      </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19377,7 +19353,7 @@
       </c>
       <c r="I405" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J405" s="2" t="inlineStr">
@@ -19404,18 +19380,18 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -19437,22 +19413,22 @@
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -19463,7 +19439,7 @@
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -19485,31 +19461,35 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
-      <c r="G408" s="2" t="inlineStr"/>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19517,7 +19497,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -19529,22 +19509,22 @@
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -19573,22 +19553,22 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -19599,7 +19579,7 @@
       <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -19636,18 +19616,18 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -19684,20 +19664,16 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr"/>
-      <c r="G412" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區中豐路225號對面</t>
-        </is>
-      </c>
+      <c r="G412" s="2" t="inlineStr"/>
       <c r="H412" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19705,7 +19681,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
@@ -19732,7 +19708,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -19776,7 +19752,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -19787,7 +19763,7 @@
       <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -19824,18 +19800,18 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr"/>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -19872,7 +19848,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -19883,7 +19859,7 @@
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區中豐路225號對面</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -19920,20 +19896,16 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區永順一街30號旁</t>
-        </is>
-      </c>
+      <c r="G417" s="2" t="inlineStr"/>
       <c r="H417" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19941,7 +19913,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr">
@@ -19968,12 +19940,20 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E418" s="2" t="inlineStr"/>
+          <t>君臨塘詩-慕荷</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F418" s="2" t="inlineStr"/>
-      <c r="G418" s="2" t="inlineStr"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
+        </is>
+      </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19981,7 +19961,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -20008,18 +19988,18 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區水青路520號對面</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -20056,16 +20036,20 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr"/>
-      <c r="G420" s="2" t="inlineStr"/>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
+        </is>
+      </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20073,7 +20057,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr">
@@ -20100,16 +20084,20 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大亮FIKA</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
-      <c r="G421" s="2" t="inlineStr"/>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20117,7 +20105,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
@@ -20144,7 +20132,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
+          <t>大清上景</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr"/>
@@ -20184,16 +20172,20 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20201,7 +20193,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -20228,20 +20220,16 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20249,7 +20237,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20276,20 +20264,16 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>大睦I-CITY(A19)</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
-      <c r="G425" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
-        </is>
-      </c>
+      <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20297,7 +20281,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr">
@@ -20324,7 +20308,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
+          <t>大睦站前首席</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr"/>
@@ -20364,20 +20348,16 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G427" s="2" t="inlineStr"/>
       <c r="H427" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20385,7 +20365,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr">
@@ -20412,16 +20392,20 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
+        </is>
+      </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20429,7 +20413,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
@@ -20456,12 +20440,20 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E429" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F429" s="2" t="inlineStr"/>
-      <c r="G429" s="2" t="inlineStr"/>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20469,7 +20461,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr">
@@ -20496,7 +20488,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宇惠曦</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr"/>
@@ -20536,7 +20528,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
@@ -20547,7 +20539,7 @@
       <c r="F431" s="2" t="inlineStr"/>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青溪段450地號</t>
+          <t>桃園市中壢區豐興段235地號</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
@@ -20584,20 +20576,16 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>宜誠泱</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
-        </is>
-      </c>
+      <c r="G432" s="2" t="inlineStr"/>
       <c r="H432" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20605,7 +20593,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20632,7 +20620,7 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr"/>
@@ -20672,14 +20660,10 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E434" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr"/>
       <c r="F434" s="2" t="inlineStr"/>
       <c r="G434" s="2" t="inlineStr"/>
       <c r="H434" s="2" t="inlineStr">
@@ -20716,16 +20700,20 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr"/>
-      <c r="G435" s="2" t="inlineStr"/>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青溪段450地號</t>
+        </is>
+      </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20733,7 +20721,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr">
@@ -20760,7 +20748,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>廣川市</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -20771,7 +20759,7 @@
       <c r="F436" s="2" t="inlineStr"/>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青埔五街</t>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
@@ -20808,7 +20796,7 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
+          <t>弘鼎金家園</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr"/>
@@ -20848,28 +20836,24 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20896,10 +20880,14 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E439" s="2" t="inlineStr"/>
+          <t>憶聲智匯科技園區</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F439" s="2" t="inlineStr"/>
       <c r="G439" s="2" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr">
@@ -20936,12 +20924,20 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
-        </is>
-      </c>
-      <c r="E440" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F440" s="2" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr"/>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20949,7 +20945,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -20976,20 +20972,12 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E441" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr"/>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G441" s="2" t="inlineStr"/>
       <c r="H441" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20997,7 +20985,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -21024,20 +21012,28 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E442" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr"/>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21064,20 +21060,12 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>晶采學</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr"/>
       <c r="F443" s="2" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21085,7 +21073,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
@@ -21112,14 +21100,10 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
-        </is>
-      </c>
-      <c r="E444" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr"/>
       <c r="F444" s="2" t="inlineStr"/>
       <c r="G444" s="2" t="inlineStr"/>
       <c r="H444" s="2" t="inlineStr">
@@ -21156,7 +21140,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>樂MORE</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -21167,7 +21151,7 @@
       <c r="F445" s="2" t="inlineStr"/>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區月桃路615巷</t>
+          <t>桃園市中壢區民溪三路209巷25號</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -21204,14 +21188,10 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr"/>
       <c r="F446" s="2" t="inlineStr"/>
       <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
@@ -21248,16 +21228,20 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr"/>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21265,7 +21249,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21292,20 +21276,16 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G448" s="2" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21313,7 +21293,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21340,16 +21320,20 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr"/>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21357,7 +21341,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21384,7 +21368,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -21428,7 +21412,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -21472,18 +21456,18 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr"/>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區元生三街</t>
+          <t>桃園市中壢區青埔二街</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -21520,20 +21504,16 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
-        </is>
-      </c>
+      <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21541,7 +21521,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr">
@@ -21568,7 +21548,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -21590,7 +21570,7 @@
       </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21592,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -21656,7 +21636,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -21700,16 +21680,20 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr"/>
-      <c r="G457" s="2" t="inlineStr"/>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區元生三街</t>
+        </is>
+      </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21717,7 +21701,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr">
@@ -21744,12 +21728,20 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E458" s="2" t="inlineStr"/>
+          <t>聯懋杉苑</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F458" s="2" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr"/>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21757,7 +21749,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
@@ -21784,7 +21776,7 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
@@ -21828,7 +21820,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -21872,7 +21864,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -21916,7 +21908,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>藍海帝國-綠景苑</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -21960,14 +21952,10 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
-        </is>
-      </c>
-      <c r="E463" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr"/>
       <c r="F463" s="2" t="inlineStr"/>
       <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr">
@@ -22004,20 +21992,16 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr"/>
-      <c r="G464" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G464" s="2" t="inlineStr"/>
       <c r="H464" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22025,7 +22009,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
@@ -22047,12 +22031,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -22091,25 +22075,21 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr"/>
-      <c r="G466" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G466" s="2" t="inlineStr"/>
       <c r="H466" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22117,7 +22097,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr">
@@ -22139,12 +22119,12 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22183,12 +22163,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22227,21 +22207,25 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
-      <c r="G469" s="2" t="inlineStr"/>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22249,7 +22233,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
@@ -22276,20 +22260,16 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
-      <c r="G470" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22297,7 +22277,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr">
@@ -22324,16 +22304,20 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr"/>
-      <c r="G471" s="2" t="inlineStr"/>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22341,7 +22325,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
@@ -22368,7 +22352,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -22412,7 +22396,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -22434,7 +22418,7 @@
       </c>
       <c r="J473" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22456,20 +22440,16 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr"/>
-      <c r="G474" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G474" s="2" t="inlineStr"/>
       <c r="H474" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22477,7 +22457,7 @@
       </c>
       <c r="I474" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J474" s="2" t="inlineStr">
@@ -22504,18 +22484,18 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr"/>
       <c r="G475" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區青峰路二段117~129號</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
@@ -22552,20 +22532,16 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr"/>
-      <c r="G476" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
-        </is>
-      </c>
+      <c r="G476" s="2" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22573,7 +22549,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr">
@@ -22600,20 +22576,16 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr"/>
-      <c r="G477" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區內海墘段 110-84</t>
-        </is>
-      </c>
+      <c r="G477" s="2" t="inlineStr"/>
       <c r="H477" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22621,7 +22593,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
@@ -22648,10 +22620,14 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E478" s="2" t="inlineStr"/>
+          <t>力璞翔-豐禾</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F478" s="2" t="inlineStr"/>
       <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
@@ -22666,7 +22642,7 @@
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22688,7 +22664,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -22699,7 +22675,7 @@
       <c r="F479" s="2" t="inlineStr"/>
       <c r="G479" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區園七街9號對面</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
@@ -22736,16 +22712,20 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr"/>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰段273號地號</t>
+        </is>
+      </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22753,7 +22733,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
@@ -22780,16 +22760,20 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr"/>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+        </is>
+      </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22797,7 +22781,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -22824,16 +22808,20 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>垽赫海漾星墅</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22841,7 +22829,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22868,14 +22856,10 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
-        </is>
-      </c>
-      <c r="E483" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr"/>
       <c r="F483" s="2" t="inlineStr"/>
       <c r="G483" s="2" t="inlineStr"/>
       <c r="H483" s="2" t="inlineStr">
@@ -22912,7 +22896,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -22923,7 +22907,7 @@
       <c r="F484" s="2" t="inlineStr"/>
       <c r="G484" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區環區中路與科七街</t>
+          <t>桃園市大園區園七街9號對面</t>
         </is>
       </c>
       <c r="H484" s="2" t="inlineStr">
@@ -22960,7 +22944,7 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
@@ -23004,7 +22988,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -23048,20 +23032,16 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr"/>
-      <c r="G487" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G487" s="2" t="inlineStr"/>
       <c r="H487" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23069,7 +23049,7 @@
       </c>
       <c r="I487" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J487" s="2" t="inlineStr">
@@ -23096,7 +23076,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -23140,12 +23120,20 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E489" s="2" t="inlineStr"/>
+          <t>宗佳領御</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F489" s="2" t="inlineStr"/>
-      <c r="G489" s="2" t="inlineStr"/>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23153,12 +23141,12 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23180,20 +23168,16 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G490" s="2" t="inlineStr"/>
       <c r="H490" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23201,7 +23185,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
@@ -23228,7 +23212,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -23272,16 +23256,20 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr"/>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23289,7 +23277,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -23316,20 +23304,16 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>富總日日</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G493" s="2" t="inlineStr"/>
       <c r="H493" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23337,7 +23321,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23364,20 +23348,12 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr"/>
       <c r="F494" s="2" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區後館路1巷旁</t>
-        </is>
-      </c>
+      <c r="G494" s="2" t="inlineStr"/>
       <c r="H494" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23385,12 +23361,12 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23412,7 +23388,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -23423,7 +23399,7 @@
       <c r="F495" s="2" t="inlineStr"/>
       <c r="G495" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區永園路二段152號旁</t>
         </is>
       </c>
       <c r="H495" s="2" t="inlineStr">
@@ -23460,10 +23436,14 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E496" s="2" t="inlineStr"/>
+          <t>川洋青勻</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F496" s="2" t="inlineStr"/>
       <c r="G496" s="2" t="inlineStr"/>
       <c r="H496" s="2" t="inlineStr">
@@ -23500,20 +23480,16 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr"/>
-      <c r="G497" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G497" s="2" t="inlineStr"/>
       <c r="H497" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23521,7 +23497,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr">
@@ -23548,16 +23524,20 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr"/>
-      <c r="G498" s="2" t="inlineStr"/>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園學路、學六街口</t>
+        </is>
+      </c>
       <c r="H498" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23565,7 +23545,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr">
@@ -23592,16 +23572,20 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr"/>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區後館路1巷旁</t>
+        </is>
+      </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23609,7 +23593,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -23636,7 +23620,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>日青悠</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -23647,7 +23631,7 @@
       <c r="F500" s="2" t="inlineStr"/>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號</t>
+          <t>桃園市大園區五青路63巷257號旁</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
@@ -23684,28 +23668,20 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
-        </is>
-      </c>
-      <c r="E501" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr"/>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號旁</t>
-        </is>
-      </c>
+      <c r="G501" s="2" t="inlineStr"/>
       <c r="H501" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -23732,16 +23708,20 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23749,7 +23729,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23776,7 +23756,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -23820,7 +23800,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -23864,7 +23844,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -23875,7 +23855,7 @@
       <c r="F505" s="2" t="inlineStr"/>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
@@ -23912,24 +23892,28 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr"/>
-      <c r="G506" s="2" t="inlineStr"/>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
@@ -23956,20 +23940,16 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
-      <c r="G507" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G507" s="2" t="inlineStr"/>
       <c r="H507" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23977,7 +23957,7 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J507" s="2" t="inlineStr">
@@ -24004,7 +23984,7 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -24048,10 +24028,14 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E509" s="2" t="inlineStr"/>
+          <t>興禾  築美學</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F509" s="2" t="inlineStr"/>
       <c r="G509" s="2" t="inlineStr"/>
       <c r="H509" s="2" t="inlineStr">
@@ -24088,16 +24072,20 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr"/>
-      <c r="G510" s="2" t="inlineStr"/>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24105,7 +24093,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
@@ -24132,7 +24120,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -24176,37 +24164,257 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
+          <t>薪成家II</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
+      <c r="F512" s="2" t="inlineStr"/>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>好房網</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B513" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C513" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D513" s="2" t="inlineStr">
+        <is>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E513" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr"/>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B514" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D514" s="2" t="inlineStr">
+        <is>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr"/>
+      <c r="F514" s="2" t="inlineStr"/>
+      <c r="G514" s="2" t="inlineStr"/>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B515" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C515" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D515" s="2" t="inlineStr">
+        <is>
+          <t>鈞貴極美II</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F515" s="2" t="inlineStr"/>
+      <c r="G515" s="2" t="inlineStr"/>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J515" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B516" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D516" s="2" t="inlineStr">
+        <is>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E516" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F516" s="2" t="inlineStr"/>
+      <c r="G516" s="2" t="inlineStr"/>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B517" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C517" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D517" s="2" t="inlineStr">
+        <is>
           <t>龍築靜玥</t>
         </is>
       </c>
-      <c r="E512" s="2" t="inlineStr"/>
-      <c r="F512" s="2" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr"/>
-      <c r="H512" s="2" t="inlineStr">
-        <is>
-          <t>預售屋</t>
-        </is>
-      </c>
-      <c r="I512" s="2" t="inlineStr">
+      <c r="E517" s="2" t="inlineStr"/>
+      <c r="F517" s="2" t="inlineStr"/>
+      <c r="G517" s="2" t="inlineStr"/>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr">
         <is>
           <t>樂屋網</t>
         </is>
       </c>
-      <c r="J512" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-08-04 18:22（台灣時間）　共 511 筆　資料來源：好房網、樂屋網</t>
+      <c r="J517" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-08-05 18:18（台灣時間）　共 516 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J512"/>
+  <autoFilter ref="A1:J517"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$517</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$518</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J519"/>
+  <dimension ref="A1:J520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14732,14 +14732,10 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>寶亞世界公舘</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr"/>
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="2" t="inlineStr"/>
       <c r="H306" s="2" t="inlineStr">
@@ -14754,7 +14750,7 @@
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14776,28 +14772,24 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠A基地</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr"/>
-      <c r="G307" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區環河西路三段、永和路</t>
-        </is>
-      </c>
+      <c r="G307" s="2" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
@@ -14824,7 +14816,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠B基地</t>
+          <t>左岸明珠A基地</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -14840,7 +14832,7 @@
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
@@ -14872,7 +14864,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>忻揚馥群</t>
+          <t>左岸明珠B基地</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -14883,12 +14875,12 @@
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區南山路247號</t>
+          <t>新北市中和區環河西路三段、永和路</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
@@ -14920,29 +14912,33 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>昇陽國旭</t>
+          <t>忻揚馥群</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr"/>
-      <c r="G310" s="2" t="inlineStr"/>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區南山路247號</t>
+        </is>
+      </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14964,33 +14960,29 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>昇陽國旭</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景新街112號</t>
-        </is>
-      </c>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15012,20 +15004,28 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" s="2" t="inlineStr"/>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr">
@@ -15052,7 +15052,7 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr"/>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>欽禾</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
@@ -15132,14 +15132,10 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E315" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr"/>
       <c r="F315" s="2" t="inlineStr"/>
       <c r="G315" s="2" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr">
@@ -15176,28 +15172,24 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G316" s="2" t="inlineStr"/>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr">
@@ -15224,7 +15216,7 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
@@ -15235,12 +15227,12 @@
       <c r="F317" s="2" t="inlineStr"/>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路309號</t>
+          <t>新北市中和區中和路410號</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
@@ -15272,16 +15264,20 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連城路309號</t>
+        </is>
+      </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15289,7 +15285,7 @@
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
@@ -15316,28 +15312,24 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路159巷</t>
-        </is>
-      </c>
+      <c r="G319" s="2" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J319" s="2" t="inlineStr">
@@ -15364,7 +15356,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -15375,12 +15367,12 @@
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連勝街26巷8號</t>
+          <t>新北市中和區景平路159巷</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr">
@@ -15412,16 +15404,20 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr"/>
-      <c r="G321" s="2" t="inlineStr"/>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連勝街26巷8號</t>
+        </is>
+      </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15429,7 +15425,7 @@
       </c>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J321" s="2" t="inlineStr">
@@ -15456,20 +15452,16 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區民有街49號</t>
-        </is>
-      </c>
+      <c r="G322" s="2" t="inlineStr"/>
       <c r="H322" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15477,7 +15469,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15499,23 +15491,23 @@
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街22巷2號</t>
+          <t>新北市中和區民有街49號</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -15552,16 +15544,20 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="2" t="inlineStr"/>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松柏街22巷2號</t>
+        </is>
+      </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15569,7 +15565,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J324" s="2" t="inlineStr">
@@ -15596,20 +15592,16 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr"/>
-      <c r="G325" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
-        </is>
-      </c>
+      <c r="G325" s="2" t="inlineStr"/>
       <c r="H325" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15617,7 +15609,7 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr">
@@ -15644,18 +15636,18 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路二段521號</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -15692,23 +15684,23 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr">
@@ -15740,18 +15732,18 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區金門街287巷</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -15788,24 +15780,28 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
-      <c r="G329" s="2" t="inlineStr"/>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區存德街15號</t>
+        </is>
+      </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J329" s="2" t="inlineStr">
@@ -15832,20 +15828,16 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
-      <c r="G330" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路</t>
-        </is>
-      </c>
+      <c r="G330" s="2" t="inlineStr"/>
       <c r="H330" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15853,7 +15845,7 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J330" s="2" t="inlineStr">
@@ -15880,12 +15872,20 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>寶格利</t>
-        </is>
-      </c>
-      <c r="E331" s="2" t="inlineStr"/>
+          <t>大業</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr"/>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區華江一路</t>
+        </is>
+      </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15893,12 +15893,12 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -15920,33 +15920,25 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
-        </is>
-      </c>
-      <c r="E332" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>寶格利</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr"/>
       <c r="F332" s="2" t="inlineStr"/>
-      <c r="G332" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區縣民大道一段</t>
-        </is>
-      </c>
+      <c r="G332" s="2" t="inlineStr"/>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -15968,7 +15960,7 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
@@ -15979,12 +15971,12 @@
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr">
@@ -16016,7 +16008,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -16027,12 +16019,12 @@
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
@@ -16064,18 +16056,18 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路二段183號旁</t>
+          <t>新北市板橋區文化路二段與華江一路口</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -16112,23 +16104,23 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅東路</t>
+          <t>新北市板橋區民生路二段183號旁</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
@@ -16160,7 +16152,7 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -16171,7 +16163,7 @@
       <c r="F337" s="2" t="inlineStr"/>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
@@ -16208,18 +16200,18 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr"/>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -16256,23 +16248,23 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr">
@@ -16304,7 +16296,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -16315,7 +16307,7 @@
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -16352,18 +16344,18 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16400,18 +16392,18 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -16448,7 +16440,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -16459,7 +16451,7 @@
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區田單北街61號</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -16496,18 +16488,18 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區三民路二段72號</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16544,24 +16536,28 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
-      <c r="G345" s="2" t="inlineStr"/>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區大華街72號旁</t>
+        </is>
+      </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J345" s="2" t="inlineStr">
@@ -16588,7 +16584,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -16632,28 +16628,24 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr"/>
-      <c r="G347" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
-        </is>
-      </c>
+      <c r="G347" s="2" t="inlineStr"/>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J347" s="2" t="inlineStr">
@@ -16680,18 +16672,18 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -16728,7 +16720,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -16739,7 +16731,7 @@
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16776,7 +16768,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -16787,7 +16779,7 @@
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16824,23 +16816,23 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr">
@@ -16872,23 +16864,23 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林濱河帝景</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr">
@@ -16920,7 +16912,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -16931,7 +16923,7 @@
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
@@ -16968,20 +16960,28 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E354" s="2" t="inlineStr"/>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F354" s="2" t="inlineStr"/>
-      <c r="G354" s="2" t="inlineStr"/>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
+        </is>
+      </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -17008,28 +17008,20 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr"/>
       <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
-        </is>
-      </c>
+      <c r="G355" s="2" t="inlineStr"/>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J355" s="2" t="inlineStr">
@@ -17056,7 +17048,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -17067,12 +17059,12 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr">
@@ -17104,7 +17096,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -17115,7 +17107,7 @@
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路600號對面</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -17152,18 +17144,18 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -17200,18 +17192,18 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -17248,7 +17240,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -17259,12 +17251,12 @@
       <c r="F360" s="2" t="inlineStr"/>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr">
@@ -17296,23 +17288,23 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F361" s="2" t="inlineStr"/>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區南雅南路二段68號</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
@@ -17344,23 +17336,23 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -17392,24 +17384,28 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr"/>
-      <c r="G363" s="2" t="inlineStr"/>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段65號</t>
+        </is>
+      </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J363" s="2" t="inlineStr">
@@ -17436,28 +17432,24 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>遠揚之森A⁺</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
-      <c r="G364" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區信義段217地號</t>
-        </is>
-      </c>
+      <c r="G364" s="2" t="inlineStr"/>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr">
@@ -17484,7 +17476,7 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -17495,12 +17487,12 @@
       <c r="F365" s="2" t="inlineStr"/>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr">
@@ -17532,12 +17524,20 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E366" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F366" s="2" t="inlineStr"/>
-      <c r="G366" s="2" t="inlineStr"/>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="I366" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J366" s="2" t="inlineStr">
@@ -17567,25 +17567,17 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
-        </is>
-      </c>
-      <c r="E367" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr"/>
       <c r="F367" s="2" t="inlineStr"/>
-      <c r="G367" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區環河東路一段152號</t>
-        </is>
-      </c>
+      <c r="G367" s="2" t="inlineStr"/>
       <c r="H367" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17593,7 +17585,7 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr">
@@ -17620,12 +17612,20 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr"/>
+          <t>M PLUS</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F368" s="2" t="inlineStr"/>
-      <c r="G368" s="2" t="inlineStr"/>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區環河東路一段152號</t>
+        </is>
+      </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -17660,20 +17660,12 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E369" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr"/>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G369" s="2" t="inlineStr"/>
       <c r="H369" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17681,7 +17673,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -17708,23 +17700,23 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr"/>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
@@ -17756,7 +17748,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -17767,12 +17759,12 @@
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
@@ -17804,7 +17796,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -17815,12 +17807,12 @@
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
@@ -17852,20 +17844,28 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E373" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F373" s="2" t="inlineStr"/>
-      <c r="G373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
@@ -17892,28 +17892,20 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr"/>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G374" s="2" t="inlineStr"/>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -17940,7 +17932,7 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -17951,12 +17943,12 @@
       <c r="F375" s="2" t="inlineStr"/>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr">
@@ -17988,16 +17980,20 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr"/>
-      <c r="G376" s="2" t="inlineStr"/>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18005,7 +18001,7 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr">
@@ -18022,30 +18018,26 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G377" s="2" t="inlineStr"/>
       <c r="H377" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18053,7 +18045,7 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
@@ -18080,12 +18072,20 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F378" s="2" t="inlineStr"/>
-      <c r="G378" s="2" t="inlineStr"/>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18093,7 +18093,7 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -18120,14 +18120,10 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E379" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr"/>
       <c r="F379" s="2" t="inlineStr"/>
       <c r="G379" s="2" t="inlineStr"/>
       <c r="H379" s="2" t="inlineStr">
@@ -18164,28 +18160,24 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr"/>
-      <c r="G380" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G380" s="2" t="inlineStr"/>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
@@ -18212,23 +18204,23 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
@@ -18260,16 +18252,20 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr"/>
-      <c r="G382" s="2" t="inlineStr"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18277,7 +18273,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -18304,28 +18300,24 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G383" s="2" t="inlineStr"/>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18352,7 +18344,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -18363,12 +18355,12 @@
       <c r="F384" s="2" t="inlineStr"/>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
@@ -18400,7 +18392,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -18411,12 +18403,12 @@
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I385" s="2" t="inlineStr">
@@ -18448,24 +18440,28 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr"/>
-      <c r="G386" s="2" t="inlineStr"/>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr">
@@ -18487,12 +18483,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
@@ -18536,20 +18532,16 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr"/>
-      <c r="G388" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G388" s="2" t="inlineStr"/>
       <c r="H388" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18557,7 +18549,7 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
@@ -18584,12 +18576,20 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>光全御苑</t>
-        </is>
-      </c>
-      <c r="E389" s="2" t="inlineStr"/>
+          <t>兆美萬海</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F389" s="2" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr"/>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
+        </is>
+      </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18597,12 +18597,12 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -18624,20 +18624,12 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
-        </is>
-      </c>
-      <c r="E390" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>光全御苑</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr"/>
       <c r="F390" s="2" t="inlineStr"/>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區尚頂一街</t>
-        </is>
-      </c>
+      <c r="G390" s="2" t="inlineStr"/>
       <c r="H390" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18645,12 +18637,12 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -18672,7 +18664,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -18683,7 +18675,7 @@
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
@@ -18720,12 +18712,20 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E392" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F392" s="2" t="inlineStr"/>
-      <c r="G392" s="2" t="inlineStr"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18733,7 +18733,7 @@
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -18760,20 +18760,12 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E393" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr"/>
       <c r="F393" s="2" t="inlineStr"/>
-      <c r="G393" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G393" s="2" t="inlineStr"/>
       <c r="H393" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18781,7 +18773,7 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr">
@@ -18808,7 +18800,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -18819,7 +18811,7 @@
       <c r="F394" s="2" t="inlineStr"/>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -18856,7 +18848,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -18867,7 +18859,7 @@
       <c r="F395" s="2" t="inlineStr"/>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18904,23 +18896,23 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr"/>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I396" s="2" t="inlineStr">
@@ -18952,23 +18944,23 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr"/>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I397" s="2" t="inlineStr">
@@ -19000,7 +18992,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -19011,12 +19003,12 @@
       <c r="F398" s="2" t="inlineStr"/>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr">
@@ -19048,23 +19040,23 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr"/>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr">
@@ -19096,18 +19088,18 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr"/>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -19144,16 +19136,20 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr"/>
-      <c r="G401" s="2" t="inlineStr"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19161,7 +19157,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
@@ -19188,28 +19184,24 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr"/>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G402" s="2" t="inlineStr"/>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
@@ -19236,7 +19228,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -19247,7 +19239,7 @@
       <c r="F403" s="2" t="inlineStr"/>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
@@ -19284,23 +19276,23 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr">
@@ -19332,18 +19324,18 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
@@ -19380,7 +19372,7 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -19391,7 +19383,7 @@
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -19428,7 +19420,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -19439,7 +19431,7 @@
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -19476,18 +19468,18 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -19524,16 +19516,20 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
-      <c r="G409" s="2" t="inlineStr"/>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19541,7 +19537,7 @@
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr">
@@ -19568,20 +19564,16 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
-      <c r="G410" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G410" s="2" t="inlineStr"/>
       <c r="H410" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19589,7 +19581,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
@@ -19601,33 +19593,33 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -19664,16 +19656,20 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr"/>
-      <c r="G412" s="2" t="inlineStr"/>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19681,7 +19677,7 @@
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
@@ -19708,7 +19704,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -19752,20 +19748,16 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr"/>
-      <c r="G414" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G414" s="2" t="inlineStr"/>
       <c r="H414" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19773,7 +19765,7 @@
       </c>
       <c r="I414" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J414" s="2" t="inlineStr">
@@ -19800,7 +19792,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -19811,7 +19803,7 @@
       <c r="F415" s="2" t="inlineStr"/>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -19848,18 +19840,18 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -19896,16 +19888,20 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
-      <c r="G417" s="2" t="inlineStr"/>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19913,7 +19909,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr">
@@ -19940,20 +19936,16 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
-      <c r="G418" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G418" s="2" t="inlineStr"/>
       <c r="H418" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19961,7 +19953,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -19988,18 +19980,18 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -20036,18 +20028,18 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -20084,18 +20076,18 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -20132,12 +20124,20 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E422" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F422" s="2" t="inlineStr"/>
-      <c r="G422" s="2" t="inlineStr"/>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr">
@@ -20172,20 +20172,12 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E423" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr"/>
       <c r="F423" s="2" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G423" s="2" t="inlineStr"/>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20193,7 +20185,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -20220,16 +20212,20 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr"/>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20237,7 +20233,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20264,7 +20260,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -20308,10 +20304,14 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E426" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr"/>
       <c r="H426" s="2" t="inlineStr">
@@ -20348,14 +20348,10 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E427" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr"/>
       <c r="F427" s="2" t="inlineStr"/>
       <c r="G427" s="2" t="inlineStr"/>
       <c r="H427" s="2" t="inlineStr">
@@ -20392,20 +20388,16 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20413,7 +20405,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
@@ -20440,7 +20432,7 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -20451,7 +20443,7 @@
       <c r="F429" s="2" t="inlineStr"/>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20488,12 +20480,20 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E430" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F430" s="2" t="inlineStr"/>
-      <c r="G430" s="2" t="inlineStr"/>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20501,7 +20501,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr">
@@ -20528,20 +20528,12 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E431" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr"/>
       <c r="F431" s="2" t="inlineStr"/>
-      <c r="G431" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G431" s="2" t="inlineStr"/>
       <c r="H431" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20549,7 +20541,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -20576,16 +20568,20 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr"/>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20593,7 +20589,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20620,10 +20616,14 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F433" s="2" t="inlineStr"/>
       <c r="G433" s="2" t="inlineStr"/>
       <c r="H433" s="2" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr"/>
@@ -20700,20 +20700,12 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E435" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr"/>
       <c r="F435" s="2" t="inlineStr"/>
-      <c r="G435" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G435" s="2" t="inlineStr"/>
       <c r="H435" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20721,7 +20713,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr">
@@ -20748,7 +20740,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -20759,7 +20751,7 @@
       <c r="F436" s="2" t="inlineStr"/>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
@@ -20796,12 +20788,20 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F437" s="2" t="inlineStr"/>
-      <c r="G437" s="2" t="inlineStr"/>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20809,7 +20809,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr">
@@ -20836,14 +20836,10 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr"/>
       <c r="F438" s="2" t="inlineStr"/>
       <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
@@ -20880,7 +20876,7 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -20924,20 +20920,16 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F440" s="2" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20945,7 +20937,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -20972,12 +20964,20 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E441" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -21012,28 +21012,20 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E442" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr"/>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21060,20 +21052,28 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F443" s="2" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr"/>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
@@ -21100,7 +21100,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr"/>
@@ -21140,20 +21140,12 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E445" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr"/>
       <c r="F445" s="2" t="inlineStr"/>
-      <c r="G445" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G445" s="2" t="inlineStr"/>
       <c r="H445" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21161,7 +21153,7 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr">
@@ -21188,12 +21180,20 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F446" s="2" t="inlineStr"/>
-      <c r="G446" s="2" t="inlineStr"/>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21201,7 +21201,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
@@ -21228,20 +21228,12 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr"/>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G447" s="2" t="inlineStr"/>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21249,7 +21241,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21276,16 +21268,20 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr"/>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21293,7 +21289,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21320,20 +21316,16 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G449" s="2" t="inlineStr"/>
       <c r="H449" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21341,7 +21333,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21368,16 +21360,20 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr"/>
-      <c r="G450" s="2" t="inlineStr"/>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21385,7 +21381,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr">
@@ -21412,7 +21408,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -21456,20 +21452,16 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr"/>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21477,7 +21469,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
@@ -21504,16 +21496,20 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr"/>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21521,7 +21517,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr">
@@ -21548,7 +21544,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>立信悦榕</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -21570,7 +21566,7 @@
       </c>
       <c r="J454" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -21592,7 +21588,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -21614,7 +21610,7 @@
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -21636,7 +21632,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -21680,20 +21676,16 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr"/>
-      <c r="G457" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G457" s="2" t="inlineStr"/>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21701,7 +21693,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr">
@@ -21728,7 +21720,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -21739,7 +21731,7 @@
       <c r="F458" s="2" t="inlineStr"/>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -21776,16 +21768,20 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr"/>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21793,7 +21789,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21820,7 +21816,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -21864,7 +21860,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -21908,7 +21904,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -21952,10 +21948,14 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E463" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F463" s="2" t="inlineStr"/>
       <c r="G463" s="2" t="inlineStr"/>
       <c r="H463" s="2" t="inlineStr">
@@ -21992,14 +21992,10 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E464" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr"/>
       <c r="F464" s="2" t="inlineStr"/>
       <c r="G464" s="2" t="inlineStr"/>
       <c r="H464" s="2" t="inlineStr">
@@ -22036,7 +22032,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -22080,7 +22076,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -22124,7 +22120,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22168,7 +22164,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22212,20 +22208,16 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
-      <c r="G469" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G469" s="2" t="inlineStr"/>
       <c r="H469" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22233,7 +22225,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
@@ -22255,21 +22247,25 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
-      <c r="G470" s="2" t="inlineStr"/>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22277,7 +22273,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr">
@@ -22304,20 +22300,16 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr"/>
-      <c r="G471" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G471" s="2" t="inlineStr"/>
       <c r="H471" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22325,7 +22317,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
@@ -22352,16 +22344,20 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr"/>
-      <c r="G472" s="2" t="inlineStr"/>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H472" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22369,7 +22365,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
@@ -22396,7 +22392,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -22440,7 +22436,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -22484,20 +22480,16 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr"/>
-      <c r="G475" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G475" s="2" t="inlineStr"/>
       <c r="H475" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22505,7 +22497,7 @@
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J475" s="2" t="inlineStr">
@@ -22532,16 +22524,20 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr"/>
-      <c r="G476" s="2" t="inlineStr"/>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22549,7 +22545,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr">
@@ -22576,7 +22572,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -22620,7 +22616,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -22642,7 +22638,7 @@
       </c>
       <c r="J478" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22664,20 +22660,16 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G479" s="2" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22685,12 +22677,12 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22712,18 +22704,18 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
       <c r="G480" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H480" s="2" t="inlineStr">
@@ -22760,18 +22752,18 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22808,18 +22800,18 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
@@ -22856,12 +22848,20 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E483" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E483" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F483" s="2" t="inlineStr"/>
-      <c r="G483" s="2" t="inlineStr"/>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J483" s="2" t="inlineStr">
@@ -22896,20 +22896,12 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr"/>
       <c r="F484" s="2" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G484" s="2" t="inlineStr"/>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22917,7 +22909,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
@@ -22944,16 +22936,20 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr"/>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22961,7 +22957,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -22988,7 +22984,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -23032,7 +23028,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -23076,7 +23072,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -23120,20 +23116,16 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr"/>
-      <c r="G489" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G489" s="2" t="inlineStr"/>
       <c r="H489" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23141,7 +23133,7 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr">
@@ -23168,16 +23160,20 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr"/>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23185,7 +23181,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
@@ -23212,7 +23208,7 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -23256,20 +23252,16 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G492" s="2" t="inlineStr"/>
       <c r="H492" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23277,7 +23269,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -23304,16 +23296,20 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr"/>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23321,7 +23317,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23348,10 +23344,14 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F494" s="2" t="inlineStr"/>
       <c r="G494" s="2" t="inlineStr"/>
       <c r="H494" s="2" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="J494" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23388,20 +23388,12 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E495" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr"/>
       <c r="F495" s="2" t="inlineStr"/>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G495" s="2" t="inlineStr"/>
       <c r="H495" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23409,12 +23401,12 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23436,16 +23428,20 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr"/>
-      <c r="G496" s="2" t="inlineStr"/>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23453,7 +23449,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr">
@@ -23480,7 +23476,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -23524,20 +23520,16 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr"/>
-      <c r="G498" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G498" s="2" t="inlineStr"/>
       <c r="H498" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23545,7 +23537,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr">
@@ -23572,7 +23564,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -23583,7 +23575,7 @@
       <c r="F499" s="2" t="inlineStr"/>
       <c r="G499" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H499" s="2" t="inlineStr">
@@ -23620,7 +23612,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -23631,7 +23623,7 @@
       <c r="F500" s="2" t="inlineStr"/>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
@@ -23668,12 +23660,20 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E501" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr"/>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -23708,20 +23708,12 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E502" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr"/>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G502" s="2" t="inlineStr"/>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23729,7 +23721,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23756,16 +23748,20 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr"/>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23773,7 +23769,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr">
@@ -23800,7 +23796,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -23844,20 +23840,16 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr"/>
-      <c r="G505" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G505" s="2" t="inlineStr"/>
       <c r="H505" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23865,7 +23857,7 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J505" s="2" t="inlineStr">
@@ -23892,23 +23884,23 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I506" s="2" t="inlineStr">
@@ -23940,24 +23932,28 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
-      <c r="G507" s="2" t="inlineStr"/>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J507" s="2" t="inlineStr">
@@ -23984,7 +23980,7 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -24028,7 +24024,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -24072,20 +24068,16 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr"/>
-      <c r="G510" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G510" s="2" t="inlineStr"/>
       <c r="H510" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24093,7 +24085,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
@@ -24120,16 +24112,20 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr"/>
-      <c r="G511" s="2" t="inlineStr"/>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24137,7 +24133,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr">
@@ -24164,20 +24160,16 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G512" s="2" t="inlineStr"/>
       <c r="H512" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24185,7 +24177,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -24212,16 +24204,20 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr"/>
-      <c r="G513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24229,7 +24225,7 @@
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J513" s="2" t="inlineStr">
@@ -24256,10 +24252,14 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E514" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E514" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F514" s="2" t="inlineStr"/>
       <c r="G514" s="2" t="inlineStr"/>
       <c r="H514" s="2" t="inlineStr">
@@ -24296,14 +24296,10 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E515" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr"/>
       <c r="F515" s="2" t="inlineStr"/>
       <c r="G515" s="2" t="inlineStr"/>
       <c r="H515" s="2" t="inlineStr">
@@ -24340,7 +24336,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -24384,10 +24380,14 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E517" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F517" s="2" t="inlineStr"/>
       <c r="G517" s="2" t="inlineStr"/>
       <c r="H517" s="2" t="inlineStr">
@@ -24406,15 +24406,55 @@
         </is>
       </c>
     </row>
-    <row r="519">
-      <c r="A519" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-08-05 18:18（台灣時間）　共 516 筆　資料來源：好房網、樂屋網</t>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B518" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D518" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr"/>
+      <c r="F518" s="2" t="inlineStr"/>
+      <c r="G518" s="2" t="inlineStr"/>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-08-06 18:21（台灣時間）　共 517 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J517"/>
+  <autoFilter ref="A1:J518"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$518</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$520</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J520"/>
+  <dimension ref="A1:J522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14304,14 +14304,10 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>偉鉅雙捷韻</t>
-        </is>
-      </c>
-      <c r="E297" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>偉鉅中山双匯</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr"/>
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr"/>
       <c r="H297" s="2" t="inlineStr">
@@ -14326,7 +14322,7 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14348,20 +14344,16 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>双捷橙品</t>
+          <t>偉鉅雙捷韻</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr"/>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路723號旁</t>
-        </is>
-      </c>
+      <c r="G298" s="2" t="inlineStr"/>
       <c r="H298" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14369,12 +14361,12 @@
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14396,23 +14388,23 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>君奕華品</t>
+          <t>双捷橙品</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街57巷11號</t>
+          <t>新北市中和區景平路723號旁</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
@@ -14444,23 +14436,23 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>和典永峰</t>
+          <t>君奕華品</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區立人街14巷77號</t>
+          <t>新北市中和區景新街57巷11號</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
@@ -14492,18 +14484,18 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>和御</t>
+          <t>和典永峰</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr"/>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路與新生街口</t>
+          <t>新北市中和區立人街14巷77號</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14540,7 +14532,7 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>和雅琚</t>
+          <t>和御</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -14551,7 +14543,7 @@
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區福祥路85巷口</t>
+          <t>新北市中和區連城路與新生街口</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -14588,7 +14580,7 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>大同新紀元</t>
+          <t>和雅琚</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
@@ -14599,7 +14591,7 @@
       <c r="F303" s="2" t="inlineStr"/>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路、錦和路口</t>
+          <t>新北市中和區福祥路85巷口</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -14636,18 +14628,18 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>好植</t>
+          <t>大同新紀元</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr"/>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街2號</t>
+          <t>新北市中和區連城路、錦和路口</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -14684,7 +14676,7 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>宜安三六</t>
+          <t>好植</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
@@ -14695,12 +14687,12 @@
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區保健路72號</t>
+          <t>新北市中和區景新街2號</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
@@ -14732,25 +14724,33 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>寶亞世界公舘</t>
-        </is>
-      </c>
-      <c r="E306" s="2" t="inlineStr"/>
+          <t>宜安三六</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F306" s="2" t="inlineStr"/>
-      <c r="G306" s="2" t="inlineStr"/>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區保健路72號</t>
+        </is>
+      </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14772,14 +14772,10 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
-        </is>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>寶亞世界公舘</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr"/>
       <c r="F307" s="2" t="inlineStr"/>
       <c r="G307" s="2" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
@@ -14794,7 +14790,7 @@
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14816,28 +14812,24 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠A基地</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區環河西路三段、永和路</t>
-        </is>
-      </c>
+      <c r="G308" s="2" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
@@ -14864,7 +14856,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠B基地</t>
+          <t>左岸明珠A基地</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -14880,7 +14872,7 @@
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr">
@@ -14912,7 +14904,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>忻揚馥群</t>
+          <t>左岸明珠B基地</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -14923,12 +14915,12 @@
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區南山路247號</t>
+          <t>新北市中和區環河西路三段、永和路</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
@@ -14960,29 +14952,33 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>昇陽國旭</t>
+          <t>忻揚馥群</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區南山路247號</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -15004,33 +15000,29 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>昇陽國旭</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景新街112號</t>
-        </is>
-      </c>
+      <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15052,20 +15044,28 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F313" s="2" t="inlineStr"/>
-      <c r="G313" s="2" t="inlineStr"/>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J313" s="2" t="inlineStr">
@@ -15092,7 +15092,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr"/>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>欽禾</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr"/>
@@ -15172,14 +15172,10 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr"/>
       <c r="F316" s="2" t="inlineStr"/>
       <c r="G316" s="2" t="inlineStr"/>
       <c r="H316" s="2" t="inlineStr">
@@ -15216,28 +15212,24 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G317" s="2" t="inlineStr"/>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
@@ -15264,7 +15256,7 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -15275,12 +15267,12 @@
       <c r="F318" s="2" t="inlineStr"/>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路309號</t>
+          <t>新北市中和區中和路410號</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr">
@@ -15312,16 +15304,20 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" s="2" t="inlineStr"/>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連城路309號</t>
+        </is>
+      </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15329,7 +15325,7 @@
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J319" s="2" t="inlineStr">
@@ -15356,28 +15352,24 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr"/>
-      <c r="G320" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路159巷</t>
-        </is>
-      </c>
+      <c r="G320" s="2" t="inlineStr"/>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J320" s="2" t="inlineStr">
@@ -15404,7 +15396,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr">
@@ -15415,12 +15407,12 @@
       <c r="F321" s="2" t="inlineStr"/>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連勝街26巷8號</t>
+          <t>新北市中和區景平路159巷</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr">
@@ -15452,16 +15444,20 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr"/>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連勝街26巷8號</t>
+        </is>
+      </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15469,7 +15465,7 @@
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15496,20 +15492,16 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區民有街49號</t>
-        </is>
-      </c>
+      <c r="G323" s="2" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15517,7 +15509,7 @@
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J323" s="2" t="inlineStr">
@@ -15539,23 +15531,23 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr"/>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街22巷2號</t>
+          <t>新北市中和區民有街49號</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -15592,16 +15584,20 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr"/>
-      <c r="G325" s="2" t="inlineStr"/>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松柏街22巷2號</t>
+        </is>
+      </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15609,7 +15605,7 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr">
@@ -15636,20 +15632,16 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr"/>
-      <c r="G326" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
-        </is>
-      </c>
+      <c r="G326" s="2" t="inlineStr"/>
       <c r="H326" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15657,7 +15649,7 @@
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J326" s="2" t="inlineStr">
@@ -15684,18 +15676,18 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路二段521號</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -15732,23 +15724,23 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr">
@@ -15780,18 +15772,18 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區金門街287巷</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -15828,24 +15820,28 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
-      <c r="G330" s="2" t="inlineStr"/>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區存德街15號</t>
+        </is>
+      </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J330" s="2" t="inlineStr">
@@ -15872,20 +15868,16 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路</t>
-        </is>
-      </c>
+      <c r="G331" s="2" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15893,7 +15885,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
@@ -15920,12 +15912,20 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>寶格利</t>
-        </is>
-      </c>
-      <c r="E332" s="2" t="inlineStr"/>
+          <t>大業</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F332" s="2" t="inlineStr"/>
-      <c r="G332" s="2" t="inlineStr"/>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區華江一路</t>
+        </is>
+      </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15933,12 +15933,12 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -15960,33 +15960,25 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
-        </is>
-      </c>
-      <c r="E333" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>寶格利</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr"/>
       <c r="F333" s="2" t="inlineStr"/>
-      <c r="G333" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區縣民大道一段</t>
-        </is>
-      </c>
+      <c r="G333" s="2" t="inlineStr"/>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16000,7 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -16019,12 +16011,12 @@
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
@@ -16056,7 +16048,7 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
@@ -16067,12 +16059,12 @@
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr">
@@ -16104,18 +16096,18 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路二段183號旁</t>
+          <t>新北市板橋區文化路二段與華江一路口</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -16152,23 +16144,23 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr"/>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅東路</t>
+          <t>新北市板橋區民生路二段183號旁</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr">
@@ -16200,7 +16192,7 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -16211,7 +16203,7 @@
       <c r="F338" s="2" t="inlineStr"/>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -16248,18 +16240,18 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -16296,23 +16288,23 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr">
@@ -16344,7 +16336,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -16355,7 +16347,7 @@
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16392,18 +16384,18 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -16440,18 +16432,18 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -16488,7 +16480,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -16499,7 +16491,7 @@
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區田單北街61號</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16536,18 +16528,18 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區三民路二段72號</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -16584,24 +16576,28 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr"/>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區大華街72號旁</t>
+        </is>
+      </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J346" s="2" t="inlineStr">
@@ -16628,7 +16624,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -16672,28 +16668,24 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
-      <c r="G348" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
-        </is>
-      </c>
+      <c r="G348" s="2" t="inlineStr"/>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J348" s="2" t="inlineStr">
@@ -16720,18 +16712,18 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16768,7 +16760,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -16779,7 +16771,7 @@
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16816,7 +16808,7 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
@@ -16827,7 +16819,7 @@
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -16864,23 +16856,23 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr">
@@ -16912,23 +16904,23 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林濱河帝景</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr">
@@ -16960,7 +16952,7 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -16971,7 +16963,7 @@
       <c r="F354" s="2" t="inlineStr"/>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
@@ -17008,20 +17000,28 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E355" s="2" t="inlineStr"/>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" s="2" t="inlineStr"/>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
+        </is>
+      </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I355" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J355" s="2" t="inlineStr">
@@ -17048,28 +17048,20 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
-        </is>
-      </c>
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr"/>
       <c r="F356" s="2" t="inlineStr"/>
-      <c r="G356" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
-        </is>
-      </c>
+      <c r="G356" s="2" t="inlineStr"/>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J356" s="2" t="inlineStr">
@@ -17096,7 +17088,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -17107,12 +17099,12 @@
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr">
@@ -17144,7 +17136,7 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -17155,7 +17147,7 @@
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路600號對面</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -17192,18 +17184,18 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -17240,18 +17232,18 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr"/>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -17288,7 +17280,7 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -17299,12 +17291,12 @@
       <c r="F361" s="2" t="inlineStr"/>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
@@ -17336,23 +17328,23 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區南雅南路二段68號</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -17384,23 +17376,23 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr">
@@ -17432,24 +17424,28 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
-      <c r="G364" s="2" t="inlineStr"/>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段65號</t>
+        </is>
+      </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J364" s="2" t="inlineStr">
@@ -17476,28 +17472,24 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>遠揚之森A⁺</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr"/>
-      <c r="G365" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區信義段217地號</t>
-        </is>
-      </c>
+      <c r="G365" s="2" t="inlineStr"/>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J365" s="2" t="inlineStr">
@@ -17524,7 +17516,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -17535,12 +17527,12 @@
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
@@ -17572,12 +17564,20 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E367" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F367" s="2" t="inlineStr"/>
-      <c r="G367" s="2" t="inlineStr"/>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17585,7 +17585,7 @@
       </c>
       <c r="I367" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J367" s="2" t="inlineStr">
@@ -17607,25 +17607,17 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
-        </is>
-      </c>
-      <c r="E368" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr"/>
       <c r="F368" s="2" t="inlineStr"/>
-      <c r="G368" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區環河東路一段152號</t>
-        </is>
-      </c>
+      <c r="G368" s="2" t="inlineStr"/>
       <c r="H368" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17633,7 +17625,7 @@
       </c>
       <c r="I368" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J368" s="2" t="inlineStr">
@@ -17660,12 +17652,20 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E369" s="2" t="inlineStr"/>
+          <t>M PLUS</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" s="2" t="inlineStr"/>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區環河東路一段152號</t>
+        </is>
+      </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -17700,20 +17700,12 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E370" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr"/>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G370" s="2" t="inlineStr"/>
       <c r="H370" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17721,7 +17713,7 @@
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
@@ -17748,23 +17740,23 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
@@ -17796,7 +17788,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -17807,12 +17799,12 @@
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
@@ -17844,7 +17836,7 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -17855,12 +17847,12 @@
       <c r="F373" s="2" t="inlineStr"/>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I373" s="2" t="inlineStr">
@@ -17892,20 +17884,28 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -17932,28 +17932,20 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr"/>
       <c r="F375" s="2" t="inlineStr"/>
-      <c r="G375" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G375" s="2" t="inlineStr"/>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -17980,7 +17972,7 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -17991,12 +17983,12 @@
       <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr">
@@ -18028,16 +18020,20 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18045,7 +18041,7 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
@@ -18062,30 +18058,26 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F378" s="2" t="inlineStr"/>
-      <c r="G378" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G378" s="2" t="inlineStr"/>
       <c r="H378" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18093,7 +18085,7 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -18120,12 +18112,20 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E379" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F379" s="2" t="inlineStr"/>
-      <c r="G379" s="2" t="inlineStr"/>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18133,7 +18133,7 @@
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr">
@@ -18160,14 +18160,10 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr"/>
       <c r="F380" s="2" t="inlineStr"/>
       <c r="G380" s="2" t="inlineStr"/>
       <c r="H380" s="2" t="inlineStr">
@@ -18204,28 +18200,24 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr"/>
-      <c r="G381" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G381" s="2" t="inlineStr"/>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr">
@@ -18252,23 +18244,23 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr"/>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr">
@@ -18300,16 +18292,20 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18317,7 +18313,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18344,28 +18340,24 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr"/>
-      <c r="G384" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G384" s="2" t="inlineStr"/>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -18392,7 +18384,7 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -18403,12 +18395,12 @@
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I385" s="2" t="inlineStr">
@@ -18440,7 +18432,7 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -18451,12 +18443,12 @@
       <c r="F386" s="2" t="inlineStr"/>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr">
@@ -18488,24 +18480,28 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
-      <c r="G387" s="2" t="inlineStr"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr">
@@ -18527,12 +18523,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -18576,20 +18572,16 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G389" s="2" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18597,7 +18589,7 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
@@ -18624,12 +18616,20 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>光全御苑</t>
-        </is>
-      </c>
-      <c r="E390" s="2" t="inlineStr"/>
+          <t>兆美萬海</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F390" s="2" t="inlineStr"/>
-      <c r="G390" s="2" t="inlineStr"/>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
+        </is>
+      </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18637,12 +18637,12 @@
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -18664,20 +18664,12 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
-        </is>
-      </c>
-      <c r="E391" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>光全御苑</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr"/>
       <c r="F391" s="2" t="inlineStr"/>
-      <c r="G391" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區尚頂一街</t>
-        </is>
-      </c>
+      <c r="G391" s="2" t="inlineStr"/>
       <c r="H391" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18685,12 +18677,12 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -18712,7 +18704,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -18723,7 +18715,7 @@
       <c r="F392" s="2" t="inlineStr"/>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
@@ -18760,12 +18752,20 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E393" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F393" s="2" t="inlineStr"/>
-      <c r="G393" s="2" t="inlineStr"/>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18773,7 +18773,7 @@
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr">
@@ -18800,20 +18800,12 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E394" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr"/>
       <c r="F394" s="2" t="inlineStr"/>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G394" s="2" t="inlineStr"/>
       <c r="H394" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18821,7 +18813,7 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr">
@@ -18848,7 +18840,7 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -18859,7 +18851,7 @@
       <c r="F395" s="2" t="inlineStr"/>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -18896,7 +18888,7 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -18907,7 +18899,7 @@
       <c r="F396" s="2" t="inlineStr"/>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -18944,23 +18936,23 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr"/>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I397" s="2" t="inlineStr">
@@ -18992,23 +18984,23 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr"/>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr">
@@ -19040,7 +19032,7 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -19051,12 +19043,12 @@
       <c r="F399" s="2" t="inlineStr"/>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr">
@@ -19088,23 +19080,23 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr"/>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr">
@@ -19136,18 +19128,18 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr"/>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19184,16 +19176,20 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr"/>
-      <c r="G402" s="2" t="inlineStr"/>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19201,7 +19197,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
@@ -19228,28 +19224,24 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr"/>
-      <c r="G403" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G403" s="2" t="inlineStr"/>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J403" s="2" t="inlineStr">
@@ -19276,7 +19268,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -19287,7 +19279,7 @@
       <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
@@ -19324,23 +19316,23 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
@@ -19372,18 +19364,18 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -19420,7 +19412,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -19431,7 +19423,7 @@
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -19468,7 +19460,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -19479,7 +19471,7 @@
       <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -19516,18 +19508,18 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -19564,16 +19556,20 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
-      <c r="G410" s="2" t="inlineStr"/>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19581,7 +19577,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
@@ -19608,20 +19604,16 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G411" s="2" t="inlineStr"/>
       <c r="H411" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19629,7 +19621,7 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
@@ -19641,33 +19633,33 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr"/>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -19704,16 +19696,20 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr"/>
-      <c r="G413" s="2" t="inlineStr"/>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19721,7 +19717,7 @@
       </c>
       <c r="I413" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J413" s="2" t="inlineStr">
@@ -19748,7 +19744,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -19792,20 +19788,16 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr"/>
-      <c r="G415" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G415" s="2" t="inlineStr"/>
       <c r="H415" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19813,7 +19805,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr">
@@ -19840,7 +19832,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -19851,7 +19843,7 @@
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -19888,18 +19880,18 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -19936,16 +19928,20 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
-      <c r="G418" s="2" t="inlineStr"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19953,7 +19949,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -19980,20 +19976,16 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G419" s="2" t="inlineStr"/>
       <c r="H419" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20001,7 +19993,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
@@ -20028,18 +20020,18 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -20076,18 +20068,18 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -20124,18 +20116,18 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr"/>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -20172,12 +20164,20 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E423" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F423" s="2" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20185,7 +20185,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -20212,20 +20212,12 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E424" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr"/>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20233,7 +20225,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20260,16 +20252,20 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
-      <c r="G425" s="2" t="inlineStr"/>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H425" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20277,7 +20273,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr">
@@ -20304,7 +20300,7 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -20348,10 +20344,14 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E427" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F427" s="2" t="inlineStr"/>
       <c r="G427" s="2" t="inlineStr"/>
       <c r="H427" s="2" t="inlineStr">
@@ -20388,14 +20388,10 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E428" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr"/>
       <c r="F428" s="2" t="inlineStr"/>
       <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr">
@@ -20432,20 +20428,16 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr"/>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G429" s="2" t="inlineStr"/>
       <c r="H429" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20453,7 +20445,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr">
@@ -20480,7 +20472,7 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -20491,7 +20483,7 @@
       <c r="F430" s="2" t="inlineStr"/>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
@@ -20528,12 +20520,20 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E431" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F431" s="2" t="inlineStr"/>
-      <c r="G431" s="2" t="inlineStr"/>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20541,7 +20541,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -20568,20 +20568,12 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr"/>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G432" s="2" t="inlineStr"/>
       <c r="H432" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20589,7 +20581,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20616,16 +20608,20 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr"/>
-      <c r="G433" s="2" t="inlineStr"/>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20633,7 +20629,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr">
@@ -20660,10 +20656,14 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E434" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F434" s="2" t="inlineStr"/>
       <c r="G434" s="2" t="inlineStr"/>
       <c r="H434" s="2" t="inlineStr">
@@ -20700,7 +20700,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr"/>
@@ -20740,20 +20740,12 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr"/>
       <c r="F436" s="2" t="inlineStr"/>
-      <c r="G436" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20761,7 +20753,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr">
@@ -20788,7 +20780,7 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
@@ -20799,7 +20791,7 @@
       <c r="F437" s="2" t="inlineStr"/>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
@@ -20836,12 +20828,20 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr"/>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20849,7 +20849,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20876,14 +20876,10 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E439" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr"/>
       <c r="F439" s="2" t="inlineStr"/>
       <c r="G439" s="2" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr">
@@ -20920,7 +20916,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -20964,20 +20960,16 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G441" s="2" t="inlineStr"/>
       <c r="H441" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20985,7 +20977,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -21012,12 +21004,20 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E442" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr"/>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21025,7 +21025,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21052,28 +21052,20 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr"/>
       <c r="F443" s="2" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
@@ -21100,20 +21092,28 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E444" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F444" s="2" t="inlineStr"/>
-      <c r="G444" s="2" t="inlineStr"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr"/>
@@ -21180,20 +21180,12 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr"/>
       <c r="F446" s="2" t="inlineStr"/>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21201,7 +21193,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
@@ -21228,12 +21220,20 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr"/>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21268,20 +21268,12 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr"/>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G448" s="2" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21289,7 +21281,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21316,16 +21308,20 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr"/>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21333,7 +21329,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21360,20 +21356,16 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr"/>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G450" s="2" t="inlineStr"/>
       <c r="H450" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21381,7 +21373,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr">
@@ -21408,16 +21400,20 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr"/>
-      <c r="G451" s="2" t="inlineStr"/>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21425,7 +21421,7 @@
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J451" s="2" t="inlineStr">
@@ -21452,7 +21448,7 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
@@ -21496,20 +21492,16 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21517,7 +21509,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr">
@@ -21544,16 +21536,20 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr"/>
-      <c r="G454" s="2" t="inlineStr"/>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21561,7 +21557,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr">
@@ -21588,7 +21584,7 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>立信悦榕</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -21610,7 +21606,7 @@
       </c>
       <c r="J455" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21628,7 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -21654,7 +21650,7 @@
       </c>
       <c r="J456" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -21676,7 +21672,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -21720,20 +21716,16 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G458" s="2" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21741,7 +21733,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
@@ -21768,7 +21760,7 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
@@ -21779,7 +21771,7 @@
       <c r="F459" s="2" t="inlineStr"/>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -21816,16 +21808,20 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21833,7 +21829,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
@@ -21860,7 +21856,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -21904,7 +21900,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -21948,7 +21944,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -21992,10 +21988,14 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E464" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F464" s="2" t="inlineStr"/>
       <c r="G464" s="2" t="inlineStr"/>
       <c r="H464" s="2" t="inlineStr">
@@ -22032,14 +22032,10 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E465" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr"/>
       <c r="F465" s="2" t="inlineStr"/>
       <c r="G465" s="2" t="inlineStr"/>
       <c r="H465" s="2" t="inlineStr">
@@ -22076,7 +22072,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -22120,7 +22116,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22164,7 +22160,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22208,7 +22204,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -22252,20 +22248,16 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr"/>
-      <c r="G470" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22273,7 +22265,7 @@
       </c>
       <c r="I470" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J470" s="2" t="inlineStr">
@@ -22295,21 +22287,25 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr"/>
-      <c r="G471" s="2" t="inlineStr"/>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22317,7 +22313,7 @@
       </c>
       <c r="I471" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J471" s="2" t="inlineStr">
@@ -22344,20 +22340,16 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F472" s="2" t="inlineStr"/>
-      <c r="G472" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22365,7 +22357,7 @@
       </c>
       <c r="I472" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J472" s="2" t="inlineStr">
@@ -22392,16 +22384,20 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F473" s="2" t="inlineStr"/>
-      <c r="G473" s="2" t="inlineStr"/>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H473" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22409,7 +22405,7 @@
       </c>
       <c r="I473" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J473" s="2" t="inlineStr">
@@ -22436,7 +22432,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -22480,7 +22476,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -22524,20 +22520,16 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr"/>
-      <c r="G476" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G476" s="2" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22545,7 +22537,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr">
@@ -22572,16 +22564,20 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr"/>
-      <c r="G477" s="2" t="inlineStr"/>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22589,7 +22585,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
@@ -22616,7 +22612,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -22660,7 +22656,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -22682,7 +22678,7 @@
       </c>
       <c r="J479" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22704,20 +22700,16 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22725,12 +22717,12 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22752,18 +22744,18 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
       <c r="G481" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H481" s="2" t="inlineStr">
@@ -22800,18 +22792,18 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
       <c r="G482" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H482" s="2" t="inlineStr">
@@ -22848,18 +22840,18 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr"/>
       <c r="G483" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H483" s="2" t="inlineStr">
@@ -22896,12 +22888,20 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E484" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E484" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F484" s="2" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr"/>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22909,7 +22909,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
@@ -22936,20 +22936,12 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E485" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E485" s="2" t="inlineStr"/>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G485" s="2" t="inlineStr"/>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22957,7 +22949,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -22984,16 +22976,20 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr"/>
-      <c r="G486" s="2" t="inlineStr"/>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23001,7 +22997,7 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
@@ -23028,7 +23024,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -23072,7 +23068,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -23116,7 +23112,7 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -23160,20 +23156,16 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G490" s="2" t="inlineStr"/>
       <c r="H490" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23181,7 +23173,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
@@ -23208,16 +23200,20 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr"/>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23225,7 +23221,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -23252,7 +23248,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -23296,20 +23292,16 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G493" s="2" t="inlineStr"/>
       <c r="H493" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23317,7 +23309,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23344,16 +23336,20 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr"/>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23361,7 +23357,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
@@ -23388,10 +23384,14 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E495" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F495" s="2" t="inlineStr"/>
       <c r="G495" s="2" t="inlineStr"/>
       <c r="H495" s="2" t="inlineStr">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="J495" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23428,20 +23428,12 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E496" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E496" s="2" t="inlineStr"/>
       <c r="F496" s="2" t="inlineStr"/>
-      <c r="G496" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G496" s="2" t="inlineStr"/>
       <c r="H496" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23449,12 +23441,12 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23476,16 +23468,20 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr"/>
-      <c r="G497" s="2" t="inlineStr"/>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23493,7 +23489,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr">
@@ -23520,7 +23516,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23564,20 +23560,16 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G499" s="2" t="inlineStr"/>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23585,7 +23577,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -23612,7 +23604,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -23623,7 +23615,7 @@
       <c r="F500" s="2" t="inlineStr"/>
       <c r="G500" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H500" s="2" t="inlineStr">
@@ -23660,7 +23652,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -23671,7 +23663,7 @@
       <c r="F501" s="2" t="inlineStr"/>
       <c r="G501" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H501" s="2" t="inlineStr">
@@ -23708,12 +23700,20 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E502" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23721,7 +23721,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23748,20 +23748,12 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E503" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr"/>
       <c r="F503" s="2" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G503" s="2" t="inlineStr"/>
       <c r="H503" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23769,7 +23761,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr">
@@ -23796,16 +23788,20 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr"/>
-      <c r="G504" s="2" t="inlineStr"/>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H504" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23813,7 +23809,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
@@ -23840,7 +23836,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -23884,20 +23880,16 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr"/>
-      <c r="G506" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G506" s="2" t="inlineStr"/>
       <c r="H506" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23905,7 +23897,7 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
@@ -23932,23 +23924,23 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I507" s="2" t="inlineStr">
@@ -23980,24 +23972,28 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr"/>
-      <c r="G508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -24024,7 +24020,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>立鴻晶硯</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -24046,7 +24042,7 @@
       </c>
       <c r="J509" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24068,7 +24064,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -24112,20 +24108,16 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr"/>
-      <c r="G511" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G511" s="2" t="inlineStr"/>
       <c r="H511" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24133,7 +24125,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr">
@@ -24160,7 +24152,7 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -24204,18 +24196,18 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr"/>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區環區西路597號</t>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
@@ -24252,7 +24244,7 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -24296,12 +24288,20 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E515" s="2" t="inlineStr"/>
+          <t>薪成家II</t>
+        </is>
+      </c>
+      <c r="E515" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F515" s="2" t="inlineStr"/>
-      <c r="G515" s="2" t="inlineStr"/>
+      <c r="G515" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
+          <t>逸偉A+</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -24380,14 +24380,10 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
-        </is>
-      </c>
-      <c r="E517" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E517" s="2" t="inlineStr"/>
       <c r="F517" s="2" t="inlineStr"/>
       <c r="G517" s="2" t="inlineStr"/>
       <c r="H517" s="2" t="inlineStr">
@@ -24424,10 +24420,14 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E518" s="2" t="inlineStr"/>
+          <t>鈞貴極美II</t>
+        </is>
+      </c>
+      <c r="E518" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F518" s="2" t="inlineStr"/>
       <c r="G518" s="2" t="inlineStr"/>
       <c r="H518" s="2" t="inlineStr">
@@ -24446,15 +24446,99 @@
         </is>
       </c>
     </row>
+    <row r="519">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C519" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D519" s="2" t="inlineStr">
+        <is>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E519" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
+      <c r="F519" s="2" t="inlineStr"/>
+      <c r="G519" s="2" t="inlineStr"/>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
     <row r="520">
-      <c r="A520" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-08-06 18:21（台灣時間）　共 517 筆　資料來源：好房網、樂屋網</t>
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B520" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D520" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E520" s="2" t="inlineStr"/>
+      <c r="F520" s="2" t="inlineStr"/>
+      <c r="G520" s="2" t="inlineStr"/>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-08-07 13:59（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J518"/>
+  <autoFilter ref="A1:J520"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24533,7 +24533,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-07 13:59（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-08 12:36（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24533,7 +24533,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-08 12:36（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-09 12:52（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24533,7 +24533,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-09 12:52（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-10 13:16（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24533,7 +24533,7 @@
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-10 13:16（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-11 10:35（台灣時間）　共 519 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -20209,15 +20209,11 @@
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區永順一街30號旁</t>
-        </is>
-      </c>
+      <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20225,7 +20221,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20653,15 +20649,11 @@
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr"/>
-      <c r="G434" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G434" s="2" t="inlineStr"/>
       <c r="H434" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20669,7 +20661,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr">
@@ -20825,15 +20817,11 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20841,7 +20829,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -21265,15 +21253,11 @@
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G448" s="2" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21281,7 +21265,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21805,15 +21789,11 @@
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G460" s="2" t="inlineStr"/>
       <c r="H460" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21821,7 +21801,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
@@ -24573,7 +24553,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-12 10:52（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-13 11:06（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -4405,15 +4405,11 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>新北市泰山區明志路一段168號</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4421,7 +4417,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -4541,15 +4537,11 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>新北市泰山區莊泰路與義東街口</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4557,7 +4549,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -7541,15 +7533,11 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>新北市樹林區西圳街二段12號旁</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7557,7 +7545,7 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
@@ -7584,20 +7572,16 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>騰翔 樹与苑</t>
+          <t>騰翔樹与苑</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>新北市樹林區民權街68號旁</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7605,7 +7589,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -7729,15 +7713,11 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鳳七路與龍三路口</t>
-        </is>
-      </c>
+      <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7745,7 +7725,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -7825,15 +7805,11 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區國中街與高職東街交叉口</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7841,7 +7817,7 @@
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
@@ -8249,15 +8225,11 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鶯桃路413巷</t>
-        </is>
-      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8265,7 +8237,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8297,15 +8269,11 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鶯歌路285旁</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8313,7 +8281,7 @@
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
@@ -8441,15 +8409,11 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鶯桃路二段與鳳吉一街路口</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8457,7 +8421,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -24553,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-13 11:06（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-14 11:05（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24517,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-14 11:05（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-15 09:55（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24517,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-15 09:55（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-16 10:02（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24517,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-16 10:02（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-17 10:00（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24517,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-17 10:00（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-18 09:57（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24517,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-18 09:57（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-19 09:58（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24517,7 +24517,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-19 09:58（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-20 09:58（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -4357,15 +4357,11 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>新北市泰山區明志路一段215號</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4373,7 +4369,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -24517,7 +24513,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-20 09:58（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-21 10:03（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24513,7 +24513,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-21 10:03（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-22 09:57（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24513,7 +24513,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-22 09:57（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-23 10:05（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -6612,7 +6612,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -24513,7 +24513,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-23 10:05（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-24 10:04（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -4259,17 +4259,9 @@
           <t>合嘉楓疆</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+      <c r="E82" s="2" t="inlineStr"/>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>新北市泰山區和平街及楓樹街交叉口</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4277,7 +4269,7 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -7479,17 +7471,9 @@
           <t>欣好蒔光</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+      <c r="E152" s="2" t="inlineStr"/>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>新北市樹林區柑園街一段170號對面</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7497,7 +7481,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
@@ -7983,17 +7967,9 @@
           <t>國華綻</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+      <c r="E163" s="2" t="inlineStr"/>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區鶯桃路182巷96弄</t>
-        </is>
-      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8001,7 +7977,7 @@
       </c>
       <c r="I163" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J163" s="2" t="inlineStr">
@@ -8079,17 +8055,9 @@
           <t>富霖富鄰</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+      <c r="E165" s="2" t="inlineStr"/>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>新北市鶯歌區永吉段 570 地號</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8097,7 +8065,7 @@
       </c>
       <c r="I165" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J165" s="2" t="inlineStr">
@@ -24513,7 +24481,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-24 10:04（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-25 09:59（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24481,7 +24481,7 @@
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-25 09:59（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-26 10:05（台灣時間）　共 520 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24525,7 +24525,7 @@
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-27 18:01（台灣時間）　共 521 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-28 19:34（台灣時間）　共 521 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24569,7 +24569,7 @@
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-29 15:13（台灣時間）　共 522 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-08-30 13:34（台灣時間）　共 522 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-08-31 13:48（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-01 13:21（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-01 13:21（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-02 12:47（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-02 12:47（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-03 12:42（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-03 12:42（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-04 12:45（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-04 12:45（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-05 12:41（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
